--- a/evidence/metrc/Evaluation_NY_completed.xlsx
+++ b/evidence/metrc/Evaluation_NY_completed.xlsx
@@ -936,7 +936,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="261">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1574,11 +1574,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2433,22 +2439,22 @@
       </c>
       <c r="B5" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C5" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>59123</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:09Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
@@ -2456,10 +2462,14 @@
           <t> </t>
         </is>
       </c>
-      <c r="G5" s="104" t="n"/>
-      <c r="H5" s="247" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G5" s="104" t="inlineStr">
+        <is>
+          <t>https://sandbox-api-ny.metrc.com/plantbatches/v2/plantings?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H5" s="261" t="inlineStr">
+        <is>
+          <t>[{"Name":"TP Batch 0827-1402","Type":"Clone","Count":6,"Strain":"Terpenomics Strain 0827-1402","Location":"Terpenomics Loc 0827-1402 (Updated)","Sublocation":null,"PatientLicenseNumber":null,"ActualDate":"2026-08-27","SourcePlantBatches":null}]</t>
         </is>
       </c>
     </row>
@@ -2469,13 +2479,13 @@
           <t>Create a new plant batch containing 6 plants using:</t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
       <c r="G6" s="109" t="n"/>
-      <c r="H6" s="256" t="n"/>
+      <c r="H6" s="257" t="n"/>
     </row>
     <row r="7" ht="21.95" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A7" s="121" t="inlineStr">
@@ -2483,13 +2493,13 @@
           <t>POST /plantbatches/v2/plantings</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
       <c r="G7" s="114" t="n"/>
-      <c r="H7" s="258" t="n"/>
+      <c r="H7" s="259" t="n"/>
     </row>
     <row r="8" ht="21.95" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A8" s="133" t="n"/>
@@ -2509,33 +2519,37 @@
       </c>
       <c r="B9" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C9" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>217773</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:09Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G9" s="104" t="n"/>
-      <c r="H9" s="247" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>1A4120300004532000001445</t>
+        </is>
+      </c>
+      <c r="G9" s="104" t="inlineStr">
+        <is>
+          <t>https://sandbox-api-ny.metrc.com/plantbatches/v2/packages?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H9" s="261" t="inlineStr">
+        <is>
+          <t>[{"Id":null,"PlantBatch":"TP Batch 0827-1402","Count":3,"Location":"Terpenomics Loc 0827-1402 (Updated)","Sublocation":null,"Item":"Terpenomics Clone 0827-1402","Tag":"1A4120300004532000001445","PatientLicenseNumber":null,"Note":"Evaluation step","IsTradeSample":false,"IsDonation":false,"ActualDate":"2026-08-27"}]</t>
         </is>
       </c>
     </row>
@@ -2545,13 +2559,13 @@
           <t>Create a package containing 3 clones from the Plant Batch ceated in step 1 using:</t>
         </is>
       </c>
-      <c r="B10" s="255" t="n"/>
-      <c r="C10" s="256" t="n"/>
-      <c r="D10" s="256" t="n"/>
-      <c r="E10" s="256" t="n"/>
-      <c r="F10" s="256" t="n"/>
+      <c r="B10" s="256" t="n"/>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+      <c r="F10" s="257" t="n"/>
       <c r="G10" s="109" t="n"/>
-      <c r="H10" s="256" t="n"/>
+      <c r="H10" s="257" t="n"/>
     </row>
     <row r="11" ht="21.95" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A11" s="121" t="inlineStr">
@@ -2559,13 +2573,13 @@
           <t>POST /plantbatches/v2/packages</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
-      <c r="C11" s="258" t="n"/>
-      <c r="D11" s="258" t="n"/>
-      <c r="E11" s="258" t="n"/>
-      <c r="F11" s="258" t="n"/>
+      <c r="B11" s="258" t="n"/>
+      <c r="C11" s="259" t="n"/>
+      <c r="D11" s="259" t="n"/>
+      <c r="E11" s="259" t="n"/>
+      <c r="F11" s="259" t="n"/>
       <c r="G11" s="114" t="n"/>
-      <c r="H11" s="258" t="n"/>
+      <c r="H11" s="259" t="n"/>
     </row>
     <row r="12" ht="21.95" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A12" s="133" t="n"/>
@@ -2578,33 +2592,37 @@
       </c>
       <c r="B13" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C13" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>751530, 751531</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:09Z</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G13" s="104" t="n"/>
-      <c r="H13" s="247" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>1A4120200004532000001595, 1A4120200004532000001596</t>
+        </is>
+      </c>
+      <c r="G13" s="104" t="inlineStr">
+        <is>
+          <t>https://sandbox-api-ny.metrc.com/plantbatches/v2/growthphase?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H13" s="261" t="inlineStr">
+        <is>
+          <t>[{"Name":"TP Batch 0827-1402","Count":2,"StartingTag":"1A4120200004532000001595","GrowthPhase":"Vegetative","NewLocation":"Terpenomics Loc 0827-1402 (Updated)","NewSublocation":null,"GrowthDate":"2026-08-27","PatientLicenseNumber":null}]</t>
         </is>
       </c>
     </row>
@@ -2614,13 +2632,13 @@
           <t xml:space="preserve"> Change the growth phase of 2 of the plants created in Step 1 to the Vegetative Stage using:</t>
         </is>
       </c>
-      <c r="B14" s="255" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="256" t="n"/>
+      <c r="B14" s="256" t="n"/>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+      <c r="F14" s="257" t="n"/>
       <c r="G14" s="109" t="n"/>
-      <c r="H14" s="256" t="n"/>
+      <c r="H14" s="257" t="n"/>
     </row>
     <row r="15" ht="21.95" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A15" s="121" t="inlineStr">
@@ -2628,13 +2646,13 @@
           <t>POST /plantbatches/v2/growthphase</t>
         </is>
       </c>
-      <c r="B15" s="257" t="n"/>
-      <c r="C15" s="258" t="n"/>
-      <c r="D15" s="258" t="n"/>
-      <c r="E15" s="258" t="n"/>
-      <c r="F15" s="258" t="n"/>
+      <c r="B15" s="258" t="n"/>
+      <c r="C15" s="259" t="n"/>
+      <c r="D15" s="259" t="n"/>
+      <c r="E15" s="259" t="n"/>
+      <c r="F15" s="259" t="n"/>
       <c r="G15" s="114" t="n"/>
-      <c r="H15" s="258" t="n"/>
+      <c r="H15" s="259" t="n"/>
     </row>
     <row r="16" ht="21.95" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A16" s="124" t="n"/>
@@ -2654,22 +2672,22 @@
       </c>
       <c r="B17" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C17" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D17" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>59123</t>
         </is>
       </c>
       <c r="E17" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:09Z</t>
         </is>
       </c>
       <c r="F17" s="247" t="inlineStr">
@@ -2677,10 +2695,14 @@
           <t> </t>
         </is>
       </c>
-      <c r="G17" s="104" t="n"/>
-      <c r="H17" s="247" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G17" s="104" t="inlineStr">
+        <is>
+          <t>https://sandbox-api-ny.metrc.com/plantbatches/v2/?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H17" s="261" t="inlineStr">
+        <is>
+          <t>[{"PlantBatch":"TP Batch 0827-1402","Count":1,"WasteMethodName":null,"WasteMaterialMixed":null,"WasteReasonName":"Waste","ReasonNote":"Evaluation step — destroying one immature plant.","WasteWeight":1.0,"WasteUnitOfMeasure":"Grams","ActualDate":"2026-08-27"}]</t>
         </is>
       </c>
     </row>
@@ -2690,13 +2712,13 @@
           <t xml:space="preserve">  Destroy 1 of the plants using:</t>
         </is>
       </c>
-      <c r="B18" s="255" t="n"/>
-      <c r="C18" s="256" t="n"/>
-      <c r="D18" s="256" t="n"/>
-      <c r="E18" s="256" t="n"/>
-      <c r="F18" s="256" t="n"/>
+      <c r="B18" s="256" t="n"/>
+      <c r="C18" s="257" t="n"/>
+      <c r="D18" s="257" t="n"/>
+      <c r="E18" s="257" t="n"/>
+      <c r="F18" s="257" t="n"/>
       <c r="G18" s="109" t="n"/>
-      <c r="H18" s="256" t="n"/>
+      <c r="H18" s="257" t="n"/>
     </row>
     <row r="19" ht="21.95" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A19" s="121" t="inlineStr">
@@ -2704,13 +2726,13 @@
           <t>DELETE /plantbatches/v2/</t>
         </is>
       </c>
-      <c r="B19" s="257" t="n"/>
-      <c r="C19" s="258" t="n"/>
-      <c r="D19" s="258" t="n"/>
-      <c r="E19" s="258" t="n"/>
-      <c r="F19" s="258" t="n"/>
+      <c r="B19" s="258" t="n"/>
+      <c r="C19" s="259" t="n"/>
+      <c r="D19" s="259" t="n"/>
+      <c r="E19" s="259" t="n"/>
+      <c r="F19" s="259" t="n"/>
       <c r="G19" s="114" t="n"/>
-      <c r="H19" s="258" t="n"/>
+      <c r="H19" s="259" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="176" t="n"/>
@@ -3038,12 +3060,12 @@
       </c>
       <c r="B6" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C6" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D6" s="248" t="inlineStr">
@@ -3053,23 +3075,23 @@
       </c>
       <c r="E6" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:00:21+00:00</t>
         </is>
       </c>
       <c r="F6" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120200004532000001006</t>
         </is>
       </c>
       <c r="G6" s="104" t="n"/>
       <c r="H6" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I6" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/plants/v2/location?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="I6" s="262" t="inlineStr">
+        <is>
+          <t>[{"Id":null,"Label":"1A4120200004532000001006","Location":"Terpenomics Loc 0827-1402 (Updated)","Sublocation":null,"ActualDate":"2026-08-27"}]</t>
         </is>
       </c>
     </row>
@@ -3079,14 +3101,14 @@
           <t>Move 1 of the Flowering Plants to a Different location using:</t>
         </is>
       </c>
-      <c r="B7" s="255" t="n"/>
-      <c r="C7" s="256" t="n"/>
-      <c r="D7" s="256" t="n"/>
-      <c r="E7" s="256" t="n"/>
-      <c r="F7" s="256" t="n"/>
+      <c r="B7" s="256" t="n"/>
+      <c r="C7" s="257" t="n"/>
+      <c r="D7" s="257" t="n"/>
+      <c r="E7" s="257" t="n"/>
+      <c r="F7" s="257" t="n"/>
       <c r="G7" s="109" t="n"/>
-      <c r="H7" s="256" t="n"/>
-      <c r="I7" s="256" t="n"/>
+      <c r="H7" s="257" t="n"/>
+      <c r="I7" s="257" t="n"/>
     </row>
     <row r="8" ht="16.15" customHeight="1" thickBot="1">
       <c r="A8" s="121" t="inlineStr">
@@ -3094,14 +3116,14 @@
           <t>PUT /plants/v2/location</t>
         </is>
       </c>
-      <c r="B8" s="257" t="n"/>
-      <c r="C8" s="258" t="n"/>
-      <c r="D8" s="258" t="n"/>
-      <c r="E8" s="258" t="n"/>
-      <c r="F8" s="258" t="n"/>
+      <c r="B8" s="258" t="n"/>
+      <c r="C8" s="259" t="n"/>
+      <c r="D8" s="259" t="n"/>
+      <c r="E8" s="259" t="n"/>
+      <c r="F8" s="259" t="n"/>
       <c r="G8" s="114" t="n"/>
-      <c r="H8" s="258" t="n"/>
-      <c r="I8" s="258" t="n"/>
+      <c r="H8" s="259" t="n"/>
+      <c r="I8" s="259" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" thickBot="1">
       <c r="A9" s="33" t="n"/>
@@ -3114,38 +3136,42 @@
       </c>
       <c r="B10" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C10" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D10" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>59124</t>
         </is>
       </c>
       <c r="E10" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:10Z</t>
         </is>
       </c>
       <c r="F10" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G10" s="104" t="n"/>
+          <t>1A4120200004532000001006</t>
+        </is>
+      </c>
+      <c r="G10" s="104" t="inlineStr">
+        <is>
+          <t>TP Immature 0827-1402</t>
+        </is>
+      </c>
       <c r="H10" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I10" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/plants/v2/plantings?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="I10" s="262" t="inlineStr">
+        <is>
+          <t>[{"PlantLabel":"1A4120200004532000001006","PlantBatchName":"TP Immature 0827-1402","PlantBatchType":"Clone","PlantCount":3,"LocationName":"Terpenomics Loc 0827-1402 (Updated)","SublocationName":null,"StrainName":"Terpenomics Strain 0827-1402","PatientLicenseNumber":null,"ActualDate":"2026-08-27T14:02:10Z"}]</t>
         </is>
       </c>
     </row>
@@ -3155,14 +3181,14 @@
           <t>Create an Immature Plant Batch from one of the Plants using:</t>
         </is>
       </c>
-      <c r="B11" s="255" t="n"/>
-      <c r="C11" s="256" t="n"/>
-      <c r="D11" s="256" t="n"/>
-      <c r="E11" s="256" t="n"/>
-      <c r="F11" s="256" t="n"/>
+      <c r="B11" s="256" t="n"/>
+      <c r="C11" s="257" t="n"/>
+      <c r="D11" s="257" t="n"/>
+      <c r="E11" s="257" t="n"/>
+      <c r="F11" s="257" t="n"/>
       <c r="G11" s="109" t="n"/>
-      <c r="H11" s="256" t="n"/>
-      <c r="I11" s="256" t="n"/>
+      <c r="H11" s="257" t="n"/>
+      <c r="I11" s="257" t="n"/>
     </row>
     <row r="12" ht="16.15" customHeight="1" thickBot="1">
       <c r="A12" s="121" t="inlineStr">
@@ -3170,14 +3196,14 @@
           <t xml:space="preserve"> POST/plants/v2/plantings </t>
         </is>
       </c>
-      <c r="B12" s="257" t="n"/>
-      <c r="C12" s="258" t="n"/>
-      <c r="D12" s="258" t="n"/>
-      <c r="E12" s="258" t="n"/>
-      <c r="F12" s="258" t="n"/>
+      <c r="B12" s="258" t="n"/>
+      <c r="C12" s="259" t="n"/>
+      <c r="D12" s="259" t="n"/>
+      <c r="E12" s="259" t="n"/>
+      <c r="F12" s="259" t="n"/>
       <c r="G12" s="114" t="n"/>
-      <c r="H12" s="258" t="n"/>
-      <c r="I12" s="258" t="n"/>
+      <c r="H12" s="259" t="n"/>
+      <c r="I12" s="259" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="135" t="n"/>
@@ -3198,38 +3224,38 @@
       </c>
       <c r="B14" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C14" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D14" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>218906</t>
         </is>
       </c>
       <c r="E14" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:10Z</t>
         </is>
       </c>
       <c r="F14" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120300004532000001446</t>
         </is>
       </c>
       <c r="G14" s="104" t="n"/>
       <c r="H14" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I14" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/plants/v2/plantbatch/packages?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="I14" s="262" t="inlineStr">
+        <is>
+          <t>[{"PlantLabel":"1A4120200004532000001006","PackageTag":"1A4120300004532000001446","PlantBatchType":"Clone","Item":"Terpenomics Clone 0827-1402","Location":"Terpenomics Loc 0827-1402 (Updated)","Sublocation":null,"Note":null,"IsTradeSample":false,"PatientLicenseNumber":null,"IsDonation":false,"Count":3,"ActualDate":"2026-08-27T14:02:10Z"}]</t>
         </is>
       </c>
     </row>
@@ -3239,14 +3265,14 @@
           <t>Create a Package of Seeds or Clones from one of the Plants using:</t>
         </is>
       </c>
-      <c r="B15" s="255" t="n"/>
-      <c r="C15" s="256" t="n"/>
-      <c r="D15" s="256" t="n"/>
-      <c r="E15" s="256" t="n"/>
-      <c r="F15" s="256" t="n"/>
+      <c r="B15" s="256" t="n"/>
+      <c r="C15" s="257" t="n"/>
+      <c r="D15" s="257" t="n"/>
+      <c r="E15" s="257" t="n"/>
+      <c r="F15" s="257" t="n"/>
       <c r="G15" s="109" t="n"/>
-      <c r="H15" s="256" t="n"/>
-      <c r="I15" s="256" t="n"/>
+      <c r="H15" s="257" t="n"/>
+      <c r="I15" s="257" t="n"/>
     </row>
     <row r="16" ht="16.15" customHeight="1" thickBot="1">
       <c r="A16" s="121" t="inlineStr">
@@ -3254,14 +3280,14 @@
           <t xml:space="preserve">POST/plants/v2/plantbatch/packages </t>
         </is>
       </c>
-      <c r="B16" s="257" t="n"/>
-      <c r="C16" s="258" t="n"/>
-      <c r="D16" s="258" t="n"/>
-      <c r="E16" s="258" t="n"/>
-      <c r="F16" s="258" t="n"/>
+      <c r="B16" s="258" t="n"/>
+      <c r="C16" s="259" t="n"/>
+      <c r="D16" s="259" t="n"/>
+      <c r="E16" s="259" t="n"/>
+      <c r="F16" s="259" t="n"/>
       <c r="G16" s="114" t="n"/>
-      <c r="H16" s="258" t="n"/>
-      <c r="I16" s="258" t="n"/>
+      <c r="H16" s="259" t="n"/>
+      <c r="I16" s="259" t="n"/>
     </row>
     <row r="17" ht="13.15" customHeight="1" thickBot="1">
       <c r="A17" s="135" t="n"/>
@@ -3282,38 +3308,38 @@
       </c>
       <c r="B18" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C18" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D18" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>752259</t>
         </is>
       </c>
       <c r="E18" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:11Z</t>
         </is>
       </c>
       <c r="F18" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120200004532000001085</t>
         </is>
       </c>
       <c r="G18" s="247" t="n"/>
       <c r="H18" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I18" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/plants/v2/?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="I18" s="262" t="inlineStr">
+        <is>
+          <t>[{"Id":null,"Label":"1A4120200004532000001085","WasteMethodName":null,"WasteMaterialMixed":null,"WasteWeight":15.0,"WasteUnitOfMeasureName":"Grams","WasteReasonName":"Waste","Count":0,"ReasonNote":"Evaluation step — plant destruction.","ActualDate":"2026-08-27"}]</t>
         </is>
       </c>
     </row>
@@ -3323,14 +3349,14 @@
           <t xml:space="preserve">Destroy one of the plants using:                                                                      </t>
         </is>
       </c>
-      <c r="B19" s="255" t="n"/>
-      <c r="C19" s="256" t="n"/>
-      <c r="D19" s="256" t="n"/>
-      <c r="E19" s="256" t="n"/>
-      <c r="F19" s="256" t="n"/>
-      <c r="G19" s="256" t="n"/>
-      <c r="H19" s="256" t="n"/>
-      <c r="I19" s="256" t="n"/>
+      <c r="B19" s="256" t="n"/>
+      <c r="C19" s="257" t="n"/>
+      <c r="D19" s="257" t="n"/>
+      <c r="E19" s="257" t="n"/>
+      <c r="F19" s="257" t="n"/>
+      <c r="G19" s="257" t="n"/>
+      <c r="H19" s="257" t="n"/>
+      <c r="I19" s="257" t="n"/>
     </row>
     <row r="20" ht="18.95" customHeight="1" thickBot="1">
       <c r="A20" s="121" t="inlineStr">
@@ -3338,14 +3364,14 @@
           <t xml:space="preserve"> DELETE /plants/v2/</t>
         </is>
       </c>
-      <c r="B20" s="257" t="n"/>
-      <c r="C20" s="258" t="n"/>
-      <c r="D20" s="258" t="n"/>
-      <c r="E20" s="258" t="n"/>
-      <c r="F20" s="258" t="n"/>
-      <c r="G20" s="258" t="n"/>
-      <c r="H20" s="258" t="n"/>
-      <c r="I20" s="258" t="n"/>
+      <c r="B20" s="258" t="n"/>
+      <c r="C20" s="259" t="n"/>
+      <c r="D20" s="259" t="n"/>
+      <c r="E20" s="259" t="n"/>
+      <c r="F20" s="259" t="n"/>
+      <c r="G20" s="259" t="n"/>
+      <c r="H20" s="259" t="n"/>
+      <c r="I20" s="259" t="n"/>
     </row>
     <row r="21" ht="23.25" customHeight="1" thickBot="1">
       <c r="B21" s="2" t="n"/>
@@ -3365,38 +3391,38 @@
       </c>
       <c r="B22" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C22" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D22" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>28811</t>
         </is>
       </c>
       <c r="E22" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:11Z</t>
         </is>
       </c>
       <c r="F22" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120200004532000001112</t>
         </is>
       </c>
       <c r="G22" s="247" t="n"/>
       <c r="H22" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I22" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/plants/v2/manicure?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="I22" s="262" t="inlineStr">
+        <is>
+          <t>[{"Plant":"1A4120200004532000001112","Weight":25.0,"UnitOfWeight":"Grams","DryingLocation":"Terpenomics Loc 0827-1402 (Updated)","DryingSublocation":null,"HarvestName":null,"PatientLicenseNumber":null,"ActualDate":"2026-08-27","PlantCount":1}]</t>
         </is>
       </c>
     </row>
@@ -3406,14 +3432,14 @@
           <t xml:space="preserve">Manicure a portion of a Plant using:                                                                          </t>
         </is>
       </c>
-      <c r="B23" s="255" t="n"/>
-      <c r="C23" s="256" t="n"/>
-      <c r="D23" s="256" t="n"/>
-      <c r="E23" s="256" t="n"/>
-      <c r="F23" s="256" t="n"/>
-      <c r="G23" s="256" t="n"/>
-      <c r="H23" s="256" t="n"/>
-      <c r="I23" s="256" t="n"/>
+      <c r="B23" s="256" t="n"/>
+      <c r="C23" s="257" t="n"/>
+      <c r="D23" s="257" t="n"/>
+      <c r="E23" s="257" t="n"/>
+      <c r="F23" s="257" t="n"/>
+      <c r="G23" s="257" t="n"/>
+      <c r="H23" s="257" t="n"/>
+      <c r="I23" s="257" t="n"/>
     </row>
     <row r="24" ht="18.95" customHeight="1" thickBot="1">
       <c r="A24" s="121" t="inlineStr">
@@ -3421,14 +3447,14 @@
           <t>POST/plants/v2/manicure</t>
         </is>
       </c>
-      <c r="B24" s="257" t="n"/>
-      <c r="C24" s="258" t="n"/>
-      <c r="D24" s="258" t="n"/>
-      <c r="E24" s="258" t="n"/>
-      <c r="F24" s="258" t="n"/>
-      <c r="G24" s="258" t="n"/>
-      <c r="H24" s="258" t="n"/>
-      <c r="I24" s="258" t="n"/>
+      <c r="B24" s="258" t="n"/>
+      <c r="C24" s="259" t="n"/>
+      <c r="D24" s="259" t="n"/>
+      <c r="E24" s="259" t="n"/>
+      <c r="F24" s="259" t="n"/>
+      <c r="G24" s="259" t="n"/>
+      <c r="H24" s="259" t="n"/>
+      <c r="I24" s="259" t="n"/>
     </row>
     <row r="25" ht="23.25" customHeight="1" thickBot="1">
       <c r="B25" s="25" t="n"/>
@@ -3448,38 +3474,42 @@
       </c>
       <c r="B26" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C26" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D26" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>28708, 28708</t>
         </is>
       </c>
       <c r="E26" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:11Z</t>
         </is>
       </c>
       <c r="F26" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G26" s="247" t="n"/>
+          <t>1A4120200004532000001112, 1A4120200004532000001113</t>
+        </is>
+      </c>
+      <c r="G26" s="247" t="inlineStr">
+        <is>
+          <t>TP Harvest 0827-1402</t>
+        </is>
+      </c>
       <c r="H26" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I26" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/plants/v2/harvest?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="I26" s="262" t="inlineStr">
+        <is>
+          <t>[{"Plant":"1A4120200004532000001112","Weight":100.0,"UnitOfWeight":"Grams","DryingLocation":"Terpenomics Loc 0827-1402 (Updated)","DryingSublocation":null,"HarvestName":"TP Harvest 0827-1402","PatientLicenseNumber":null,"ActualDate":"2026-08-27"},{"Plant":"1A4120200004532000001113","Weight":100.0,"UnitOfWeight":"Grams","DryingLocation":"Terpenomics Loc 0827-1402 (Updated)","DryingSublocation":null,"HarvestName":"TP Harvest 0827-1402","PatientLicenseNumber":null,"ActualDate":"2026-08-27"}]</t>
         </is>
       </c>
     </row>
@@ -3489,14 +3519,14 @@
           <t xml:space="preserve">Using the 2 remaining Plants create a Harvest: (This can be done per plant or all at once, to join a harvest you must use the exact harvest name and it must be the same calender day.)                                               </t>
         </is>
       </c>
-      <c r="B27" s="255" t="n"/>
-      <c r="C27" s="256" t="n"/>
-      <c r="D27" s="256" t="n"/>
-      <c r="E27" s="256" t="n"/>
-      <c r="F27" s="256" t="n"/>
-      <c r="G27" s="256" t="n"/>
-      <c r="H27" s="256" t="n"/>
-      <c r="I27" s="256" t="n"/>
+      <c r="B27" s="256" t="n"/>
+      <c r="C27" s="257" t="n"/>
+      <c r="D27" s="257" t="n"/>
+      <c r="E27" s="257" t="n"/>
+      <c r="F27" s="257" t="n"/>
+      <c r="G27" s="257" t="n"/>
+      <c r="H27" s="257" t="n"/>
+      <c r="I27" s="257" t="n"/>
     </row>
     <row r="28" ht="20.25" customHeight="1" thickBot="1">
       <c r="A28" s="121" t="inlineStr">
@@ -3504,14 +3534,14 @@
           <t>PUT /plants/v2/harvest</t>
         </is>
       </c>
-      <c r="B28" s="257" t="n"/>
-      <c r="C28" s="258" t="n"/>
-      <c r="D28" s="258" t="n"/>
-      <c r="E28" s="258" t="n"/>
-      <c r="F28" s="258" t="n"/>
-      <c r="G28" s="258" t="n"/>
-      <c r="H28" s="258" t="n"/>
-      <c r="I28" s="258" t="n"/>
+      <c r="B28" s="258" t="n"/>
+      <c r="C28" s="259" t="n"/>
+      <c r="D28" s="259" t="n"/>
+      <c r="E28" s="259" t="n"/>
+      <c r="F28" s="259" t="n"/>
+      <c r="G28" s="259" t="n"/>
+      <c r="H28" s="259" t="n"/>
+      <c r="I28" s="259" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -3911,38 +3941,42 @@
       </c>
       <c r="B5" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C5" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>218907</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:11Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G5" s="104" t="n"/>
+          <t>1A4120300004532000001447</t>
+        </is>
+      </c>
+      <c r="G5" s="104" t="inlineStr">
+        <is>
+          <t>TP Harvest 0827-1402</t>
+        </is>
+      </c>
       <c r="H5" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I5" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/harvests/v2/packages?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="I5" s="262" t="inlineStr">
+        <is>
+          <t>[{"Tag":"1A4120300004532000001447","Location":"Terpenomics Loc 0827-1402 (Updated)","Sublocation":null,"Item":"Terpenomics Item 0827-1402","UnitOfWeight":"Grams","PatientLicenseNumber":null,"Note":"Evaluation step","IsProductionBatch":false,"ProductionBatchNumber":null,"IsTradeSample":false,"IsDonation":false,"ProductRequiresRemediation":false,"RemediateProduct":false,"ActualDate":"2026-08-27","Ingredients":[{"HarvestId":28811,"HarvestName":null,"Weight":50.0,"UnitOfWeight":"Grams"}]}]</t>
         </is>
       </c>
     </row>
@@ -3952,14 +3986,14 @@
           <t xml:space="preserve">Using the Harvest Created in Step 6 from Plants, create a package using: </t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
       <c r="G6" s="109" t="n"/>
-      <c r="H6" s="256" t="n"/>
-      <c r="I6" s="256" t="n"/>
+      <c r="H6" s="257" t="n"/>
+      <c r="I6" s="257" t="n"/>
     </row>
     <row r="7" ht="16.15" customHeight="1" thickBot="1">
       <c r="A7" s="121" t="inlineStr">
@@ -3967,14 +4001,14 @@
           <t>POST /harvests/v2/packages</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
       <c r="G7" s="114" t="n"/>
-      <c r="H7" s="258" t="n"/>
-      <c r="I7" s="258" t="n"/>
+      <c r="H7" s="259" t="n"/>
+      <c r="I7" s="259" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" thickBot="1">
       <c r="A8" s="33" t="n"/>
@@ -3995,22 +4029,22 @@
       </c>
       <c r="B9" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C9" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>28811</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:12Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
@@ -4018,15 +4052,19 @@
           <t> </t>
         </is>
       </c>
-      <c r="G9" s="104" t="n"/>
+      <c r="G9" s="104" t="inlineStr">
+        <is>
+          <t>TP Harvest 0827-1402</t>
+        </is>
+      </c>
       <c r="H9" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I9" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/harvests/v2/waste?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="I9" s="262" t="inlineStr">
+        <is>
+          <t>[{"Id":28811,"WasteType":"Plant Material","UnitOfWeight":"Grams","WasteWeight":25.0,"ActualDate":"2026-08-27"}]</t>
         </is>
       </c>
     </row>
@@ -4036,14 +4074,14 @@
           <t xml:space="preserve">Using the Harvest Created in Step 6 from Plants, Remove the remaining weight as Waste.  (MOISTURE LOSS IS NOT REMOVED AS WASTE): </t>
         </is>
       </c>
-      <c r="B10" s="255" t="n"/>
-      <c r="C10" s="256" t="n"/>
-      <c r="D10" s="256" t="n"/>
-      <c r="E10" s="256" t="n"/>
-      <c r="F10" s="256" t="n"/>
+      <c r="B10" s="256" t="n"/>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+      <c r="F10" s="257" t="n"/>
       <c r="G10" s="109" t="n"/>
-      <c r="H10" s="256" t="n"/>
-      <c r="I10" s="256" t="n"/>
+      <c r="H10" s="257" t="n"/>
+      <c r="I10" s="257" t="n"/>
     </row>
     <row r="11" ht="16.15" customHeight="1" thickBot="1">
       <c r="A11" s="121" t="inlineStr">
@@ -4051,14 +4089,14 @@
           <t>POST /harvests/v2/waste</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
-      <c r="C11" s="258" t="n"/>
-      <c r="D11" s="258" t="n"/>
-      <c r="E11" s="258" t="n"/>
-      <c r="F11" s="258" t="n"/>
+      <c r="B11" s="258" t="n"/>
+      <c r="C11" s="259" t="n"/>
+      <c r="D11" s="259" t="n"/>
+      <c r="E11" s="259" t="n"/>
+      <c r="F11" s="259" t="n"/>
       <c r="G11" s="114" t="n"/>
-      <c r="H11" s="258" t="n"/>
-      <c r="I11" s="258" t="n"/>
+      <c r="H11" s="259" t="n"/>
+      <c r="I11" s="259" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" thickBot="1">
       <c r="A12" s="33" t="n"/>
@@ -4071,22 +4109,22 @@
       </c>
       <c r="B13" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C13" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>28811</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:12Z</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
@@ -4094,15 +4132,19 @@
           <t> </t>
         </is>
       </c>
-      <c r="G13" s="104" t="n"/>
+      <c r="G13" s="104" t="inlineStr">
+        <is>
+          <t>TP Harvest 0827-1402</t>
+        </is>
+      </c>
       <c r="H13" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I13" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/harvests/v2/finish?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="I13" s="262" t="inlineStr">
+        <is>
+          <t>[{"Id":28811,"ActualDate":"2026-08-27"}]</t>
         </is>
       </c>
     </row>
@@ -4112,14 +4154,14 @@
           <t xml:space="preserve"> Using the Harvest in step 2 -  Finish that Harvest using:</t>
         </is>
       </c>
-      <c r="B14" s="255" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="256" t="n"/>
+      <c r="B14" s="256" t="n"/>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+      <c r="F14" s="257" t="n"/>
       <c r="G14" s="109" t="n"/>
-      <c r="H14" s="256" t="n"/>
-      <c r="I14" s="256" t="n"/>
+      <c r="H14" s="257" t="n"/>
+      <c r="I14" s="257" t="n"/>
     </row>
     <row r="15" ht="16.15" customHeight="1" thickBot="1">
       <c r="A15" s="121" t="inlineStr">
@@ -4127,14 +4169,14 @@
           <t>PUT /harvests/v2/finish</t>
         </is>
       </c>
-      <c r="B15" s="257" t="n"/>
-      <c r="C15" s="258" t="n"/>
-      <c r="D15" s="258" t="n"/>
-      <c r="E15" s="258" t="n"/>
-      <c r="F15" s="258" t="n"/>
+      <c r="B15" s="258" t="n"/>
+      <c r="C15" s="259" t="n"/>
+      <c r="D15" s="259" t="n"/>
+      <c r="E15" s="259" t="n"/>
+      <c r="F15" s="259" t="n"/>
       <c r="G15" s="114" t="n"/>
-      <c r="H15" s="258" t="n"/>
-      <c r="I15" s="258" t="n"/>
+      <c r="H15" s="259" t="n"/>
+      <c r="I15" s="259" t="n"/>
     </row>
     <row r="16" ht="21.6" customHeight="1" thickBot="1">
       <c r="A16" s="135" t="n"/>
@@ -4155,22 +4197,22 @@
       </c>
       <c r="B17" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C17" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D17" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>28811</t>
         </is>
       </c>
       <c r="E17" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:12Z</t>
         </is>
       </c>
       <c r="F17" s="247" t="inlineStr">
@@ -4178,15 +4220,19 @@
           <t> </t>
         </is>
       </c>
-      <c r="G17" s="104" t="n"/>
+      <c r="G17" s="104" t="inlineStr">
+        <is>
+          <t>TP Harvest 0827-1402</t>
+        </is>
+      </c>
       <c r="H17" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I17" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/harvests/v2/unfinish?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="I17" s="262" t="inlineStr">
+        <is>
+          <t>[{"Id":28811}]</t>
         </is>
       </c>
     </row>
@@ -4196,14 +4242,14 @@
           <t xml:space="preserve">Using the Harvest finished in Step 3 - Unfinish that Harvest using:    </t>
         </is>
       </c>
-      <c r="B18" s="256" t="n"/>
-      <c r="C18" s="256" t="n"/>
-      <c r="D18" s="256" t="n"/>
-      <c r="E18" s="256" t="n"/>
-      <c r="F18" s="256" t="n"/>
+      <c r="B18" s="257" t="n"/>
+      <c r="C18" s="257" t="n"/>
+      <c r="D18" s="257" t="n"/>
+      <c r="E18" s="257" t="n"/>
+      <c r="F18" s="257" t="n"/>
       <c r="G18" s="109" t="n"/>
-      <c r="H18" s="256" t="n"/>
-      <c r="I18" s="256" t="n"/>
+      <c r="H18" s="257" t="n"/>
+      <c r="I18" s="257" t="n"/>
     </row>
     <row r="19" ht="16.15" customHeight="1" thickBot="1">
       <c r="A19" s="150" t="inlineStr">
@@ -4211,14 +4257,14 @@
           <t>PUT /harvests/v2/unfinish</t>
         </is>
       </c>
-      <c r="B19" s="258" t="n"/>
-      <c r="C19" s="258" t="n"/>
-      <c r="D19" s="258" t="n"/>
-      <c r="E19" s="258" t="n"/>
-      <c r="F19" s="258" t="n"/>
+      <c r="B19" s="259" t="n"/>
+      <c r="C19" s="259" t="n"/>
+      <c r="D19" s="259" t="n"/>
+      <c r="E19" s="259" t="n"/>
+      <c r="F19" s="259" t="n"/>
       <c r="G19" s="114" t="n"/>
-      <c r="H19" s="258" t="n"/>
-      <c r="I19" s="258" t="n"/>
+      <c r="H19" s="259" t="n"/>
+      <c r="I19" s="259" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="135" t="n"/>
@@ -4543,37 +4589,37 @@
       </c>
       <c r="B5" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C5" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>217774</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:12Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120300004532000001448</t>
         </is>
       </c>
       <c r="G5" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H5" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/packages/v2/?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H5" s="262" t="inlineStr">
+        <is>
+          <t>[{"Tag":"1A4120300004532000001448","Location":"Terpenomics Loc 0827-1402 (Updated)","Sublocation":null,"Item":"Terpenomics Item 0827-1402","Quantity":10.0,"UnitOfMeasure":"Grams","PatientLicenseNumber":null,"Note":"Evaluation step","IsProductionBatch":false,"ProductionBatchNumber":null,"IsDonation":false,"IsTradeSample":false,"ProductRequiresRemediation":false,"UseSameItem":true,"ActualDate":"2026-08-27","Ingredients":[{"Package":"1A4120300004532000001447","Quantity":10.0,"UnitOfMeasure":"Grams"}]}]</t>
         </is>
       </c>
     </row>
@@ -4583,13 +4629,13 @@
           <t>Using the Package created in Harvest Step 1 OR create a package from an existing package that you have found.  Create a package from another package using:</t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
-      <c r="G6" s="256" t="n"/>
-      <c r="H6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
+      <c r="G6" s="257" t="n"/>
+      <c r="H6" s="257" t="n"/>
     </row>
     <row r="7" ht="16.15" customHeight="1" thickBot="1">
       <c r="A7" s="121" t="inlineStr">
@@ -4597,13 +4643,13 @@
           <t>POST/packages/v2/</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
-      <c r="G7" s="258" t="n"/>
-      <c r="H7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
+      <c r="G7" s="259" t="n"/>
+      <c r="H7" s="259" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" thickBot="1">
       <c r="A8" s="1" t="n"/>
@@ -4623,12 +4669,12 @@
       </c>
       <c r="B9" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C9" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D9" s="248" t="inlineStr">
@@ -4638,22 +4684,22 @@
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:12Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120300004532000001448</t>
         </is>
       </c>
       <c r="G9" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H9" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/packages/v2/item?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H9" s="262" t="inlineStr">
+        <is>
+          <t>[{"Label":"1A4120300004532000001448","Item":"Terpenomics Alt Item 0827-1402"}]</t>
         </is>
       </c>
     </row>
@@ -4663,13 +4709,13 @@
           <t xml:space="preserve"> Using the new package created in Step 1 Change the item of a package using:                               </t>
         </is>
       </c>
-      <c r="B10" s="255" t="n"/>
-      <c r="C10" s="256" t="n"/>
-      <c r="D10" s="256" t="n"/>
-      <c r="E10" s="256" t="n"/>
-      <c r="F10" s="256" t="n"/>
-      <c r="G10" s="256" t="n"/>
-      <c r="H10" s="256" t="n"/>
+      <c r="B10" s="256" t="n"/>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+      <c r="F10" s="257" t="n"/>
+      <c r="G10" s="257" t="n"/>
+      <c r="H10" s="257" t="n"/>
     </row>
     <row r="11" ht="16.15" customHeight="1" thickBot="1">
       <c r="A11" s="121" t="inlineStr">
@@ -4677,13 +4723,13 @@
           <t>PUT/packages/v2/item</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
-      <c r="C11" s="258" t="n"/>
-      <c r="D11" s="258" t="n"/>
-      <c r="E11" s="258" t="n"/>
-      <c r="F11" s="258" t="n"/>
-      <c r="G11" s="258" t="n"/>
-      <c r="H11" s="258" t="n"/>
+      <c r="B11" s="258" t="n"/>
+      <c r="C11" s="259" t="n"/>
+      <c r="D11" s="259" t="n"/>
+      <c r="E11" s="259" t="n"/>
+      <c r="F11" s="259" t="n"/>
+      <c r="G11" s="259" t="n"/>
+      <c r="H11" s="259" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" thickBot="1">
       <c r="A12" s="1" t="n"/>
@@ -4696,12 +4742,12 @@
       </c>
       <c r="B13" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C13" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D13" s="248" t="inlineStr">
@@ -4711,22 +4757,22 @@
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:13Z</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120300004532000001448</t>
         </is>
       </c>
       <c r="G13" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H13" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/packages/v2/adjust?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H13" s="262" t="inlineStr">
+        <is>
+          <t>[{"Label":"1A4120300004532000001448","Quantity":0,"UnitOfMeasure":"Grams","AdjustmentReason":"Drying","AdjustmentDate":"2026-08-27","ReasonNote":"Evaluation step — adjusting to zero."}]</t>
         </is>
       </c>
     </row>
@@ -4736,13 +4782,13 @@
           <t xml:space="preserve">Using the Package from Step 2 Adjust The weight or quantity  to 0 using: ** Note if you are going to POST sales using this package, wait to finish the package until you post sales.     </t>
         </is>
       </c>
-      <c r="B14" s="255" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="256" t="n"/>
-      <c r="G14" s="256" t="n"/>
-      <c r="H14" s="256" t="n"/>
+      <c r="B14" s="256" t="n"/>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+      <c r="F14" s="257" t="n"/>
+      <c r="G14" s="257" t="n"/>
+      <c r="H14" s="257" t="n"/>
     </row>
     <row r="15" ht="16.15" customHeight="1" thickBot="1">
       <c r="A15" s="121" t="inlineStr">
@@ -4750,13 +4796,13 @@
           <t>PUT/packages/v2/adjust</t>
         </is>
       </c>
-      <c r="B15" s="257" t="n"/>
-      <c r="C15" s="258" t="n"/>
-      <c r="D15" s="258" t="n"/>
-      <c r="E15" s="258" t="n"/>
-      <c r="F15" s="258" t="n"/>
-      <c r="G15" s="258" t="n"/>
-      <c r="H15" s="258" t="n"/>
+      <c r="B15" s="258" t="n"/>
+      <c r="C15" s="259" t="n"/>
+      <c r="D15" s="259" t="n"/>
+      <c r="E15" s="259" t="n"/>
+      <c r="F15" s="259" t="n"/>
+      <c r="G15" s="259" t="n"/>
+      <c r="H15" s="259" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="135" t="n"/>
@@ -4776,12 +4822,12 @@
       </c>
       <c r="B17" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C17" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D17" s="248" t="inlineStr">
@@ -4791,22 +4837,22 @@
       </c>
       <c r="E17" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:13Z</t>
         </is>
       </c>
       <c r="F17" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120300004532000001448</t>
         </is>
       </c>
       <c r="G17" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H17" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/packages/v2/finish?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H17" s="262" t="inlineStr">
+        <is>
+          <t>[{"Label":"1A4120300004532000001448","ActualDate":"2026-08-27"}]</t>
         </is>
       </c>
     </row>
@@ -4816,13 +4862,13 @@
           <t xml:space="preserve"> Using the Package from Step 3, Finish that package using: </t>
         </is>
       </c>
-      <c r="B18" s="255" t="n"/>
-      <c r="C18" s="256" t="n"/>
-      <c r="D18" s="256" t="n"/>
-      <c r="E18" s="256" t="n"/>
-      <c r="F18" s="256" t="n"/>
-      <c r="G18" s="256" t="n"/>
-      <c r="H18" s="256" t="n"/>
+      <c r="B18" s="256" t="n"/>
+      <c r="C18" s="257" t="n"/>
+      <c r="D18" s="257" t="n"/>
+      <c r="E18" s="257" t="n"/>
+      <c r="F18" s="257" t="n"/>
+      <c r="G18" s="257" t="n"/>
+      <c r="H18" s="257" t="n"/>
     </row>
     <row r="19" ht="16.15" customHeight="1" thickBot="1">
       <c r="A19" s="121" t="inlineStr">
@@ -4830,13 +4876,13 @@
           <t>PUT/packages/v2/finish</t>
         </is>
       </c>
-      <c r="B19" s="257" t="n"/>
-      <c r="C19" s="258" t="n"/>
-      <c r="D19" s="258" t="n"/>
-      <c r="E19" s="258" t="n"/>
-      <c r="F19" s="258" t="n"/>
-      <c r="G19" s="258" t="n"/>
-      <c r="H19" s="258" t="n"/>
+      <c r="B19" s="258" t="n"/>
+      <c r="C19" s="259" t="n"/>
+      <c r="D19" s="259" t="n"/>
+      <c r="E19" s="259" t="n"/>
+      <c r="F19" s="259" t="n"/>
+      <c r="G19" s="259" t="n"/>
+      <c r="H19" s="259" t="n"/>
     </row>
     <row r="20" ht="13.15" customHeight="1" thickBot="1">
       <c r="A20" s="124" t="n"/>
@@ -4856,12 +4902,12 @@
       </c>
       <c r="B21" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C21" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D21" s="248" t="inlineStr">
@@ -4871,22 +4917,22 @@
       </c>
       <c r="E21" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:13Z</t>
         </is>
       </c>
       <c r="F21" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120300004532000001448</t>
         </is>
       </c>
       <c r="G21" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H21" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/packages/v2/unfinish?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H21" s="262" t="inlineStr">
+        <is>
+          <t>[{"Label":"1A4120300004532000001448"}]</t>
         </is>
       </c>
     </row>
@@ -4896,13 +4942,13 @@
           <t>Using the new package created in Packages Step 1                             Unfinish a package using:</t>
         </is>
       </c>
-      <c r="B22" s="255" t="n"/>
-      <c r="C22" s="256" t="n"/>
-      <c r="D22" s="256" t="n"/>
-      <c r="E22" s="256" t="n"/>
-      <c r="F22" s="256" t="n"/>
-      <c r="G22" s="256" t="n"/>
-      <c r="H22" s="256" t="n"/>
+      <c r="B22" s="256" t="n"/>
+      <c r="C22" s="257" t="n"/>
+      <c r="D22" s="257" t="n"/>
+      <c r="E22" s="257" t="n"/>
+      <c r="F22" s="257" t="n"/>
+      <c r="G22" s="257" t="n"/>
+      <c r="H22" s="257" t="n"/>
     </row>
     <row r="23" ht="16.15" customHeight="1" thickBot="1">
       <c r="A23" s="121" t="inlineStr">
@@ -4910,13 +4956,13 @@
           <t>PUT/packages/v2/unfinish</t>
         </is>
       </c>
-      <c r="B23" s="257" t="n"/>
-      <c r="C23" s="258" t="n"/>
-      <c r="D23" s="258" t="n"/>
-      <c r="E23" s="258" t="n"/>
-      <c r="F23" s="258" t="n"/>
-      <c r="G23" s="258" t="n"/>
-      <c r="H23" s="258" t="n"/>
+      <c r="B23" s="258" t="n"/>
+      <c r="C23" s="259" t="n"/>
+      <c r="D23" s="259" t="n"/>
+      <c r="E23" s="259" t="n"/>
+      <c r="F23" s="259" t="n"/>
+      <c r="G23" s="259" t="n"/>
+      <c r="H23" s="259" t="n"/>
     </row>
     <row r="24" ht="25.9" customHeight="1">
       <c r="A24" s="136" t="n"/>
@@ -5281,13 +5327,13 @@
           <t xml:space="preserve">Record a lab test result using: </t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
-      <c r="G6" s="256" t="n"/>
-      <c r="H6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
+      <c r="G6" s="257" t="n"/>
+      <c r="H6" s="257" t="n"/>
     </row>
     <row r="7" ht="25.9" customHeight="1" thickBot="1">
       <c r="A7" s="121" t="inlineStr">
@@ -5295,13 +5341,13 @@
           <t>POST/labtests/v2/record</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
-      <c r="G7" s="258" t="n"/>
-      <c r="H7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
+      <c r="G7" s="259" t="n"/>
+      <c r="H7" s="259" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -7447,7 +7493,7 @@
           <t>https://sandbox-api-ny.metrc.com/labtests/v2/results?packageId=218855&amp;licenseNumber=SF-SBX-NY-17-30301</t>
         </is>
       </c>
-      <c r="H5" s="260" t="inlineStr">
+      <c r="H5" s="262" t="inlineStr">
         <is>
           <t>{"Data":[],"Total":0,"TotalRecords":0,"PageSize":0,"RecordsOnPage":0,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
         </is>
@@ -7459,13 +7505,13 @@
           <t xml:space="preserve">Record a lab test result using: </t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
-      <c r="G6" s="256" t="n"/>
-      <c r="H6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
+      <c r="G6" s="257" t="n"/>
+      <c r="H6" s="257" t="n"/>
     </row>
     <row r="7" ht="16.15" customHeight="1" thickBot="1">
       <c r="A7" s="121" t="inlineStr">
@@ -7473,13 +7519,13 @@
           <t>POST/labtests/v2/record</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
-      <c r="G7" s="258" t="n"/>
-      <c r="H7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
+      <c r="G7" s="259" t="n"/>
+      <c r="H7" s="259" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -7713,13 +7759,13 @@
           <t xml:space="preserve"> Create a sales receipt using:</t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
-      <c r="G6" s="256" t="n"/>
-      <c r="H6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
+      <c r="G6" s="257" t="n"/>
+      <c r="H6" s="257" t="n"/>
     </row>
     <row r="7" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A7" s="121" t="inlineStr">
@@ -7727,13 +7773,13 @@
           <t>POST/sales/v2/receipts</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
-      <c r="G7" s="258" t="n"/>
-      <c r="H7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
+      <c r="G7" s="259" t="n"/>
+      <c r="H7" s="259" t="n"/>
     </row>
     <row r="8" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A8" s="133" t="n"/>
@@ -7793,13 +7839,13 @@
           <t xml:space="preserve"> Update the sales receipt created in Step 1 using: </t>
         </is>
       </c>
-      <c r="B10" s="255" t="n"/>
-      <c r="C10" s="256" t="n"/>
-      <c r="D10" s="256" t="n"/>
-      <c r="E10" s="256" t="n"/>
-      <c r="F10" s="256" t="n"/>
-      <c r="G10" s="256" t="n"/>
-      <c r="H10" s="256" t="n"/>
+      <c r="B10" s="256" t="n"/>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+      <c r="F10" s="257" t="n"/>
+      <c r="G10" s="257" t="n"/>
+      <c r="H10" s="257" t="n"/>
     </row>
     <row r="11" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A11" s="121" t="inlineStr">
@@ -7807,13 +7853,13 @@
           <t>PUT/sales/v2/receipts</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
-      <c r="C11" s="258" t="n"/>
-      <c r="D11" s="258" t="n"/>
-      <c r="E11" s="258" t="n"/>
-      <c r="F11" s="258" t="n"/>
-      <c r="G11" s="258" t="n"/>
-      <c r="H11" s="258" t="n"/>
+      <c r="B11" s="258" t="n"/>
+      <c r="C11" s="259" t="n"/>
+      <c r="D11" s="259" t="n"/>
+      <c r="E11" s="259" t="n"/>
+      <c r="F11" s="259" t="n"/>
+      <c r="G11" s="259" t="n"/>
+      <c r="H11" s="259" t="n"/>
     </row>
     <row r="12" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A12" s="133" t="n"/>
@@ -7866,13 +7912,13 @@
           <t xml:space="preserve"> Void the sales receipt created in Step 1 using:</t>
         </is>
       </c>
-      <c r="B14" s="255" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="256" t="n"/>
-      <c r="G14" s="256" t="n"/>
-      <c r="H14" s="256" t="n"/>
+      <c r="B14" s="256" t="n"/>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+      <c r="F14" s="257" t="n"/>
+      <c r="G14" s="257" t="n"/>
+      <c r="H14" s="257" t="n"/>
     </row>
     <row r="15" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A15" s="121" t="inlineStr">
@@ -7880,13 +7926,13 @@
           <t>DELETE/sales/v2/receipts/{id}</t>
         </is>
       </c>
-      <c r="B15" s="257" t="n"/>
-      <c r="C15" s="258" t="n"/>
-      <c r="D15" s="258" t="n"/>
-      <c r="E15" s="258" t="n"/>
-      <c r="F15" s="258" t="n"/>
-      <c r="G15" s="258" t="n"/>
-      <c r="H15" s="258" t="n"/>
+      <c r="B15" s="258" t="n"/>
+      <c r="C15" s="259" t="n"/>
+      <c r="D15" s="259" t="n"/>
+      <c r="E15" s="259" t="n"/>
+      <c r="F15" s="259" t="n"/>
+      <c r="G15" s="259" t="n"/>
+      <c r="H15" s="259" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="134" t="n"/>
@@ -8140,37 +8186,37 @@
       </c>
       <c r="B5" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C5" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-5-30301</t>
         </is>
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>682</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:15Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120300004533000000001</t>
         </is>
       </c>
       <c r="G5" s="248" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H5" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/sales/v2/receipts?licenseNumber=SF-SBX-NY-5-30301</t>
+        </is>
+      </c>
+      <c r="H5" s="262" t="inlineStr">
+        <is>
+          <t>[{"SalesDateTime":"2026-08-27T14:02:14Z","ExternalReceiptNumber":"TP-0827-1402","SalesCustomerType":"Consumer","PatientLicenseNumber":null,"CaregiverLicenseNumber":null,"IdentificationMethod":null,"PatientRegistrationLocationId":null,"Transactions":[{"PackageLabel":"1A4120300004533000000001","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":9.99}]}]</t>
         </is>
       </c>
     </row>
@@ -8180,13 +8226,13 @@
           <t xml:space="preserve"> Create a sales receipt using:</t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
-      <c r="G6" s="256" t="n"/>
-      <c r="H6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
+      <c r="G6" s="257" t="n"/>
+      <c r="H6" s="257" t="n"/>
     </row>
     <row r="7" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A7" s="121" t="inlineStr">
@@ -8194,13 +8240,13 @@
           <t>POST/sales/v2/receipts</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
-      <c r="G7" s="258" t="n"/>
-      <c r="H7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
+      <c r="G7" s="259" t="n"/>
+      <c r="H7" s="259" t="n"/>
     </row>
     <row r="8" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A8" s="133" t="n"/>
@@ -8219,37 +8265,37 @@
       </c>
       <c r="B9" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C9" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-5-30301</t>
         </is>
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>682</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:15Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120300004533000000001</t>
         </is>
       </c>
       <c r="G9" s="248" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H9" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/sales/v2/receipts?licenseNumber=SF-SBX-NY-5-30301</t>
+        </is>
+      </c>
+      <c r="H9" s="262" t="inlineStr">
+        <is>
+          <t>[{"SalesDateTime":"2026-08-27T14:02:15Z","ExternalReceiptNumber":"TP-0827-1402","SalesCustomerType":"Consumer","PatientLicenseNumber":null,"CaregiverLicenseNumber":null,"IdentificationMethod":null,"PatientRegistrationLocationId":null,"Transactions":[{"PackageLabel":"1A4120300004533000000001","Quantity":2.0,"UnitOfMeasure":"Each","TotalAmount":19.98}],"Id":682}]</t>
         </is>
       </c>
     </row>
@@ -8259,13 +8305,13 @@
           <t xml:space="preserve"> Update the sales receipt created in Step 1 using: </t>
         </is>
       </c>
-      <c r="B10" s="255" t="n"/>
-      <c r="C10" s="256" t="n"/>
-      <c r="D10" s="256" t="n"/>
-      <c r="E10" s="256" t="n"/>
-      <c r="F10" s="256" t="n"/>
-      <c r="G10" s="256" t="n"/>
-      <c r="H10" s="256" t="n"/>
+      <c r="B10" s="256" t="n"/>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+      <c r="F10" s="257" t="n"/>
+      <c r="G10" s="257" t="n"/>
+      <c r="H10" s="257" t="n"/>
     </row>
     <row r="11" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A11" s="121" t="inlineStr">
@@ -8273,13 +8319,13 @@
           <t>PUT/sales/v2/receipts</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
-      <c r="C11" s="258" t="n"/>
-      <c r="D11" s="258" t="n"/>
-      <c r="E11" s="258" t="n"/>
-      <c r="F11" s="258" t="n"/>
-      <c r="G11" s="258" t="n"/>
-      <c r="H11" s="258" t="n"/>
+      <c r="B11" s="258" t="n"/>
+      <c r="C11" s="259" t="n"/>
+      <c r="D11" s="259" t="n"/>
+      <c r="E11" s="259" t="n"/>
+      <c r="F11" s="259" t="n"/>
+      <c r="G11" s="259" t="n"/>
+      <c r="H11" s="259" t="n"/>
     </row>
     <row r="12" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A12" s="133" t="n"/>
@@ -8292,32 +8338,32 @@
       </c>
       <c r="B13" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C13" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-5-30301</t>
         </is>
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>682</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:15Z</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120300004533000000001</t>
         </is>
       </c>
       <c r="G13" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/sales/v2/receipts/682?licenseNumber=SF-SBX-NY-5-30301</t>
         </is>
       </c>
       <c r="H13" s="248" t="inlineStr">
@@ -8332,13 +8378,13 @@
           <t xml:space="preserve"> Void the sales receipt created in Step 1 using:</t>
         </is>
       </c>
-      <c r="B14" s="255" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="256" t="n"/>
-      <c r="G14" s="256" t="n"/>
-      <c r="H14" s="256" t="n"/>
+      <c r="B14" s="256" t="n"/>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+      <c r="F14" s="257" t="n"/>
+      <c r="G14" s="257" t="n"/>
+      <c r="H14" s="257" t="n"/>
     </row>
     <row r="15" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A15" s="121" t="inlineStr">
@@ -8346,13 +8392,13 @@
           <t>DELETE/sales/v2/receipts/{id}</t>
         </is>
       </c>
-      <c r="B15" s="257" t="n"/>
-      <c r="C15" s="258" t="n"/>
-      <c r="D15" s="258" t="n"/>
-      <c r="E15" s="258" t="n"/>
-      <c r="F15" s="258" t="n"/>
-      <c r="G15" s="258" t="n"/>
-      <c r="H15" s="258" t="n"/>
+      <c r="B15" s="258" t="n"/>
+      <c r="C15" s="259" t="n"/>
+      <c r="D15" s="259" t="n"/>
+      <c r="E15" s="259" t="n"/>
+      <c r="F15" s="259" t="n"/>
+      <c r="G15" s="259" t="n"/>
+      <c r="H15" s="259" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" thickBot="1">
       <c r="A16" s="1" t="n"/>
@@ -8372,12 +8418,12 @@
       </c>
       <c r="B17" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>401</t>
         </is>
       </c>
       <c r="C17" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-5-30301</t>
         </is>
       </c>
       <c r="D17" s="248" t="inlineStr">
@@ -8387,7 +8433,7 @@
       </c>
       <c r="E17" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:15Z</t>
         </is>
       </c>
       <c r="F17" s="247" t="inlineStr">
@@ -8397,7 +8443,7 @@
       </c>
       <c r="G17" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/patients/v2/statuses/PTN-123-456?licenseNumber=SF-SBX-NY-5-30301</t>
         </is>
       </c>
       <c r="H17" s="248" t="inlineStr">
@@ -8412,13 +8458,13 @@
           <t>Verify a patient’s “FlowerOuncesAvailable” using:</t>
         </is>
       </c>
-      <c r="B18" s="255" t="n"/>
-      <c r="C18" s="256" t="n"/>
-      <c r="D18" s="256" t="n"/>
-      <c r="E18" s="256" t="n"/>
-      <c r="F18" s="256" t="n"/>
-      <c r="G18" s="256" t="n"/>
-      <c r="H18" s="256" t="n"/>
+      <c r="B18" s="256" t="n"/>
+      <c r="C18" s="257" t="n"/>
+      <c r="D18" s="257" t="n"/>
+      <c r="E18" s="257" t="n"/>
+      <c r="F18" s="257" t="n"/>
+      <c r="G18" s="257" t="n"/>
+      <c r="H18" s="257" t="n"/>
     </row>
     <row r="19" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A19" s="121" t="inlineStr">
@@ -8426,13 +8472,13 @@
           <t>GET/patients/v2/statuses/{patientLicenseNumber}</t>
         </is>
       </c>
-      <c r="B19" s="257" t="n"/>
-      <c r="C19" s="258" t="n"/>
-      <c r="D19" s="258" t="n"/>
-      <c r="E19" s="258" t="n"/>
-      <c r="F19" s="258" t="n"/>
-      <c r="G19" s="258" t="n"/>
-      <c r="H19" s="258" t="n"/>
+      <c r="B19" s="258" t="n"/>
+      <c r="C19" s="259" t="n"/>
+      <c r="D19" s="259" t="n"/>
+      <c r="E19" s="259" t="n"/>
+      <c r="F19" s="259" t="n"/>
+      <c r="G19" s="259" t="n"/>
+      <c r="H19" s="259" t="n"/>
     </row>
     <row r="20" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A20" s="133" t="n"/>
@@ -8445,37 +8491,37 @@
       </c>
       <c r="B21" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C21" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-5-30301</t>
         </is>
       </c>
       <c r="D21" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>679</t>
         </is>
       </c>
       <c r="E21" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:15Z</t>
         </is>
       </c>
       <c r="F21" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120300004533000000001</t>
         </is>
       </c>
       <c r="G21" s="248" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H21" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/sales/v2/receipts?licenseNumber=SF-SBX-NY-5-30301</t>
+        </is>
+      </c>
+      <c r="H21" s="262" t="inlineStr">
+        <is>
+          <t>[{"SalesDateTime":"2026-08-27T14:02:15Z","ExternalReceiptNumber":"TP-0827-1402-EP","SalesCustomerType":"ExternalPatient","PatientLicenseNumber":"PTN-123-456","CaregiverLicenseNumber":null,"IdentificationMethod":null,"PatientRegistrationLocationId":null,"Transactions":[{"PackageLabel":"1A4120300004533000000001","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":9.99}]}]</t>
         </is>
       </c>
     </row>
@@ -8485,13 +8531,13 @@
           <t xml:space="preserve"> Create a sales receipt with a customer type being ExternalPatient using:</t>
         </is>
       </c>
-      <c r="B22" s="255" t="n"/>
-      <c r="C22" s="256" t="n"/>
-      <c r="D22" s="256" t="n"/>
-      <c r="E22" s="256" t="n"/>
-      <c r="F22" s="256" t="n"/>
-      <c r="G22" s="256" t="n"/>
-      <c r="H22" s="256" t="n"/>
+      <c r="B22" s="256" t="n"/>
+      <c r="C22" s="257" t="n"/>
+      <c r="D22" s="257" t="n"/>
+      <c r="E22" s="257" t="n"/>
+      <c r="F22" s="257" t="n"/>
+      <c r="G22" s="257" t="n"/>
+      <c r="H22" s="257" t="n"/>
     </row>
     <row r="23" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A23" s="186" t="inlineStr">
@@ -8499,13 +8545,13 @@
           <t>POST/sales/v2/receipts</t>
         </is>
       </c>
-      <c r="B23" s="257" t="n"/>
-      <c r="C23" s="258" t="n"/>
-      <c r="D23" s="258" t="n"/>
-      <c r="E23" s="258" t="n"/>
-      <c r="F23" s="258" t="n"/>
-      <c r="G23" s="258" t="n"/>
-      <c r="H23" s="258" t="n"/>
+      <c r="B23" s="258" t="n"/>
+      <c r="C23" s="259" t="n"/>
+      <c r="D23" s="259" t="n"/>
+      <c r="E23" s="259" t="n"/>
+      <c r="F23" s="259" t="n"/>
+      <c r="G23" s="259" t="n"/>
+      <c r="H23" s="259" t="n"/>
     </row>
     <row r="24" ht="10.15" customHeight="1">
       <c r="B24" s="2" t="n"/>
@@ -8801,37 +8847,37 @@
       </c>
       <c r="B5" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C5" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-5-30301</t>
         </is>
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>405</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:16Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120300004533000000002</t>
         </is>
       </c>
       <c r="G5" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H5" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/sales/v2/deliveries?licenseNumber=SF-SBX-NY-5-30301</t>
+        </is>
+      </c>
+      <c r="H5" s="262" t="inlineStr">
+        <is>
+          <t>[{"SalesDateTime":"2026-08-27T14:02:15Z","SalesCustomerType":"Consumer","PatientLicenseNumber":null,"ConsumerId":null,"DriverEmployeeId":"1","DriverName":"Evaluation Driver","DriversLicenseNumber":"D0000001","PhoneNumberForQuestions":"+1-555-000-0000","VehicleMake":"Car","VehicleModel":"Small","VehicleLicensePlateNumber":"TP-0001","RecipientAddressStreet1":"1 Evaluation Way","RecipientAddressCity":"Albany","RecipientAddressState":"NY","RecipientAddressPostalCode":"12207","PlannedRoute":"Drive to destination.","EstimatedDepartureDateTime":"2026-08-27T15:02:15Z","EstimatedArrivalDateTime":"2026-08-27T17:02:15Z","Transactions":[{"PackageLabel":"1A4120300004533000000002","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":9.99},{"PackageLabel":"1A4120300004533000000003","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":19.98},{"PackageLabel":"1A4120300004533000000004","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":29.97}]}]</t>
         </is>
       </c>
     </row>
@@ -8841,13 +8887,13 @@
           <t>Create a valid home delivery with a SalesCustomerType as “Patient” or "Consumer" as it applies to the State  with three (3) Transactions using:</t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
-      <c r="G6" s="256" t="n"/>
-      <c r="H6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
+      <c r="G6" s="257" t="n"/>
+      <c r="H6" s="257" t="n"/>
     </row>
     <row r="7" ht="24" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A7" s="121" t="inlineStr">
@@ -8855,13 +8901,13 @@
           <t>POST/sales/v2/deliveries</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
-      <c r="G7" s="258" t="n"/>
-      <c r="H7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
+      <c r="G7" s="259" t="n"/>
+      <c r="H7" s="259" t="n"/>
     </row>
     <row r="8" ht="21.4" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A8" s="122" t="n"/>
@@ -8881,37 +8927,37 @@
       </c>
       <c r="B9" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C9" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-5-30301</t>
         </is>
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>405</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:16Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120300004533000000002</t>
         </is>
       </c>
       <c r="G9" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H9" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/sales/v2/deliveries?licenseNumber=SF-SBX-NY-5-30301</t>
+        </is>
+      </c>
+      <c r="H9" s="262" t="inlineStr">
+        <is>
+          <t>[{"SalesDateTime":"2026-08-27T14:02:15Z","SalesCustomerType":"Consumer","PatientLicenseNumber":null,"ConsumerId":null,"DriverEmployeeId":"1","DriverName":"Evaluation Driver","DriversLicenseNumber":"D0000001","PhoneNumberForQuestions":"+1-555-000-0000","VehicleMake":"Car","VehicleModel":"Small","VehicleLicensePlateNumber":"TP-0001","RecipientAddressStreet1":"1 Evaluation Way","RecipientAddressCity":"Albany","RecipientAddressState":"NY","RecipientAddressPostalCode":"12207","PlannedRoute":"Drive to destination.","EstimatedDepartureDateTime":"2026-08-27T15:02:15Z","EstimatedArrivalDateTime":"2026-08-27T17:02:15Z","Transactions":[{"PackageLabel":"1A4120300004533000000002","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":9.99},{"PackageLabel":"1A4120300004533000000003","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":19.98}],"Id":405}]</t>
         </is>
       </c>
     </row>
@@ -8921,13 +8967,13 @@
           <t>Using the Delivery created in Step 1 remove ONE of the Transactions using:</t>
         </is>
       </c>
-      <c r="B10" s="255" t="n"/>
-      <c r="C10" s="256" t="n"/>
-      <c r="D10" s="256" t="n"/>
-      <c r="E10" s="256" t="n"/>
-      <c r="F10" s="256" t="n"/>
-      <c r="G10" s="256" t="n"/>
-      <c r="H10" s="256" t="n"/>
+      <c r="B10" s="256" t="n"/>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+      <c r="F10" s="257" t="n"/>
+      <c r="G10" s="257" t="n"/>
+      <c r="H10" s="257" t="n"/>
     </row>
     <row r="11" ht="21.4" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A11" s="121" t="inlineStr">
@@ -8935,13 +8981,13 @@
           <t>PUT/sales/v2/deliveries/complete</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
-      <c r="C11" s="258" t="n"/>
-      <c r="D11" s="258" t="n"/>
-      <c r="E11" s="258" t="n"/>
-      <c r="F11" s="258" t="n"/>
-      <c r="G11" s="258" t="n"/>
-      <c r="H11" s="258" t="n"/>
+      <c r="B11" s="258" t="n"/>
+      <c r="C11" s="259" t="n"/>
+      <c r="D11" s="259" t="n"/>
+      <c r="E11" s="259" t="n"/>
+      <c r="F11" s="259" t="n"/>
+      <c r="G11" s="259" t="n"/>
+      <c r="H11" s="259" t="n"/>
     </row>
     <row r="12" ht="21.4" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A12" s="122" t="n"/>
@@ -8954,37 +9000,37 @@
       </c>
       <c r="B13" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C13" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-5-30301</t>
         </is>
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>405</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:16Z</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A4120300004533000000002</t>
         </is>
       </c>
       <c r="G13" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H13" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/sales/v2/deliveries/complete?licenseNumber=SF-SBX-NY-5-30301</t>
+        </is>
+      </c>
+      <c r="H13" s="262" t="inlineStr">
+        <is>
+          <t>[{"Id":405,"ActualArrivalDateTime":"2026-08-27T14:02:16Z","PaymentType":null,"AcceptedPackages":["1A4120300004533000000002"],"ReturnedPackages":[{"Label":"1A4120300004533000000003","ReturnQuantityVerified":1.0,"ReturnUnitOfMeasure":"Each","ReturnReason":"Unable to Deliver","ReturnReasonNote":"Evaluation step"}]}]</t>
         </is>
       </c>
     </row>
@@ -8994,13 +9040,13 @@
           <t>Using the Delivery created in Step 1 Complete the home delivery  with one (1) AcceptedPackage and one (1) ReturnedPackage</t>
         </is>
       </c>
-      <c r="B14" s="255" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="256" t="n"/>
-      <c r="G14" s="256" t="n"/>
-      <c r="H14" s="256" t="n"/>
+      <c r="B14" s="256" t="n"/>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+      <c r="F14" s="257" t="n"/>
+      <c r="G14" s="257" t="n"/>
+      <c r="H14" s="257" t="n"/>
     </row>
     <row r="15" ht="21.4" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A15" s="121" t="inlineStr">
@@ -9008,13 +9054,13 @@
           <t>PUT /sales/v2/deliveries/complete</t>
         </is>
       </c>
-      <c r="B15" s="257" t="n"/>
-      <c r="C15" s="258" t="n"/>
-      <c r="D15" s="258" t="n"/>
-      <c r="E15" s="258" t="n"/>
-      <c r="F15" s="258" t="n"/>
-      <c r="G15" s="258" t="n"/>
-      <c r="H15" s="258" t="n"/>
+      <c r="B15" s="258" t="n"/>
+      <c r="C15" s="259" t="n"/>
+      <c r="D15" s="259" t="n"/>
+      <c r="E15" s="259" t="n"/>
+      <c r="F15" s="259" t="n"/>
+      <c r="G15" s="259" t="n"/>
+      <c r="H15" s="259" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="182" t="n"/>
@@ -9337,13 +9383,13 @@
           <t>Record Retail Delivery –  Create the Delivery with 2 Destinations (legs) each with 2 packages and a package for unplanned purposes</t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
-      <c r="G6" s="256" t="n"/>
-      <c r="H6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
+      <c r="G6" s="257" t="n"/>
+      <c r="H6" s="257" t="n"/>
     </row>
     <row r="7" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A7" s="155" t="inlineStr">
@@ -9351,13 +9397,13 @@
           <t>POST/sales/v2/deliveries/retailer</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
-      <c r="G7" s="258" t="n"/>
-      <c r="H7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
+      <c r="G7" s="259" t="n"/>
+      <c r="H7" s="259" t="n"/>
     </row>
     <row r="8" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A8" s="122" t="n"/>
@@ -9417,13 +9463,13 @@
           <t>Depart for Retail Delivery using the above Retail DeliveryID -  This marks the Retailer Delivery as DEPARTED in the UI</t>
         </is>
       </c>
-      <c r="B10" s="255" t="n"/>
-      <c r="C10" s="256" t="n"/>
-      <c r="D10" s="256" t="n"/>
-      <c r="E10" s="256" t="n"/>
-      <c r="F10" s="256" t="n"/>
-      <c r="G10" s="256" t="n"/>
-      <c r="H10" s="256" t="n"/>
+      <c r="B10" s="256" t="n"/>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+      <c r="F10" s="257" t="n"/>
+      <c r="G10" s="257" t="n"/>
+      <c r="H10" s="257" t="n"/>
     </row>
     <row r="11" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A11" s="121" t="inlineStr">
@@ -9431,13 +9477,13 @@
           <t>POST/sales/v2/deliveries/retailer/depart</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
-      <c r="C11" s="258" t="n"/>
-      <c r="D11" s="258" t="n"/>
-      <c r="E11" s="258" t="n"/>
-      <c r="F11" s="258" t="n"/>
-      <c r="G11" s="258" t="n"/>
-      <c r="H11" s="258" t="n"/>
+      <c r="B11" s="258" t="n"/>
+      <c r="C11" s="259" t="n"/>
+      <c r="D11" s="259" t="n"/>
+      <c r="E11" s="259" t="n"/>
+      <c r="F11" s="259" t="n"/>
+      <c r="G11" s="259" t="n"/>
+      <c r="H11" s="259" t="n"/>
     </row>
     <row r="12" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A12" s="157" t="n"/>
@@ -9497,13 +9543,13 @@
           <t>To create an Unplanned Sale using the extra packages created in step 1 - Create an unplanned sale using this POST</t>
         </is>
       </c>
-      <c r="B14" s="255" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="256" t="n"/>
-      <c r="G14" s="256" t="n"/>
-      <c r="H14" s="256" t="n"/>
+      <c r="B14" s="256" t="n"/>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+      <c r="F14" s="257" t="n"/>
+      <c r="G14" s="257" t="n"/>
+      <c r="H14" s="257" t="n"/>
     </row>
     <row r="15" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A15" s="121" t="inlineStr">
@@ -9511,13 +9557,13 @@
           <t>POST/sales/v2/deliveries/retailer/sale</t>
         </is>
       </c>
-      <c r="B15" s="257" t="n"/>
-      <c r="C15" s="258" t="n"/>
-      <c r="D15" s="258" t="n"/>
-      <c r="E15" s="258" t="n"/>
-      <c r="F15" s="258" t="n"/>
-      <c r="G15" s="258" t="n"/>
-      <c r="H15" s="258" t="n"/>
+      <c r="B15" s="258" t="n"/>
+      <c r="C15" s="259" t="n"/>
+      <c r="D15" s="259" t="n"/>
+      <c r="E15" s="259" t="n"/>
+      <c r="F15" s="259" t="n"/>
+      <c r="G15" s="259" t="n"/>
+      <c r="H15" s="259" t="n"/>
     </row>
     <row r="16" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A16" s="122" t="n"/>
@@ -9566,13 +9612,13 @@
           <t>End the Retail delivery using RetailDeliveryID</t>
         </is>
       </c>
-      <c r="B18" s="255" t="n"/>
-      <c r="C18" s="256" t="n"/>
-      <c r="D18" s="256" t="n"/>
-      <c r="E18" s="256" t="n"/>
-      <c r="F18" s="256" t="n"/>
-      <c r="G18" s="256" t="n"/>
-      <c r="H18" s="256" t="n"/>
+      <c r="B18" s="256" t="n"/>
+      <c r="C18" s="257" t="n"/>
+      <c r="D18" s="257" t="n"/>
+      <c r="E18" s="257" t="n"/>
+      <c r="F18" s="257" t="n"/>
+      <c r="G18" s="257" t="n"/>
+      <c r="H18" s="257" t="n"/>
     </row>
     <row r="19" ht="16.15" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A19" s="121" t="inlineStr">
@@ -9580,13 +9626,13 @@
           <t>POST/sales/v2/deliveries/retailer/end</t>
         </is>
       </c>
-      <c r="B19" s="257" t="n"/>
-      <c r="C19" s="258" t="n"/>
-      <c r="D19" s="258" t="n"/>
-      <c r="E19" s="258" t="n"/>
-      <c r="F19" s="258" t="n"/>
-      <c r="G19" s="258" t="n"/>
-      <c r="H19" s="258" t="n"/>
+      <c r="B19" s="258" t="n"/>
+      <c r="C19" s="259" t="n"/>
+      <c r="D19" s="259" t="n"/>
+      <c r="E19" s="259" t="n"/>
+      <c r="F19" s="259" t="n"/>
+      <c r="G19" s="259" t="n"/>
+      <c r="H19" s="259" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -10318,10 +10364,10 @@
       </c>
       <c r="G5" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/transfers/v2/incoming?lastModifiedStart=2026-08-26T13%3A40%3A30Z&amp;lastModifiedEnd=2026-08-27T13%3A40%3A30Z&amp;licenseNumber=SF-SBX-NY-14-30301</t>
-        </is>
-      </c>
-      <c r="H5" s="260" t="inlineStr">
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/incoming?lastModifiedStart=2026-08-26T14%3A02%3A32Z&amp;lastModifiedEnd=2026-08-27T14%3A02%3A32Z&amp;licenseNumber=SF-SBX-NY-14-30301</t>
+        </is>
+      </c>
+      <c r="H5" s="262" t="inlineStr">
         <is>
           <t>{"Data":[{"Id":38509,"ManifestNumber":"0000038509","InvoiceNumber":"Invoice 123","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-7-30301","ShipperFacilityName":"Sandbox MED Cultivator","Name":null,"TransporterFacilityLicenseNumber":"","TransporterFacilityName":"","DriverName":"","DriverOccupationalLicenseNumber":"","DriverVehicleLicenseNumber":"","VehicleMake":"","VehicleModel":"","VehicleLicensePlateNumber":"","VehicleRegistrationNumber":"","DeliveryCount":1,"ReceivedDeliveryCount":1,"PackageCount":3,"ReceivedPackageCount":3,"ContainsPlantPackage":false,"ContainsProductPackage":true,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:16:38+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:16:40+00:00","DeliveryId":38509,"RecipientFacilityLicenseNumber":"SF-SBX-NY-14-30301","RecipientFacilityName":"Sandbox AU Processor","ShipmentTypeName":"Affiliated Transfer","ShipmentTransactionType":"Standard","EstimatedDepartureDateTime":"2026-08-28T07:16:38.340","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"2026-08-28T19:16:38.340","ActualArrivalDateTime":null,"DeliveryPackageCount":3,"DeliveryReceivedPackageCount":3,"ReceivedDateTime":"2026-08-27T13:16:39+00:00","EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":38510,"ManifestNumber":"0000038510","InvoiceNumber":"Invoice 123","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-7-30301","ShipperFacilityName":"Sandbox MED Cultivator","Name":null,"TransporterFacilityLicenseNumber":"","TransporterFacilityName":"","DriverName":"","DriverOccupationalLicenseNumber":"","DriverVehicleLicenseNumber":"","VehicleMake":"","VehicleModel":"","VehicleLicensePlateNumber":"","VehicleRegistrationNumber":"","DeliveryCount":1,"ReceivedDeliveryCount":1,"PackageCount":3,"ReceivedPackageCount":3,"ContainsPlantPackage":false,"ContainsProductPackage":true,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:16:50+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:16:51+00:00","DeliveryId":38510,"RecipientFacilityLicenseNumber":"SF-SBX-NY-14-30301","RecipientFacilityName":"Sandbox AU Processor","ShipmentTypeName":"Affiliated Transfer","ShipmentTransactionType":"Standard","EstimatedDepartureDateTime":"2026-08-28T07:16:50.067","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"2026-08-28T19:16:50.067","ActualArrivalDateTime":null,"DeliveryPackageCount":3,"DeliveryReceivedPackageCount":3,"ReceivedDateTime":"2026-08-27T13:16:50+00:00","EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null}],"Total":2,"TotalRecords":2,"PageSize":2,"RecordsOnPage":2,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
         </is>
@@ -10333,13 +10379,13 @@
           <t>Find a Incoming Transfer</t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
-      <c r="G6" s="256" t="n"/>
-      <c r="H6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
+      <c r="G6" s="257" t="n"/>
+      <c r="H6" s="257" t="n"/>
     </row>
     <row r="7" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A7" s="121" t="inlineStr">
@@ -10347,13 +10393,13 @@
           <t>GET/transfers/v2/incoming</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
-      <c r="G7" s="258" t="n"/>
-      <c r="H7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
+      <c r="G7" s="259" t="n"/>
+      <c r="H7" s="259" t="n"/>
     </row>
     <row r="8" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A8" s="122" t="n"/>
@@ -10392,10 +10438,10 @@
       </c>
       <c r="G9" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/transfers/v2/outgoing?lastModifiedStart=2026-08-26T13%3A40%3A30Z&amp;lastModifiedEnd=2026-08-27T13%3A40%3A30Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
-        </is>
-      </c>
-      <c r="H9" s="260" t="inlineStr">
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/outgoing?lastModifiedStart=2026-08-26T14%3A02%3A32Z&amp;lastModifiedEnd=2026-08-27T14%3A02%3A32Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H9" s="262" t="inlineStr">
         <is>
           <t>{"Data":[{"Id":38515,"ManifestNumber":"0000038515","InvoiceNumber":"Invoice 123","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":null,"TransporterFacilityLicenseNumber":"","TransporterFacilityName":"","DriverName":"","DriverOccupationalLicenseNumber":"","DriverVehicleLicenseNumber":"","VehicleMake":"","VehicleModel":"","VehicleLicensePlateNumber":"","VehicleRegistrationNumber":"","DeliveryCount":1,"ReceivedDeliveryCount":1,"PackageCount":3,"ReceivedPackageCount":3,"ContainsPlantPackage":false,"ContainsProductPackage":true,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:23:03+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:23:04+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":38516,"ManifestNumber":"0000038516","InvoiceNumber":"Invoice 123","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":null,"TransporterFacilityLicenseNumber":"","TransporterFacilityName":"","DriverName":"","DriverOccupationalLicenseNumber":"","DriverVehicleLicenseNumber":"","VehicleMake":"","VehicleModel":"","VehicleLicensePlateNumber":"","VehicleRegistrationNumber":"","DeliveryCount":1,"ReceivedDeliveryCount":1,"PackageCount":3,"ReceivedPackageCount":3,"ContainsPlantPackage":false,"ContainsProductPackage":true,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:23:33+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:23:33+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null}],"Total":2,"TotalRecords":2,"PageSize":2,"RecordsOnPage":2,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
         </is>
@@ -10407,13 +10453,13 @@
           <t>Find a Outgoing  Transfer</t>
         </is>
       </c>
-      <c r="B10" s="255" t="n"/>
-      <c r="C10" s="256" t="n"/>
-      <c r="D10" s="256" t="n"/>
-      <c r="E10" s="256" t="n"/>
-      <c r="F10" s="256" t="n"/>
-      <c r="G10" s="256" t="n"/>
-      <c r="H10" s="256" t="n"/>
+      <c r="B10" s="256" t="n"/>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+      <c r="F10" s="257" t="n"/>
+      <c r="G10" s="257" t="n"/>
+      <c r="H10" s="257" t="n"/>
     </row>
     <row r="11" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A11" s="121" t="inlineStr">
@@ -10421,13 +10467,13 @@
           <t>GET /transfers/v2/outgoing</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
-      <c r="C11" s="258" t="n"/>
-      <c r="D11" s="258" t="n"/>
-      <c r="E11" s="258" t="n"/>
-      <c r="F11" s="258" t="n"/>
-      <c r="G11" s="258" t="n"/>
-      <c r="H11" s="258" t="n"/>
+      <c r="B11" s="258" t="n"/>
+      <c r="C11" s="259" t="n"/>
+      <c r="D11" s="259" t="n"/>
+      <c r="E11" s="259" t="n"/>
+      <c r="F11" s="259" t="n"/>
+      <c r="G11" s="259" t="n"/>
+      <c r="H11" s="259" t="n"/>
     </row>
     <row r="12" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A12" s="122" t="n"/>
@@ -10465,10 +10511,10 @@
       </c>
       <c r="G13" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/transfers/v2/rejected?lastModifiedStart=2026-08-25T13%3A40%3A30Z&amp;lastModifiedEnd=2026-08-26T13%3A40%3A30Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
-        </is>
-      </c>
-      <c r="H13" s="260" t="inlineStr">
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/rejected?lastModifiedStart=2026-08-25T14%3A02%3A33Z&amp;lastModifiedEnd=2026-08-26T14%3A02%3A33Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H13" s="262" t="inlineStr">
         <is>
           <t>{"Data":[],"Total":0,"TotalRecords":0,"PageSize":0,"RecordsOnPage":0,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
         </is>
@@ -10480,13 +10526,13 @@
           <t>Find a Rejected  Transfer</t>
         </is>
       </c>
-      <c r="B14" s="255" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="256" t="n"/>
-      <c r="G14" s="256" t="n"/>
-      <c r="H14" s="256" t="n"/>
+      <c r="B14" s="256" t="n"/>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+      <c r="F14" s="257" t="n"/>
+      <c r="G14" s="257" t="n"/>
+      <c r="H14" s="257" t="n"/>
     </row>
     <row r="15" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A15" s="121" t="inlineStr">
@@ -10494,13 +10540,13 @@
           <t>GET /transfers/v2/rejected</t>
         </is>
       </c>
-      <c r="B15" s="257" t="n"/>
-      <c r="C15" s="258" t="n"/>
-      <c r="D15" s="258" t="n"/>
-      <c r="E15" s="258" t="n"/>
-      <c r="F15" s="258" t="n"/>
-      <c r="G15" s="258" t="n"/>
-      <c r="H15" s="258" t="n"/>
+      <c r="B15" s="258" t="n"/>
+      <c r="C15" s="259" t="n"/>
+      <c r="D15" s="259" t="n"/>
+      <c r="E15" s="259" t="n"/>
+      <c r="F15" s="259" t="n"/>
+      <c r="G15" s="259" t="n"/>
+      <c r="H15" s="259" t="n"/>
     </row>
     <row r="16" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A16" s="124" t="n"/>
@@ -10548,7 +10594,7 @@
           <t>https://sandbox-api-ny.metrc.com/transfers/v2/38509/deliveries</t>
         </is>
       </c>
-      <c r="H17" s="260" t="inlineStr">
+      <c r="H17" s="262" t="inlineStr">
         <is>
           <t>{"Data":[{"Id":38509,"ManifestNumber":null,"DeliveryNumber":0,"RecipientFacilityLicenseNumber":"SF-SBX-NY-14-30301","RecipientFacilityName":"Sandbox AU Processor","ShipmentTypeName":"Affiliated Transfer","ShipmentTransactionType":"Standard","InvoiceNumber":"Invoice 123","PaymentTermDays":null,"PaymentDueDate":null,"EstimatedDepartureDateTime":"2026-08-28T07:16:38.340","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"2026-08-28T19:16:38.340","ActualArrivalDateTime":null,"GrossWeight":null,"GrossUnitOfWeightId":null,"GrossUnitOfWeightName":null,"PlannedRoute":"I will use this route.","DeliveryPackageCount":3,"DeliveryReceivedPackageCount":3,"ReceivedDateTime":"2026-08-27T13:16:39+00:00","EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"RejectedPackagesReturned":false,"PDFDocumentFileSystemId":null}],"Total":1,"TotalRecords":1,"PageSize":1,"RecordsOnPage":1,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
         </is>
@@ -10560,13 +10606,13 @@
           <t>Find a Transfer by the Manifest ID number</t>
         </is>
       </c>
-      <c r="B18" s="255" t="n"/>
-      <c r="C18" s="256" t="n"/>
-      <c r="D18" s="256" t="n"/>
-      <c r="E18" s="256" t="n"/>
-      <c r="F18" s="256" t="n"/>
-      <c r="G18" s="256" t="n"/>
-      <c r="H18" s="256" t="n"/>
+      <c r="B18" s="256" t="n"/>
+      <c r="C18" s="257" t="n"/>
+      <c r="D18" s="257" t="n"/>
+      <c r="E18" s="257" t="n"/>
+      <c r="F18" s="257" t="n"/>
+      <c r="G18" s="257" t="n"/>
+      <c r="H18" s="257" t="n"/>
     </row>
     <row r="19" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A19" s="121" t="inlineStr">
@@ -10574,13 +10620,13 @@
           <t>GET /transfers/v2/{id}/deliveries</t>
         </is>
       </c>
-      <c r="B19" s="257" t="n"/>
-      <c r="C19" s="258" t="n"/>
-      <c r="D19" s="258" t="n"/>
-      <c r="E19" s="258" t="n"/>
-      <c r="F19" s="258" t="n"/>
-      <c r="G19" s="258" t="n"/>
-      <c r="H19" s="258" t="n"/>
+      <c r="B19" s="258" t="n"/>
+      <c r="C19" s="259" t="n"/>
+      <c r="D19" s="259" t="n"/>
+      <c r="E19" s="259" t="n"/>
+      <c r="F19" s="259" t="n"/>
+      <c r="G19" s="259" t="n"/>
+      <c r="H19" s="259" t="n"/>
     </row>
     <row r="20" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A20" s="124" t="n"/>
@@ -10615,7 +10661,7 @@
       </c>
       <c r="E21" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T13:40:31Z</t>
+          <t>2026-08-27T14:02:33Z</t>
         </is>
       </c>
       <c r="F21" s="247" t="inlineStr">
@@ -10628,7 +10674,7 @@
           <t>https://sandbox-api-ny.metrc.com/transfers/v2/deliveries/38509/packages</t>
         </is>
       </c>
-      <c r="H21" s="260" t="inlineStr">
+      <c r="H21" s="262" t="inlineStr">
         <is>
           <t>{"Data":[{"PackageId":218655,"PackageLabel":"1A412030000453A000000011","PackageType":"Product","SourceHarvestNames":"2026-07-08-SBX Default Location Type Location 1-M","SourcePackageLabels":"","ItemId":294435,"ProductName":"SBX Bud/Flower - Bulk SBX Strain 1 Item","ItemName":"SBX Bud/Flower - Bulk SBX Strain 1 Item","ProductCategoryName":"Bud/Flower - Bulk","ItemCategoryName":"Bud/Flower - Bulk","ItemStrainName":"SBX Strain 1","ItemBrandName":null,"ItemUnitCbdPercent":null,"ItemUnitCbdContent":null,"ItemUnitCbdContentUnitOfMeasureName":null,"ItemUnitCbdContentDose":null,"ItemUnitCbdContentDoseUnitOfMeasureName":null,"ItemUnitThcPercent":null,"ItemUnitThcContent":null,"ItemUnitThcContentUnitOfMeasureName":null,"ItemUnitThcContentDose":null,"ItemUnitThcContentDoseUnitOfMeasureName":null,"ItemUnitCbdAPercent":null,"ItemUnitCbdAContent":null,"ItemUnitCbdAContentUnitOfMeasureName":null,"ItemUnitCbdAContentDose":null,"ItemUnitCbdAContentDoseUnitOfMeasureName":null,"ItemUnitThcAPercent":null,"ItemUnitThcAContent":null,"ItemUnitThcAContentUnitOfMeasureName":null,"ItemUnitThcAContentDose":null,"ItemUnitThcAContentDoseUnitOfMeasureName":null,"ItemUnitVolume":null,"ItemUnitVolumeUnitOfMeasureName":null,"ItemUnitWeight":null,"ItemUnitWeightUnitOfMeasureName":null,"ItemServingSize":"","ItemSupplyDurationDays":null,"ItemUnitQuantity":null,"ItemUnitQuantityUnitOfMeasureName":null,"LabTestingState":"NotSubmitted","ProductionBatchNumber":null,"IsTradeSample":false,"IsTradeSamplePersistent":false,"SourcePackageIsTradeSample":false,"IsDonation":false,"SourcePackageIsDonation":false,"IsTestingSample":false,"ProductRequiresRemediation":false,"ContainsRemediatedProduct":false,"RemediationDate":null,"ContainsPreTreatedProduct":false,"PreTreatmentDate":null,"ShipmentPackageState":"Accepted","ShippedQuantity":11.0,"ShippedUnitOfMeasureName":"Grams","PackagedDate":"2026-07-18","ExpirationDate":null,"SellByDate":null,"UseByDate":null,"GrossUnitOfWeightName":null,"ReceivedQuantity":11.0,"ReceivedUnitOfMeasureName":"Grams","ProductLabel":null,"SourceProductionBatchNumbers":null,"ExternalId":null,"IsFinishedGood":false,"CreatedQuantity":11.0,"CreatedQuantityUnitOfMeasureAbbreviation":"g","TagId":null},{"PackageId":218656,"PackageLabel":"1A412030000453A000000012","PackageType":"Product","SourceHarvestNames":"2026-07-08-SBX Default Location Type Location 1-H","SourcePackageLabels":"","ItemId":294435,"ProductName":"SBX Bud/Flower - Bulk SBX Strain 1 Item","ItemName":"SBX Bud/Flower - Bulk SBX Strain 1 Item","ProductCategoryName":"Bud/Flower - Bulk","ItemCategoryName":"Bud/Flower - Bulk","ItemStrainName":"SBX Strain 1","ItemBrandName":null,"ItemUnitCbdPercent":null,"ItemUnitCbdContent":null,"ItemUnitCbdContentUnitOfMeasureName":null,"ItemUnitCbdContentDose":null,"ItemUnitCbdContentDoseUnitOfMeasureName":null,"ItemUnitThcPercent":null,"ItemUnitThcContent":null,"ItemUnitThcContentUnitOfMeasureName":null,"ItemUnitThcContentDose":null,"ItemUnitThcContentDoseUnitOfMeasureName":null,"ItemUnitCbdAPercent":null,"ItemUnitCbdAContent":null,"ItemUnitCbdAContentUnitOfMeasureName":null,"ItemUnitCbdAContentDose":null,"ItemUnitCbdAContentDoseUnitOfMeasureName":null,"ItemUnitThcAPercent":null,"ItemUnitThcAContent":null,"ItemUnitThcAContentUnitOfMeasureName":null,"ItemUnitThcAContentDose":null,"ItemUnitThcAContentDoseUnitOfMeasureName":null,"ItemUnitVolume":null,"ItemUnitVolumeUnitOfMeasureName":null,"ItemUnitWeight":null,"ItemUnitWeightUnitOfMeasureName":null,"ItemServingSize":"","ItemSupplyDurationDays":null,"ItemUnitQuantity":null,"ItemUnitQuantityUnitOfMeasureName":null,"LabTestingState":"NotSubmitted","ProductionBatchNumber":null,"IsTradeSample":false,"IsTradeSamplePersistent":false,"SourcePackageIsTradeSample":false,"IsDonation":false,"SourcePackageIsDonation":false,"IsTestingSample":false,"ProductRequiresRemediation":false,"ContainsRemediatedProduct":false,"RemediationDate":null,"ContainsPreTreatedProduct":false,"PreTreatmentDate":null,"ShipmentPackageState":"Accepted","ShippedQuantity":9.0,"ShippedUnitOfMeasureName":"Grams","PackagedDate":"2026-07-18","ExpirationDate":null,"SellByDate":null,"UseByDate":null,"GrossUnitOfWeightName":null,"ReceivedQuantity":9.0,"ReceivedUnitOfMeasureName":"Grams","ProductLabel":null,"SourceProductionBatchNumbers":null,"ExternalId":null,"IsFinishedGood":false,"CreatedQuantity":9.0,"CreatedQuantityUnitOfMeasureAbbreviation":"g","TagId":null},{"PackageId":218657,"PackageLabel":"1A412030000453A000000013","PackageType":"Product","SourceHarvestNames":"2026-07-08-SBX Default Location Type Location 1-M","SourcePackageLabels":"","ItemId":294435,"ProductName":"SBX Bud/Flower - Bulk SBX Strain 1 Item","ItemName":"SBX Bud/Flower - Bulk SBX Strain 1 Item","ProductCategoryName":"Bud/Flower - Bulk","ItemCategoryName":"Bud/Flower - Bulk","ItemStrainName":"SBX Strain 1","ItemBrandName":null,"ItemUnitCbdPercent":null,"ItemUnitCbdContent":null,"ItemUnitCbdContentUnitOfMeasureName":null,"ItemUnitCbdContentDose":null,"ItemUnitCbdContentDoseUnitOfMeasureName":null,"ItemUnitThcPercent":null,"ItemUnitThcContent":null,"ItemUnitThcContentUnitOfMeasureName":null,"ItemUnitThcContentDose":null,"ItemUnitThcContentDoseUnitOfMeasureName":null,"ItemUnitCbdAPercent":null,"ItemUnitCbdAContent":null,"ItemUnitCbdAContentUnitOfMeasureName":null,"ItemUnitCbdAContentDose":null,"ItemUnitCbdAContentDoseUnitOfMeasureName":null,"ItemUnitThcAPercent":null,"ItemUnitThcAContent":null,"ItemUnitThcAContentUnitOfMeasureName":null,"ItemUnitThcAContentDose":null,"ItemUnitThcAContentDoseUnitOfMeasureName":null,"ItemUnitVolume":null,"ItemUnitVolumeUnitOfMeasureName":null,"ItemUnitWeight":null,"ItemUnitWeightUnitOfMeasureName":null,"ItemServingSize":"","ItemSupplyDurationDays":null,"ItemUnitQuantity":null,"ItemUnitQuantityUnitOfMeasureName":null,"LabTestingState":"NotSubmitted","ProductionBatchNumber":null,"IsTradeSample":false,"IsTradeSamplePersistent":false,"SourcePackageIsTradeSample":false,"IsDonation":false,"SourcePackageIsDonation":false,"IsTestingSample":false,"ProductRequiresRemediation":false,"ContainsRemediatedProduct":false,"RemediationDate":null,"ContainsPreTreatedProduct":false,"PreTreatmentDate":null,"ShipmentPackageState":"Accepted","ShippedQuantity":15.0,"ShippedUnitOfMeasureName":"Grams","PackagedDate":"2026-07-18","ExpirationDate":null,"SellByDate":null,"UseByDate":null,"GrossUnitOfWeightName":null,"ReceivedQuantity":15.0,"ReceivedUnitOfMeasureName":"Grams","ProductLabel":null,"SourceProductionBatchNumbers":null,"ExternalId":null,"IsFinishedGood":false,"CreatedQuantity":15.0,"CreatedQuantityUnitOfMeasureAbbreviation":"g","TagId":null}],"Total":3,"TotalRecords":3,"PageSize":3,"RecordsOnPage":3,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
         </is>
@@ -10640,13 +10686,13 @@
           <t xml:space="preserve"> Find The Packages Using the Delivery ID number                               </t>
         </is>
       </c>
-      <c r="B22" s="255" t="n"/>
-      <c r="C22" s="256" t="n"/>
-      <c r="D22" s="256" t="n"/>
-      <c r="E22" s="256" t="n"/>
-      <c r="F22" s="256" t="n"/>
-      <c r="G22" s="256" t="n"/>
-      <c r="H22" s="256" t="n"/>
+      <c r="B22" s="256" t="n"/>
+      <c r="C22" s="257" t="n"/>
+      <c r="D22" s="257" t="n"/>
+      <c r="E22" s="257" t="n"/>
+      <c r="F22" s="257" t="n"/>
+      <c r="G22" s="257" t="n"/>
+      <c r="H22" s="257" t="n"/>
     </row>
     <row r="23" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A23" s="121" t="inlineStr">
@@ -10654,13 +10700,13 @@
           <t>GET /transfers/v2/delivery/{id}/packages</t>
         </is>
       </c>
-      <c r="B23" s="257" t="n"/>
-      <c r="C23" s="258" t="n"/>
-      <c r="D23" s="258" t="n"/>
-      <c r="E23" s="258" t="n"/>
-      <c r="F23" s="258" t="n"/>
-      <c r="G23" s="258" t="n"/>
-      <c r="H23" s="258" t="n"/>
+      <c r="B23" s="258" t="n"/>
+      <c r="C23" s="259" t="n"/>
+      <c r="D23" s="259" t="n"/>
+      <c r="E23" s="259" t="n"/>
+      <c r="F23" s="259" t="n"/>
+      <c r="G23" s="259" t="n"/>
+      <c r="H23" s="259" t="n"/>
     </row>
     <row r="24" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A24" s="122" t="n"/>
@@ -10680,7 +10726,7 @@
       </c>
       <c r="B25" s="249" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C25" s="248" t="inlineStr">
@@ -10695,12 +10741,12 @@
       </c>
       <c r="E25" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T13:40:31Z</t>
+          <t>2026-08-27T14:02:33Z</t>
         </is>
       </c>
       <c r="F25" s="247" t="inlineStr">
         <is>
-          <t> </t>
+          <t>1A412030000453A000000011, 1A412030000453A000000012, 1A412030000453A000000013</t>
         </is>
       </c>
       <c r="G25" s="247" t="inlineStr">
@@ -10708,9 +10754,9 @@
           <t>https://sandbox-api-ny.metrc.com/transfers/v2/deliveries/38509/packages/wholesale</t>
         </is>
       </c>
-      <c r="H25" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="H25" s="262" t="inlineStr">
+        <is>
+          <t>{"Data":[{"PackageId":218655,"PackageLabel":"1A412030000453A000000011","ShipperWholesalePrice":null,"ReceiverWholesalePrice":null},{"PackageId":218656,"PackageLabel":"1A412030000453A000000012","ShipperWholesalePrice":null,"ReceiverWholesalePrice":null},{"PackageId":218657,"PackageLabel":"1A412030000453A000000013","ShipperWholesalePrice":null,"ReceiverWholesalePrice":null}],"Total":3,"TotalRecords":3,"PageSize":3,"RecordsOnPage":3,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
         </is>
       </c>
     </row>
@@ -10720,13 +10766,13 @@
           <t xml:space="preserve"> Transfers Wholesale Find Packages Wholesale Pricing Using the Delivery ID                                                                                        </t>
         </is>
       </c>
-      <c r="B26" s="255" t="n"/>
-      <c r="C26" s="256" t="n"/>
-      <c r="D26" s="256" t="n"/>
-      <c r="E26" s="256" t="n"/>
-      <c r="F26" s="256" t="n"/>
-      <c r="G26" s="256" t="n"/>
-      <c r="H26" s="256" t="n"/>
+      <c r="B26" s="256" t="n"/>
+      <c r="C26" s="257" t="n"/>
+      <c r="D26" s="257" t="n"/>
+      <c r="E26" s="257" t="n"/>
+      <c r="F26" s="257" t="n"/>
+      <c r="G26" s="257" t="n"/>
+      <c r="H26" s="257" t="n"/>
     </row>
     <row r="27" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A27" s="121" t="inlineStr">
@@ -10734,13 +10780,13 @@
           <t xml:space="preserve"> GET/transfers/v2/delivery/{id}/packages/wholesale</t>
         </is>
       </c>
-      <c r="B27" s="257" t="n"/>
-      <c r="C27" s="258" t="n"/>
-      <c r="D27" s="258" t="n"/>
-      <c r="E27" s="258" t="n"/>
-      <c r="F27" s="258" t="n"/>
-      <c r="G27" s="258" t="n"/>
-      <c r="H27" s="258" t="n"/>
+      <c r="B27" s="258" t="n"/>
+      <c r="C27" s="259" t="n"/>
+      <c r="D27" s="259" t="n"/>
+      <c r="E27" s="259" t="n"/>
+      <c r="F27" s="259" t="n"/>
+      <c r="G27" s="259" t="n"/>
+      <c r="H27" s="259" t="n"/>
     </row>
     <row r="28" ht="25.9" customHeight="1">
       <c r="A28" s="130" t="n"/>
@@ -11089,22 +11135,22 @@
       </c>
       <c r="B5" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C5" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>16006</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:18Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
@@ -11114,12 +11160,12 @@
       </c>
       <c r="G5" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H5" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/templates/outgoing?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H5" s="262" t="inlineStr">
+        <is>
+          <t>[{"Name":"TP Template A 0827-1402","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-5-30301","InvoiceNumber":"INV-A-0827-1402","TransferTypeName":"Affiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-27T15:02:16Z","EstimatedArrivalDateTime":"2026-08-27T18:02:16Z","Transporters":[],"Packages":[]}]}]</t>
         </is>
       </c>
     </row>
@@ -11129,13 +11175,13 @@
           <t>Set up a Template A</t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
-      <c r="G6" s="256" t="n"/>
-      <c r="H6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
+      <c r="G6" s="257" t="n"/>
+      <c r="H6" s="257" t="n"/>
     </row>
     <row r="7" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A7" s="121" t="inlineStr">
@@ -11143,13 +11189,13 @@
           <t>POST/transfers/v2/templates/outgoing</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
-      <c r="G7" s="258" t="n"/>
-      <c r="H7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
+      <c r="G7" s="259" t="n"/>
+      <c r="H7" s="259" t="n"/>
     </row>
     <row r="8" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A8" s="122" t="n"/>
@@ -11163,22 +11209,22 @@
       </c>
       <c r="B9" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C9" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>16007</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:18Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
@@ -11188,12 +11234,12 @@
       </c>
       <c r="G9" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H9" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/templates/outgoing?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H9" s="262" t="inlineStr">
+        <is>
+          <t>[{"Name":"TP Template B 0827-1402","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-5-30301","InvoiceNumber":"INV-B-0827-1402","TransferTypeName":"Affiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-27T15:02:16Z","EstimatedArrivalDateTime":"2026-08-27T18:02:16Z","Transporters":[],"Packages":[]}]}]</t>
         </is>
       </c>
     </row>
@@ -11203,13 +11249,13 @@
           <t>Set up a Template B</t>
         </is>
       </c>
-      <c r="B10" s="255" t="n"/>
-      <c r="C10" s="256" t="n"/>
-      <c r="D10" s="256" t="n"/>
-      <c r="E10" s="256" t="n"/>
-      <c r="F10" s="256" t="n"/>
-      <c r="G10" s="256" t="n"/>
-      <c r="H10" s="256" t="n"/>
+      <c r="B10" s="256" t="n"/>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+      <c r="F10" s="257" t="n"/>
+      <c r="G10" s="257" t="n"/>
+      <c r="H10" s="257" t="n"/>
     </row>
     <row r="11" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A11" s="121" t="inlineStr">
@@ -11217,13 +11263,13 @@
           <t>POST/transfers/v2/templates/outgoing</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
-      <c r="C11" s="258" t="n"/>
-      <c r="D11" s="258" t="n"/>
-      <c r="E11" s="258" t="n"/>
-      <c r="F11" s="258" t="n"/>
-      <c r="G11" s="258" t="n"/>
-      <c r="H11" s="258" t="n"/>
+      <c r="B11" s="258" t="n"/>
+      <c r="C11" s="259" t="n"/>
+      <c r="D11" s="259" t="n"/>
+      <c r="E11" s="259" t="n"/>
+      <c r="F11" s="259" t="n"/>
+      <c r="G11" s="259" t="n"/>
+      <c r="H11" s="259" t="n"/>
     </row>
     <row r="12" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A12" s="122" t="n"/>
@@ -11236,22 +11282,22 @@
       </c>
       <c r="B13" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C13" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>16006, 16007</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:18+00:00</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
@@ -11261,12 +11307,12 @@
       </c>
       <c r="G13" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H13" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/templates/outgoing?lastModifiedStart=2026-08-26T14%3A02%3A18Z&amp;lastModifiedEnd=2026-08-27T14%3A02%3A18Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H13" s="262" t="inlineStr">
+        <is>
+          <t>{"Data":[{"Id":16006,"ManifestNumber":"T-0000016006","InvoiceNumber":"INV-A-0827-1402","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0827-1402","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T14:02:18+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T14:02:18+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":16007,"ManifestNumber":"T-0000016007","InvoiceNumber":"INV-B-0827-1402","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0827-1402","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T14:02:18+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T14:02:18+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15909,"ManifestNumber":"T-0000015909","InvoiceNumber":"INV-A-0827-1400","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0827-1400 (Updated)","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T14:00:28+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T14:00:28+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":16005,"ManifestNumber":"T-0000016005","InvoiceNumber":"INV-B-0827-1400","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0827-1400","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T14:00:28+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T14:00:28+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15907,"ManifestNumber":"T-0000015907","InvoiceNumber":"INV-A-0827-1359","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0827-1359 (Updated)","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:59:46+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:59:46+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15908,"ManifestNumber":"T-0000015908","InvoiceNumber":"INV-B-0827-1359","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0827-1359","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:59:46+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:59:46+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15906,"ManifestNumber":"T-0000015906","InvoiceNumber":"INV-B-0827-1358","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0827-1358","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:59:06+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:59:06+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":16004,"ManifestNumber":"T-0000016004","InvoiceNumber":"INV-A-0827-1358","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0827-1358 (Updated)","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:59:06+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:59:07+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15905,"ManifestNumber":"T-0000015905","InvoiceNumber":"INV-B-0827-1357","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0827-1357","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:57:53+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:57:53+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":16003,"ManifestNumber":"T-0000016003","InvoiceNumber":"INV-A-0827-1357","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0827-1357 (Updated)","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:57:53+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:57:53+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15903,"ManifestNumber":"T-0000015903","InvoiceNumber":"INV-A-0827-1355","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0827-1355 (Updated)","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:56:00+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:56:01+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15904,"ManifestNumber":"T-0000015904","InvoiceNumber":"INV-B-0827-1355","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0827-1355","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:56:00+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:56:00+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15902,"ManifestNumber":"T-0000015902","InvoiceNumber":"INV-A-0827-1353","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0827-1353 (Updated)","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:54:08+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:54:08+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":16002,"ManifestNumber":"T-0000016002","InvoiceNumber":"INV-B-0827-1353","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0827-1353","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:54:08+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:54:08+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null}],"Total":14,"TotalRecords":14,"PageSize":14,"RecordsOnPage":14,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
         </is>
       </c>
     </row>
@@ -11276,13 +11322,13 @@
           <t>Find the two Templates created in Step 1a and 1b  using the date search</t>
         </is>
       </c>
-      <c r="B14" s="255" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="256" t="n"/>
-      <c r="G14" s="256" t="n"/>
-      <c r="H14" s="256" t="n"/>
+      <c r="B14" s="256" t="n"/>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+      <c r="F14" s="257" t="n"/>
+      <c r="G14" s="257" t="n"/>
+      <c r="H14" s="257" t="n"/>
     </row>
     <row r="15" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A15" s="121" t="inlineStr">
@@ -11290,13 +11336,13 @@
           <t>GE</t>
         </is>
       </c>
-      <c r="B15" s="257" t="n"/>
-      <c r="C15" s="258" t="n"/>
-      <c r="D15" s="258" t="n"/>
-      <c r="E15" s="258" t="n"/>
-      <c r="F15" s="258" t="n"/>
-      <c r="G15" s="258" t="n"/>
-      <c r="H15" s="258" t="n"/>
+      <c r="B15" s="258" t="n"/>
+      <c r="C15" s="259" t="n"/>
+      <c r="D15" s="259" t="n"/>
+      <c r="E15" s="259" t="n"/>
+      <c r="F15" s="259" t="n"/>
+      <c r="G15" s="259" t="n"/>
+      <c r="H15" s="259" t="n"/>
     </row>
     <row r="16" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A16" s="124" t="n"/>
@@ -11316,7 +11362,7 @@
       </c>
       <c r="B17" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C17" s="248" t="inlineStr">
@@ -11326,12 +11372,12 @@
       </c>
       <c r="D17" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>16006</t>
         </is>
       </c>
       <c r="E17" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:18Z</t>
         </is>
       </c>
       <c r="F17" s="247" t="inlineStr">
@@ -11341,12 +11387,12 @@
       </c>
       <c r="G17" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H17" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/templates/outgoing/16006/deliveries</t>
+        </is>
+      </c>
+      <c r="H17" s="262" t="inlineStr">
+        <is>
+          <t>{"Data":[{"Id":16511,"ManifestNumber":null,"DeliveryNumber":0,"RecipientFacilityLicenseNumber":"SF-SBX-NY-5-30301","RecipientFacilityName":"Sandbox AU Dispensary","ShipmentTypeName":"Affiliated Transfer","ShipmentTransactionType":"Standard","InvoiceNumber":"INV-A-0827-1402","PaymentTermDays":null,"PaymentDueDate":null,"EstimatedDepartureDateTime":"2026-08-27T15:02:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"2026-08-27T18:02:00.000","ActualArrivalDateTime":null,"GrossWeight":null,"GrossUnitOfWeightId":null,"GrossUnitOfWeightName":null,"PlannedRoute":"Evaluation route.","DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"RejectedPackagesReturned":false,"PDFDocumentFileSystemId":null}],"Total":1,"TotalRecords":1,"PageSize":1,"RecordsOnPage":1,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
         </is>
       </c>
     </row>
@@ -11356,13 +11402,13 @@
           <t xml:space="preserve">Find a Template by the Template ID number </t>
         </is>
       </c>
-      <c r="B18" s="255" t="n"/>
-      <c r="C18" s="256" t="n"/>
-      <c r="D18" s="256" t="n"/>
-      <c r="E18" s="256" t="n"/>
-      <c r="F18" s="256" t="n"/>
-      <c r="G18" s="256" t="n"/>
-      <c r="H18" s="256" t="n"/>
+      <c r="B18" s="256" t="n"/>
+      <c r="C18" s="257" t="n"/>
+      <c r="D18" s="257" t="n"/>
+      <c r="E18" s="257" t="n"/>
+      <c r="F18" s="257" t="n"/>
+      <c r="G18" s="257" t="n"/>
+      <c r="H18" s="257" t="n"/>
     </row>
     <row r="19" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A19" s="121" t="inlineStr">
@@ -11370,13 +11416,13 @@
           <t>GET /transfers/v2/templates/{id}/deliveries</t>
         </is>
       </c>
-      <c r="B19" s="257" t="n"/>
-      <c r="C19" s="258" t="n"/>
-      <c r="D19" s="258" t="n"/>
-      <c r="E19" s="258" t="n"/>
-      <c r="F19" s="258" t="n"/>
-      <c r="G19" s="258" t="n"/>
-      <c r="H19" s="258" t="n"/>
+      <c r="B19" s="258" t="n"/>
+      <c r="C19" s="259" t="n"/>
+      <c r="D19" s="259" t="n"/>
+      <c r="E19" s="259" t="n"/>
+      <c r="F19" s="259" t="n"/>
+      <c r="G19" s="259" t="n"/>
+      <c r="H19" s="259" t="n"/>
     </row>
     <row r="20" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A20" s="124" t="n"/>
@@ -11396,22 +11442,22 @@
       </c>
       <c r="B21" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C21" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D21" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>16006</t>
         </is>
       </c>
       <c r="E21" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:18Z</t>
         </is>
       </c>
       <c r="F21" s="247" t="inlineStr">
@@ -11421,12 +11467,12 @@
       </c>
       <c r="G21" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H21" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/templates/outgoing?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H21" s="262" t="inlineStr">
+        <is>
+          <t>[{"Name":"TP Template A 0827-1402 (Updated)","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-5-30301","InvoiceNumber":"INV-A-0827-1402","TransferTypeName":"Affiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-27T15:02:16Z","EstimatedArrivalDateTime":"2026-08-27T18:02:16Z","Transporters":[],"Packages":[],"TransferDestinationId":0}],"TransferTemplateId":16006}]</t>
         </is>
       </c>
     </row>
@@ -11436,13 +11482,13 @@
           <t>Update one of the Templates created in Step 1 by using</t>
         </is>
       </c>
-      <c r="B22" s="255" t="n"/>
-      <c r="C22" s="256" t="n"/>
-      <c r="D22" s="256" t="n"/>
-      <c r="E22" s="256" t="n"/>
-      <c r="F22" s="256" t="n"/>
-      <c r="G22" s="256" t="n"/>
-      <c r="H22" s="256" t="n"/>
+      <c r="B22" s="256" t="n"/>
+      <c r="C22" s="257" t="n"/>
+      <c r="D22" s="257" t="n"/>
+      <c r="E22" s="257" t="n"/>
+      <c r="F22" s="257" t="n"/>
+      <c r="G22" s="257" t="n"/>
+      <c r="H22" s="257" t="n"/>
     </row>
     <row r="23" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A23" s="121" t="inlineStr">
@@ -11450,13 +11496,13 @@
           <t>PUT/transfers/v2/templates/outgoing</t>
         </is>
       </c>
-      <c r="B23" s="257" t="n"/>
-      <c r="C23" s="258" t="n"/>
-      <c r="D23" s="258" t="n"/>
-      <c r="E23" s="258" t="n"/>
-      <c r="F23" s="258" t="n"/>
-      <c r="G23" s="258" t="n"/>
-      <c r="H23" s="258" t="n"/>
+      <c r="B23" s="258" t="n"/>
+      <c r="C23" s="259" t="n"/>
+      <c r="D23" s="259" t="n"/>
+      <c r="E23" s="259" t="n"/>
+      <c r="F23" s="259" t="n"/>
+      <c r="G23" s="259" t="n"/>
+      <c r="H23" s="259" t="n"/>
     </row>
     <row r="24" ht="25.9" customHeight="1">
       <c r="A24" s="136" t="n"/>
@@ -11792,12 +11838,12 @@
       </c>
       <c r="B5" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>401</t>
         </is>
       </c>
       <c r="C5" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D5" s="248" t="inlineStr">
@@ -11807,7 +11853,7 @@
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:18Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
@@ -11817,12 +11863,12 @@
       </c>
       <c r="G5" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H5" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/external/incoming?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H5" s="262" t="inlineStr">
+        <is>
+          <t>[{"ShipperLicenseNumber":"SF-SBX-NY-5-30301","ShipperName":"Evaluation Shipper","ShipperMainPhoneNumber":"555-000-0000","ShipperAddress1":"1 Evaluation Way","ShipperAddress2":null,"ShipperAddressCity":"Albany","ShipperAddressState":"NY","ShipperAddressPostalCode":"12207","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-3-30301","InvoiceNumber":"EXT-A-0827-1402","TransferTypeName":"Beginning Inventory","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-27T15:02:18Z","EstimatedArrivalDateTime":"2026-08-27T18:02:18Z","GrossWeight":null,"GrossUnitOfWeightId":null,"Transporters":[],"Packages":[]}]}]</t>
         </is>
       </c>
     </row>
@@ -11832,13 +11878,13 @@
           <t>Set up an external Incoming transfer</t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
-      <c r="G6" s="256" t="n"/>
-      <c r="H6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
+      <c r="G6" s="257" t="n"/>
+      <c r="H6" s="257" t="n"/>
     </row>
     <row r="7" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A7" s="121" t="inlineStr">
@@ -11846,13 +11892,13 @@
           <t>POST/transfers/v2/external/incoming</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
-      <c r="G7" s="258" t="n"/>
-      <c r="H7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
+      <c r="G7" s="259" t="n"/>
+      <c r="H7" s="259" t="n"/>
     </row>
     <row r="8" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A8" s="122" t="n"/>
@@ -11866,12 +11912,12 @@
       </c>
       <c r="B9" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>401</t>
         </is>
       </c>
       <c r="C9" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D9" s="248" t="inlineStr">
@@ -11881,7 +11927,7 @@
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:18Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
@@ -11891,12 +11937,12 @@
       </c>
       <c r="G9" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H9" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/external/incoming?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H9" s="262" t="inlineStr">
+        <is>
+          <t>[{"ShipperLicenseNumber":"SF-SBX-NY-5-30301","ShipperName":"Evaluation Shipper","ShipperMainPhoneNumber":"555-000-0000","ShipperAddress1":"1 Evaluation Way","ShipperAddress2":null,"ShipperAddressCity":"Albany","ShipperAddressState":"NY","ShipperAddressPostalCode":"12207","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-3-30301","InvoiceNumber":"EXT-B-0827-1402","TransferTypeName":"Beginning Inventory","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-27T15:02:18Z","EstimatedArrivalDateTime":"2026-08-27T18:02:18Z","GrossWeight":null,"GrossUnitOfWeightId":null,"Transporters":[],"Packages":[]}]}]</t>
         </is>
       </c>
     </row>
@@ -11906,13 +11952,13 @@
           <t>Set up an external Incoming transfer</t>
         </is>
       </c>
-      <c r="B10" s="255" t="n"/>
-      <c r="C10" s="256" t="n"/>
-      <c r="D10" s="256" t="n"/>
-      <c r="E10" s="256" t="n"/>
-      <c r="F10" s="256" t="n"/>
-      <c r="G10" s="256" t="n"/>
-      <c r="H10" s="256" t="n"/>
+      <c r="B10" s="256" t="n"/>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+      <c r="F10" s="257" t="n"/>
+      <c r="G10" s="257" t="n"/>
+      <c r="H10" s="257" t="n"/>
     </row>
     <row r="11" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A11" s="121" t="inlineStr">
@@ -11920,13 +11966,13 @@
           <t>POST/transfers/v2/external/incoming</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
-      <c r="C11" s="258" t="n"/>
-      <c r="D11" s="258" t="n"/>
-      <c r="E11" s="258" t="n"/>
-      <c r="F11" s="258" t="n"/>
-      <c r="G11" s="258" t="n"/>
-      <c r="H11" s="258" t="n"/>
+      <c r="B11" s="258" t="n"/>
+      <c r="C11" s="259" t="n"/>
+      <c r="D11" s="259" t="n"/>
+      <c r="E11" s="259" t="n"/>
+      <c r="F11" s="259" t="n"/>
+      <c r="G11" s="259" t="n"/>
+      <c r="H11" s="259" t="n"/>
     </row>
     <row r="12" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A12" s="122" t="n"/>
@@ -11939,12 +11985,12 @@
       </c>
       <c r="B13" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C13" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D13" s="248" t="inlineStr">
@@ -11954,7 +12000,7 @@
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2026-08-27T14:02:18Z</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
@@ -11964,12 +12010,12 @@
       </c>
       <c r="G13" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H13" s="248" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/incoming?lastModifiedStart=2026-08-26T14%3A02%3A18Z&amp;lastModifiedEnd=2026-08-27T14%3A02%3A18Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="H13" s="262" t="inlineStr">
+        <is>
+          <t>{"Data":[],"Total":0,"TotalRecords":0,"PageSize":0,"RecordsOnPage":0,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
         </is>
       </c>
     </row>
@@ -11979,13 +12025,13 @@
           <t xml:space="preserve"> Find the two Transfers created in Step 1a and 1b by using the date parameter search</t>
         </is>
       </c>
-      <c r="B14" s="255" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="256" t="n"/>
-      <c r="G14" s="256" t="n"/>
-      <c r="H14" s="256" t="n"/>
+      <c r="B14" s="256" t="n"/>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+      <c r="F14" s="257" t="n"/>
+      <c r="G14" s="257" t="n"/>
+      <c r="H14" s="257" t="n"/>
     </row>
     <row r="15" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A15" s="121" t="inlineStr">
@@ -11993,13 +12039,13 @@
           <t xml:space="preserve">  GET/transfers/v2/incoming</t>
         </is>
       </c>
-      <c r="B15" s="257" t="n"/>
-      <c r="C15" s="258" t="n"/>
-      <c r="D15" s="258" t="n"/>
-      <c r="E15" s="258" t="n"/>
-      <c r="F15" s="258" t="n"/>
-      <c r="G15" s="258" t="n"/>
-      <c r="H15" s="258" t="n"/>
+      <c r="B15" s="258" t="n"/>
+      <c r="C15" s="259" t="n"/>
+      <c r="D15" s="259" t="n"/>
+      <c r="E15" s="259" t="n"/>
+      <c r="F15" s="259" t="n"/>
+      <c r="G15" s="259" t="n"/>
+      <c r="H15" s="259" t="n"/>
     </row>
     <row r="16" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A16" s="124" t="n"/>
@@ -12059,13 +12105,13 @@
           <t>Update one of the Transfers created in Step 1 by using:</t>
         </is>
       </c>
-      <c r="B18" s="255" t="n"/>
-      <c r="C18" s="256" t="n"/>
-      <c r="D18" s="256" t="n"/>
-      <c r="E18" s="256" t="n"/>
-      <c r="F18" s="256" t="n"/>
-      <c r="G18" s="256" t="n"/>
-      <c r="H18" s="256" t="n"/>
+      <c r="B18" s="256" t="n"/>
+      <c r="C18" s="257" t="n"/>
+      <c r="D18" s="257" t="n"/>
+      <c r="E18" s="257" t="n"/>
+      <c r="F18" s="257" t="n"/>
+      <c r="G18" s="257" t="n"/>
+      <c r="H18" s="257" t="n"/>
     </row>
     <row r="19" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A19" s="121" t="inlineStr">
@@ -12073,13 +12119,13 @@
           <t>PUT/transfers/v2/external/incoming</t>
         </is>
       </c>
-      <c r="B19" s="257" t="n"/>
-      <c r="C19" s="258" t="n"/>
-      <c r="D19" s="258" t="n"/>
-      <c r="E19" s="258" t="n"/>
-      <c r="F19" s="258" t="n"/>
-      <c r="G19" s="258" t="n"/>
-      <c r="H19" s="258" t="n"/>
+      <c r="B19" s="258" t="n"/>
+      <c r="C19" s="259" t="n"/>
+      <c r="D19" s="259" t="n"/>
+      <c r="E19" s="259" t="n"/>
+      <c r="F19" s="259" t="n"/>
+      <c r="G19" s="259" t="n"/>
+      <c r="H19" s="259" t="n"/>
     </row>
     <row r="20" ht="16.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A20" s="124" t="n"/>
@@ -12139,13 +12185,13 @@
           <t>Delete the Transfer not updated in Step 3 by using:</t>
         </is>
       </c>
-      <c r="B22" s="255" t="n"/>
-      <c r="C22" s="256" t="n"/>
-      <c r="D22" s="256" t="n"/>
-      <c r="E22" s="256" t="n"/>
-      <c r="F22" s="256" t="n"/>
-      <c r="G22" s="256" t="n"/>
-      <c r="H22" s="256" t="n"/>
+      <c r="B22" s="256" t="n"/>
+      <c r="C22" s="257" t="n"/>
+      <c r="D22" s="257" t="n"/>
+      <c r="E22" s="257" t="n"/>
+      <c r="F22" s="257" t="n"/>
+      <c r="G22" s="257" t="n"/>
+      <c r="H22" s="257" t="n"/>
     </row>
     <row r="23" ht="19.15" customFormat="1" customHeight="1" s="1" thickBot="1">
       <c r="A23" s="121" t="inlineStr">
@@ -12153,13 +12199,13 @@
           <t>DELETE/transfers/v2/external/incoming/{id}</t>
         </is>
       </c>
-      <c r="B23" s="257" t="n"/>
-      <c r="C23" s="258" t="n"/>
-      <c r="D23" s="258" t="n"/>
-      <c r="E23" s="258" t="n"/>
-      <c r="F23" s="258" t="n"/>
-      <c r="G23" s="258" t="n"/>
-      <c r="H23" s="258" t="n"/>
+      <c r="B23" s="258" t="n"/>
+      <c r="C23" s="259" t="n"/>
+      <c r="D23" s="259" t="n"/>
+      <c r="E23" s="259" t="n"/>
+      <c r="F23" s="259" t="n"/>
+      <c r="G23" s="259" t="n"/>
+      <c r="H23" s="259" t="n"/>
     </row>
     <row r="24" ht="15.6" customFormat="1" customHeight="1" s="1">
       <c r="A24" s="122" t="n"/>
@@ -15754,30 +15800,34 @@
       </c>
       <c r="B5" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C5" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>39528</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Terpenomics Loc 0827-1402</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G5" s="104" t="n"/>
+          <t>https://sandbox-api-ny.metrc.com/locations/v2/?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="G5" s="255" t="inlineStr">
+        <is>
+          <t>[{"Name":"Terpenomics Loc 0827-1402","LocationTypeName":"Default Location Type"}]</t>
+        </is>
+      </c>
       <c r="H5" s="247" t="inlineStr">
         <is>
           <t> </t>
@@ -15795,14 +15845,14 @@
           <t xml:space="preserve">Create a new location using:      </t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
       <c r="G6" s="109" t="n"/>
-      <c r="H6" s="256" t="n"/>
-      <c r="I6" s="256" t="n"/>
+      <c r="H6" s="257" t="n"/>
+      <c r="I6" s="257" t="n"/>
     </row>
     <row r="7" ht="16.15" customHeight="1" thickBot="1">
       <c r="A7" s="110" t="inlineStr">
@@ -15810,14 +15860,14 @@
           <t xml:space="preserve"> POST /locations/v2/</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
       <c r="G7" s="114" t="n"/>
-      <c r="H7" s="258" t="n"/>
-      <c r="I7" s="258" t="n"/>
+      <c r="H7" s="259" t="n"/>
+      <c r="I7" s="259" t="n"/>
     </row>
     <row r="8" ht="16.15" customHeight="1" thickBot="1">
       <c r="A8" s="11" t="n"/>
@@ -15838,30 +15888,34 @@
       </c>
       <c r="B9" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C9" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>39528</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Terpenomics Loc 0827-1402 (Updated)</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G9" s="104" t="n"/>
+          <t>https://sandbox-api-ny.metrc.com/locations/v2/?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="G9" s="255" t="inlineStr">
+        <is>
+          <t>[{"Id":39528,"Name":"Terpenomics Loc 0827-1402 (Updated)","LocationTypeName":"Default Location Type"}]</t>
+        </is>
+      </c>
       <c r="H9" s="247" t="inlineStr">
         <is>
           <t> </t>
@@ -15879,14 +15933,14 @@
           <t>Update the name of the location created in Step 1 using:</t>
         </is>
       </c>
-      <c r="B10" s="255" t="n"/>
-      <c r="C10" s="256" t="n"/>
-      <c r="D10" s="256" t="n"/>
-      <c r="E10" s="256" t="n"/>
-      <c r="F10" s="256" t="n"/>
+      <c r="B10" s="256" t="n"/>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+      <c r="F10" s="257" t="n"/>
       <c r="G10" s="109" t="n"/>
-      <c r="H10" s="256" t="n"/>
-      <c r="I10" s="256" t="n"/>
+      <c r="H10" s="257" t="n"/>
+      <c r="I10" s="257" t="n"/>
     </row>
     <row r="11" ht="16.15" customHeight="1" thickBot="1">
       <c r="A11" s="110" t="inlineStr">
@@ -15894,14 +15948,14 @@
           <t>PUT/locations/v2/</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
-      <c r="C11" s="258" t="n"/>
-      <c r="D11" s="258" t="n"/>
-      <c r="E11" s="258" t="n"/>
-      <c r="F11" s="258" t="n"/>
+      <c r="B11" s="258" t="n"/>
+      <c r="C11" s="259" t="n"/>
+      <c r="D11" s="259" t="n"/>
+      <c r="E11" s="259" t="n"/>
+      <c r="F11" s="259" t="n"/>
       <c r="G11" s="114" t="n"/>
-      <c r="H11" s="258" t="n"/>
-      <c r="I11" s="258" t="n"/>
+      <c r="H11" s="259" t="n"/>
+      <c r="I11" s="259" t="n"/>
     </row>
     <row r="12" ht="16.15" customHeight="1" thickBot="1">
       <c r="A12" s="11" t="n"/>
@@ -15914,30 +15968,34 @@
       </c>
       <c r="B13" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C13" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>39528</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Terpenomics Loc 0827-1402 (Updated)</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G13" s="104" t="n"/>
+          <t>https://sandbox-api-ny.metrc.com/locations/v2/39528?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="G13" s="255" t="inlineStr">
+        <is>
+          <t>{"Id":39528,"Name":"Terpenomics Loc 0827-1402 (Updated)","LocationTypeId":1,"LocationTypeName":"Default Location Type","ForPlantBatches":true,"ForPlants":true,"ForHarvests":true,"ForPackages":true}</t>
+        </is>
+      </c>
       <c r="H13" s="247" t="inlineStr">
         <is>
           <t> </t>
@@ -15955,14 +16013,14 @@
           <t xml:space="preserve">View the location Created and Updated in Step 1 &amp; 2 by the ID number : </t>
         </is>
       </c>
-      <c r="B14" s="255" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="256" t="n"/>
+      <c r="B14" s="256" t="n"/>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+      <c r="F14" s="257" t="n"/>
       <c r="G14" s="109" t="n"/>
-      <c r="H14" s="256" t="n"/>
-      <c r="I14" s="256" t="n"/>
+      <c r="H14" s="257" t="n"/>
+      <c r="I14" s="257" t="n"/>
     </row>
     <row r="15" ht="16.15" customHeight="1" thickBot="1">
       <c r="A15" s="110" t="inlineStr">
@@ -15970,14 +16028,14 @@
           <t>GET /locations/v2/{id}</t>
         </is>
       </c>
-      <c r="B15" s="257" t="n"/>
-      <c r="C15" s="258" t="n"/>
-      <c r="D15" s="258" t="n"/>
-      <c r="E15" s="258" t="n"/>
-      <c r="F15" s="258" t="n"/>
+      <c r="B15" s="258" t="n"/>
+      <c r="C15" s="259" t="n"/>
+      <c r="D15" s="259" t="n"/>
+      <c r="E15" s="259" t="n"/>
+      <c r="F15" s="259" t="n"/>
       <c r="G15" s="114" t="n"/>
-      <c r="H15" s="258" t="n"/>
-      <c r="I15" s="258" t="n"/>
+      <c r="H15" s="259" t="n"/>
+      <c r="I15" s="259" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
@@ -16218,30 +16276,34 @@
       </c>
       <c r="B5" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C5" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>62112</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Terpenomics Strain 0827-1402</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G5" s="104" t="n"/>
+          <t>https://sandbox-api-ny.metrc.com/strains/v2/?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="G5" s="255" t="inlineStr">
+        <is>
+          <t>[{"Name":"Terpenomics Strain 0827-1402","TestingStatus":"None","ThcLevel":0.1865,"CbdLevel":0.1075,"IndicaPercentage":25.0,"SativaPercentage":75.0}]</t>
+        </is>
+      </c>
       <c r="H5" s="247" t="inlineStr">
         <is>
           <t> </t>
@@ -16259,14 +16321,14 @@
           <t xml:space="preserve">Create a new Strain using:      </t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
       <c r="G6" s="109" t="n"/>
-      <c r="H6" s="256" t="n"/>
-      <c r="I6" s="256" t="n"/>
+      <c r="H6" s="257" t="n"/>
+      <c r="I6" s="257" t="n"/>
     </row>
     <row r="7" ht="16.15" customHeight="1" thickBot="1">
       <c r="A7" s="110" t="inlineStr">
@@ -16274,14 +16336,14 @@
           <t xml:space="preserve"> POST/strains/v2/</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
       <c r="G7" s="114" t="n"/>
-      <c r="H7" s="258" t="n"/>
-      <c r="I7" s="258" t="n"/>
+      <c r="H7" s="259" t="n"/>
+      <c r="I7" s="259" t="n"/>
     </row>
     <row r="8" ht="16.15" customHeight="1" thickBot="1">
       <c r="A8" s="11" t="n"/>
@@ -16302,30 +16364,34 @@
       </c>
       <c r="B9" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C9" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>62112</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Terpenomics Strain 0827-1402</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G9" s="104" t="n"/>
+          <t>https://sandbox-api-ny.metrc.com/strains/v2/?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="G9" s="255" t="inlineStr">
+        <is>
+          <t>[{"Id":62112,"Name":"Terpenomics Strain 0827-1402","TestingStatus":"None","ThcLevel":0.1865,"CbdLevel":0.1075,"IndicaPercentage":60.0,"SativaPercentage":40.0}]</t>
+        </is>
+      </c>
       <c r="H9" s="247" t="inlineStr">
         <is>
           <t> </t>
@@ -16343,14 +16409,14 @@
           <t xml:space="preserve"> Update the Strain by changing the Indica and Sativa Percentage  </t>
         </is>
       </c>
-      <c r="B10" s="255" t="n"/>
-      <c r="C10" s="256" t="n"/>
-      <c r="D10" s="256" t="n"/>
-      <c r="E10" s="256" t="n"/>
-      <c r="F10" s="256" t="n"/>
+      <c r="B10" s="256" t="n"/>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+      <c r="F10" s="257" t="n"/>
       <c r="G10" s="109" t="n"/>
-      <c r="H10" s="256" t="n"/>
-      <c r="I10" s="256" t="n"/>
+      <c r="H10" s="257" t="n"/>
+      <c r="I10" s="257" t="n"/>
     </row>
     <row r="11" ht="16.15" customHeight="1" thickBot="1">
       <c r="A11" s="110" t="inlineStr">
@@ -16358,14 +16424,14 @@
           <t>PUT/strains/v2/</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
-      <c r="C11" s="258" t="n"/>
-      <c r="D11" s="258" t="n"/>
-      <c r="E11" s="258" t="n"/>
-      <c r="F11" s="258" t="n"/>
+      <c r="B11" s="258" t="n"/>
+      <c r="C11" s="259" t="n"/>
+      <c r="D11" s="259" t="n"/>
+      <c r="E11" s="259" t="n"/>
+      <c r="F11" s="259" t="n"/>
       <c r="G11" s="114" t="n"/>
-      <c r="H11" s="258" t="n"/>
-      <c r="I11" s="258" t="n"/>
+      <c r="H11" s="259" t="n"/>
+      <c r="I11" s="259" t="n"/>
     </row>
     <row r="12" ht="16.15" customHeight="1" thickBot="1">
       <c r="A12" s="11" t="n"/>
@@ -16378,30 +16444,34 @@
       </c>
       <c r="B13" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C13" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>62112</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Terpenomics Strain 0827-1402</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G13" s="104" t="n"/>
+          <t>https://sandbox-api-ny.metrc.com/strains/v2/62112?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="G13" s="255" t="inlineStr">
+        <is>
+          <t>{"Id":62112,"Name":"Terpenomics Strain 0827-1402","TestingStatus":"None","ThcLevel":0.1865,"CbdLevel":0.1075,"IndicaPercentage":60.0,"SativaPercentage":40.0,"IsUsed":false,"Genetics":"60% Indica / 40% Sativa"}</t>
+        </is>
+      </c>
       <c r="H13" s="247" t="inlineStr">
         <is>
           <t> </t>
@@ -16419,14 +16489,14 @@
           <t xml:space="preserve">View the Strain Created and Updated in Step 1 &amp; 2 by the ID number : </t>
         </is>
       </c>
-      <c r="B14" s="255" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="256" t="n"/>
+      <c r="B14" s="256" t="n"/>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+      <c r="F14" s="257" t="n"/>
       <c r="G14" s="109" t="n"/>
-      <c r="H14" s="256" t="n"/>
-      <c r="I14" s="256" t="n"/>
+      <c r="H14" s="257" t="n"/>
+      <c r="I14" s="257" t="n"/>
     </row>
     <row r="15" ht="16.15" customHeight="1" thickBot="1">
       <c r="A15" s="110" t="inlineStr">
@@ -16434,14 +16504,14 @@
           <t>GET/strains/v2/{id}</t>
         </is>
       </c>
-      <c r="B15" s="257" t="n"/>
-      <c r="C15" s="258" t="n"/>
-      <c r="D15" s="258" t="n"/>
-      <c r="E15" s="258" t="n"/>
-      <c r="F15" s="258" t="n"/>
+      <c r="B15" s="258" t="n"/>
+      <c r="C15" s="259" t="n"/>
+      <c r="D15" s="259" t="n"/>
+      <c r="E15" s="259" t="n"/>
+      <c r="F15" s="259" t="n"/>
       <c r="G15" s="114" t="n"/>
-      <c r="H15" s="258" t="n"/>
-      <c r="I15" s="258" t="n"/>
+      <c r="H15" s="259" t="n"/>
+      <c r="I15" s="259" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
@@ -16682,30 +16752,34 @@
       </c>
       <c r="B5" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C5" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>293817</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Terpenomics Item 0827-1402</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G5" s="104" t="n"/>
+          <t>https://sandbox-api-ny.metrc.com/items/v2/?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="G5" s="255" t="inlineStr">
+        <is>
+          <t>[{"ItemCategory":"Bud/Flower - Bulk","Name":"Terpenomics Item 0827-1402","UnitOfMeasure":"Grams","Strain":"Terpenomics Strain 0827-1402"}]</t>
+        </is>
+      </c>
       <c r="H5" s="247" t="inlineStr">
         <is>
           <t> </t>
@@ -16723,14 +16797,14 @@
           <t xml:space="preserve">Create a new Item using:      </t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
       <c r="G6" s="109" t="n"/>
-      <c r="H6" s="256" t="n"/>
-      <c r="I6" s="256" t="n"/>
+      <c r="H6" s="257" t="n"/>
+      <c r="I6" s="257" t="n"/>
     </row>
     <row r="7" ht="16.15" customHeight="1" thickBot="1">
       <c r="A7" s="110" t="inlineStr">
@@ -16738,14 +16812,14 @@
           <t xml:space="preserve"> POST/Items/v2/</t>
         </is>
       </c>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
       <c r="G7" s="114" t="n"/>
-      <c r="H7" s="258" t="n"/>
-      <c r="I7" s="258" t="n"/>
+      <c r="H7" s="259" t="n"/>
+      <c r="I7" s="259" t="n"/>
     </row>
     <row r="8" ht="16.15" customHeight="1" thickBot="1">
       <c r="A8" s="11" t="n"/>
@@ -16766,30 +16840,34 @@
       </c>
       <c r="B9" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C9" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>293817</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Terpenomics Item 0827-1402</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G9" s="104" t="n"/>
+          <t>https://sandbox-api-ny.metrc.com/items/v2/?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="G9" s="255" t="inlineStr">
+        <is>
+          <t>[{"ItemCategory":"Bud/Flower - Bulk","Name":"Terpenomics Item 0827-1402","UnitOfMeasure":"Kilograms","Strain":"Terpenomics Strain 0827-1402","Id":293817}]</t>
+        </is>
+      </c>
       <c r="H9" s="247" t="inlineStr">
         <is>
           <t> </t>
@@ -16807,14 +16885,14 @@
           <t xml:space="preserve"> Using the Item created in Step 1 Change the Unit of Measure Type using:      </t>
         </is>
       </c>
-      <c r="B10" s="255" t="n"/>
-      <c r="C10" s="256" t="n"/>
-      <c r="D10" s="256" t="n"/>
-      <c r="E10" s="256" t="n"/>
-      <c r="F10" s="256" t="n"/>
+      <c r="B10" s="256" t="n"/>
+      <c r="C10" s="257" t="n"/>
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+      <c r="F10" s="257" t="n"/>
       <c r="G10" s="109" t="n"/>
-      <c r="H10" s="256" t="n"/>
-      <c r="I10" s="256" t="n"/>
+      <c r="H10" s="257" t="n"/>
+      <c r="I10" s="257" t="n"/>
     </row>
     <row r="11" ht="16.15" customHeight="1" thickBot="1">
       <c r="A11" s="110" t="inlineStr">
@@ -16822,14 +16900,14 @@
           <t>PUT/Items/v2/</t>
         </is>
       </c>
-      <c r="B11" s="257" t="n"/>
-      <c r="C11" s="258" t="n"/>
-      <c r="D11" s="258" t="n"/>
-      <c r="E11" s="258" t="n"/>
-      <c r="F11" s="258" t="n"/>
+      <c r="B11" s="258" t="n"/>
+      <c r="C11" s="259" t="n"/>
+      <c r="D11" s="259" t="n"/>
+      <c r="E11" s="259" t="n"/>
+      <c r="F11" s="259" t="n"/>
       <c r="G11" s="114" t="n"/>
-      <c r="H11" s="258" t="n"/>
-      <c r="I11" s="258" t="n"/>
+      <c r="H11" s="259" t="n"/>
+      <c r="I11" s="259" t="n"/>
     </row>
     <row r="12" ht="16.15" customHeight="1" thickBot="1">
       <c r="A12" s="11" t="n"/>
@@ -16842,30 +16920,34 @@
       </c>
       <c r="B13" s="249" t="inlineStr">
         <is>
-          <t> </t>
+          <t>200</t>
         </is>
       </c>
       <c r="C13" s="248" t="inlineStr">
         <is>
-          <t> </t>
+          <t>SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>  </t>
+          <t>293817</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t> </t>
+          <t>Terpenomics Item 0827-1402</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G13" s="104" t="n"/>
+          <t>https://sandbox-api-ny.metrc.com/items/v2/293817?licenseNumber=SF-SBX-NY-3-30301</t>
+        </is>
+      </c>
+      <c r="G13" s="255" t="inlineStr">
+        <is>
+          <t>{"Id":293817,"Name":"Terpenomics Item 0827-1402","GlobalProductName":null,"GlobalProductNumber":null,"ProductCategoryName":"Bud/Flower - Bulk","ProductCategoryType":"Buds","IsExpirationDateRequired":false,"HasExpirationDate":false,"IsSellByDateRequired":false,"HasSellByDate":false,"IsUseByDateRequired":false,"HasUseByDate":false,"QuantityType":"WeightBased","DefaultLabTestingState":"NotSubmitted","UnitOfMeasureName":"Kilograms","ApprovalStatus":"Approved","ApprovalStatusDateTime":"2026-08-27T14:02:08+00:00","StrainId":62112,"StrainName":"Terpenomics Strain 0827-1402","ItemBrandId":0,"ItemBrandName":null,"AdministrationMethod":"","UnitCbdPercent":null,"UnitCbdContent":null,"UnitCbdContentUnitOfMeasureName":null,"UnitCbdContentDose":null,"UnitCbdContentDoseUnitOfMeasureName":null,"UnitCbdAPercent":null,"UnitCbdAContent":null,"UnitCbdAContentUnitOfMeasureName":null,"UnitCbdAContentDose":null,"UnitCbdAContentDoseUnitOfMeasureName":null,"UnitThcAPercent":null,"UnitThcAContent":null,"UnitThcAContentUnitOfMeasureName":null,"UnitThcAContentDose":null,"UnitThcAContentDoseUnitOfMeasureId":null,"UnitThcAContentDoseUnitOfMeasureName":null,"UnitThcPercent":null,"UnitThcContent":null,"UnitThcContentUnitOfMeasureName":null,"UnitThcContentDose":null,"UnitThcContentDoseUnitOfMeasureId":null,"UnitThcContentDoseUnitOfMeasureName":null,"UnitVolume":null,"UnitVolumeUnitOfMeasureName":null,"UnitWeight":null,"UnitWeightUnitOfMeasureName":null,"ServingSize":"","NumberOfDoses":null,"UnitQuantity":null,"UnitQuantityUnitOfMeasureName":null,"PublicIngredients":"","Description":"","Allergens":"","ProductImages":[],"ProductPhotoDescription":"","LabelImages":[],"LabelPhotoDescription":"","PackagingImages":[],"PackagingPhotoDescription":"","ProductPDFDocuments":[],"IsUsed":false,"CreatedDateTime":"2026-08-27T14:02:07.54+00:00","LabTestBatchNames":[],"ProcessingJobCategoryName":null,"ProcessingJobTypeName":null,"ProductBrandName":null}</t>
+        </is>
+      </c>
       <c r="H13" s="247" t="inlineStr">
         <is>
           <t> </t>
@@ -16883,14 +16965,14 @@
           <t xml:space="preserve">View the Item Created and Updated in Step 1 &amp; 2 by the ID number : </t>
         </is>
       </c>
-      <c r="B14" s="255" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="256" t="n"/>
+      <c r="B14" s="256" t="n"/>
+      <c r="C14" s="257" t="n"/>
+      <c r="D14" s="257" t="n"/>
+      <c r="E14" s="257" t="n"/>
+      <c r="F14" s="257" t="n"/>
       <c r="G14" s="109" t="n"/>
-      <c r="H14" s="256" t="n"/>
-      <c r="I14" s="256" t="n"/>
+      <c r="H14" s="257" t="n"/>
+      <c r="I14" s="257" t="n"/>
     </row>
     <row r="15" ht="16.15" customHeight="1" thickBot="1">
       <c r="A15" s="110" t="inlineStr">
@@ -16898,14 +16980,14 @@
           <t>GET/Items/v2/{id}</t>
         </is>
       </c>
-      <c r="B15" s="257" t="n"/>
-      <c r="C15" s="258" t="n"/>
-      <c r="D15" s="258" t="n"/>
-      <c r="E15" s="258" t="n"/>
-      <c r="F15" s="258" t="n"/>
+      <c r="B15" s="258" t="n"/>
+      <c r="C15" s="259" t="n"/>
+      <c r="D15" s="259" t="n"/>
+      <c r="E15" s="259" t="n"/>
+      <c r="F15" s="259" t="n"/>
       <c r="G15" s="114" t="n"/>
-      <c r="H15" s="258" t="n"/>
-      <c r="I15" s="258" t="n"/>
+      <c r="H15" s="259" t="n"/>
+      <c r="I15" s="259" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
@@ -17297,23 +17379,23 @@
           <t xml:space="preserve"> Create a Immature Plant Batch Containing a quantity of 6 Plants. See the Tab Closed Loop Environment for how to create the Plant batch and document here how it was done.</t>
         </is>
       </c>
-      <c r="B6" s="255" t="n"/>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="256" t="n"/>
+      <c r="B6" s="256" t="n"/>
+      <c r="C6" s="257" t="n"/>
+      <c r="D6" s="257" t="n"/>
+      <c r="E6" s="257" t="n"/>
+      <c r="F6" s="257" t="n"/>
       <c r="G6" s="240" t="n"/>
-      <c r="H6" s="256" t="n"/>
+      <c r="H6" s="257" t="n"/>
     </row>
     <row r="7" ht="21.95" customFormat="1" customHeight="1" s="1" thickBot="1">
-      <c r="A7" s="259" t="n"/>
-      <c r="B7" s="257" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-      <c r="F7" s="258" t="n"/>
+      <c r="A7" s="260" t="n"/>
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="259" t="n"/>
+      <c r="D7" s="259" t="n"/>
+      <c r="E7" s="259" t="n"/>
+      <c r="F7" s="259" t="n"/>
       <c r="G7" s="241" t="n"/>
-      <c r="H7" s="258" t="n"/>
+      <c r="H7" s="259" t="n"/>
     </row>
     <row r="8" ht="12" customFormat="1" customHeight="1" s="33">
       <c r="A8" s="133" t="n"/>
@@ -17372,13 +17454,13 @@
           <t xml:space="preserve">Create a package with 3 clones from the remaining Original Plant batch. This action will not decrease the Plant batch quantity.                            </t>
         </is>
       </c>
-      <c r="B11" s="255" t="n"/>
-      <c r="C11" s="256" t="n"/>
-      <c r="D11" s="256" t="n"/>
-      <c r="E11" s="256" t="n"/>
-      <c r="F11" s="256" t="n"/>
+      <c r="B11" s="256" t="n"/>
+      <c r="C11" s="257" t="n"/>
+      <c r="D11" s="257" t="n"/>
+      <c r="E11" s="257" t="n"/>
+      <c r="F11" s="257" t="n"/>
       <c r="G11" s="109" t="n"/>
-      <c r="H11" s="256" t="n"/>
+      <c r="H11" s="257" t="n"/>
     </row>
     <row r="12" ht="21.95" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A12" s="121" t="inlineStr">
@@ -17386,13 +17468,13 @@
           <t>POST/plantbatches/v2/packages/frommotherplant</t>
         </is>
       </c>
-      <c r="B12" s="257" t="n"/>
-      <c r="C12" s="258" t="n"/>
-      <c r="D12" s="258" t="n"/>
-      <c r="E12" s="258" t="n"/>
-      <c r="F12" s="258" t="n"/>
+      <c r="B12" s="258" t="n"/>
+      <c r="C12" s="259" t="n"/>
+      <c r="D12" s="259" t="n"/>
+      <c r="E12" s="259" t="n"/>
+      <c r="F12" s="259" t="n"/>
       <c r="G12" s="114" t="n"/>
-      <c r="H12" s="258" t="n"/>
+      <c r="H12" s="259" t="n"/>
     </row>
     <row r="13" ht="10.9" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A13" s="124" t="n"/>
@@ -17448,13 +17530,13 @@
           <t xml:space="preserve">Create a package containing 3 clones from one of the original Plant Batches above. This action will decrease the plant batch quantity                                                                                </t>
         </is>
       </c>
-      <c r="B15" s="255" t="n"/>
-      <c r="C15" s="256" t="n"/>
-      <c r="D15" s="256" t="n"/>
-      <c r="E15" s="256" t="n"/>
-      <c r="F15" s="256" t="n"/>
+      <c r="B15" s="256" t="n"/>
+      <c r="C15" s="257" t="n"/>
+      <c r="D15" s="257" t="n"/>
+      <c r="E15" s="257" t="n"/>
+      <c r="F15" s="257" t="n"/>
       <c r="G15" s="109" t="n"/>
-      <c r="H15" s="256" t="n"/>
+      <c r="H15" s="257" t="n"/>
     </row>
     <row r="16" ht="21.95" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A16" s="121" t="inlineStr">
@@ -17462,13 +17544,13 @@
           <t>POST /plantbatches/v2/packages</t>
         </is>
       </c>
-      <c r="B16" s="257" t="n"/>
-      <c r="C16" s="258" t="n"/>
-      <c r="D16" s="258" t="n"/>
-      <c r="E16" s="258" t="n"/>
-      <c r="F16" s="258" t="n"/>
+      <c r="B16" s="258" t="n"/>
+      <c r="C16" s="259" t="n"/>
+      <c r="D16" s="259" t="n"/>
+      <c r="E16" s="259" t="n"/>
+      <c r="F16" s="259" t="n"/>
       <c r="G16" s="114" t="n"/>
-      <c r="H16" s="258" t="n"/>
+      <c r="H16" s="259" t="n"/>
     </row>
     <row r="17" ht="12" customHeight="1" thickBot="1">
       <c r="A17" s="248" t="n"/>
@@ -17556,13 +17638,13 @@
           <t xml:space="preserve">Change the growth phase of 2 of the plants split in Step 2 to the Flowering Stage using:         </t>
         </is>
       </c>
-      <c r="B19" s="255" t="n"/>
-      <c r="C19" s="256" t="n"/>
-      <c r="D19" s="256" t="n"/>
-      <c r="E19" s="256" t="n"/>
-      <c r="F19" s="256" t="n"/>
+      <c r="B19" s="256" t="n"/>
+      <c r="C19" s="257" t="n"/>
+      <c r="D19" s="257" t="n"/>
+      <c r="E19" s="257" t="n"/>
+      <c r="F19" s="257" t="n"/>
       <c r="G19" s="109" t="n"/>
-      <c r="H19" s="256" t="n"/>
+      <c r="H19" s="257" t="n"/>
     </row>
     <row r="20" ht="21.95" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A20" s="121" t="inlineStr">
@@ -17570,13 +17652,13 @@
           <t>POST/plantbatches/v2/growthphase</t>
         </is>
       </c>
-      <c r="B20" s="257" t="n"/>
-      <c r="C20" s="258" t="n"/>
-      <c r="D20" s="258" t="n"/>
-      <c r="E20" s="258" t="n"/>
-      <c r="F20" s="258" t="n"/>
+      <c r="B20" s="258" t="n"/>
+      <c r="C20" s="259" t="n"/>
+      <c r="D20" s="259" t="n"/>
+      <c r="E20" s="259" t="n"/>
+      <c r="F20" s="259" t="n"/>
       <c r="G20" s="114" t="n"/>
-      <c r="H20" s="258" t="n"/>
+      <c r="H20" s="259" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" thickBot="1">
       <c r="A21" s="1" t="inlineStr">
@@ -17640,13 +17722,13 @@
           <t xml:space="preserve">  Destroy 1 of the plants in the batch that was split using:</t>
         </is>
       </c>
-      <c r="B23" s="255" t="n"/>
-      <c r="C23" s="256" t="n"/>
-      <c r="D23" s="256" t="n"/>
-      <c r="E23" s="256" t="n"/>
-      <c r="F23" s="256" t="n"/>
+      <c r="B23" s="256" t="n"/>
+      <c r="C23" s="257" t="n"/>
+      <c r="D23" s="257" t="n"/>
+      <c r="E23" s="257" t="n"/>
+      <c r="F23" s="257" t="n"/>
       <c r="G23" s="109" t="n"/>
-      <c r="H23" s="256" t="n"/>
+      <c r="H23" s="257" t="n"/>
     </row>
     <row r="24" ht="21.95" customFormat="1" customHeight="1" s="33" thickBot="1">
       <c r="A24" s="121" t="inlineStr">
@@ -17654,13 +17736,13 @@
           <t xml:space="preserve"> DELETE/plantbatches/v2/</t>
         </is>
       </c>
-      <c r="B24" s="257" t="n"/>
-      <c r="C24" s="258" t="n"/>
-      <c r="D24" s="258" t="n"/>
-      <c r="E24" s="258" t="n"/>
-      <c r="F24" s="258" t="n"/>
+      <c r="B24" s="258" t="n"/>
+      <c r="C24" s="259" t="n"/>
+      <c r="D24" s="259" t="n"/>
+      <c r="E24" s="259" t="n"/>
+      <c r="F24" s="259" t="n"/>
       <c r="G24" s="114" t="n"/>
-      <c r="H24" s="258" t="n"/>
+      <c r="H24" s="259" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>

--- a/evidence/metrc/Evaluation_NY_completed.xlsx
+++ b/evidence/metrc/Evaluation_NY_completed.xlsx
@@ -11145,12 +11145,12 @@
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>15910</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:18Z</t>
+          <t>2026-08-29T13:32:25Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="H5" s="262" t="inlineStr">
         <is>
-          <t>[{"Name":"TP Template A 0827-1402","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-5-30301","InvoiceNumber":"INV-A-0827-1402","TransferTypeName":"Affiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-27T15:02:16Z","EstimatedArrivalDateTime":"2026-08-27T18:02:16Z","Transporters":[],"Packages":[]}]}]</t>
+          <t>[{"Name":"TP Template A 0829-1332","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-6-13402","InvoiceNumber":"INV-A-0829-1332","TransferTypeName":"Unaffiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T14:32:24Z","EstimatedArrivalDateTime":"2026-08-29T17:32:24Z","Transporters":[],"Packages":[]}]}]</t>
         </is>
       </c>
     </row>
@@ -11219,12 +11219,12 @@
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>15911</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:18Z</t>
+          <t>2026-08-29T13:32:25Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="H9" s="262" t="inlineStr">
         <is>
-          <t>[{"Name":"TP Template B 0827-1402","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-5-30301","InvoiceNumber":"INV-B-0827-1402","TransferTypeName":"Affiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-27T15:02:16Z","EstimatedArrivalDateTime":"2026-08-27T18:02:16Z","Transporters":[],"Packages":[]}]}]</t>
+          <t>[{"Name":"TP Template B 0829-1332","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-6-13402","InvoiceNumber":"INV-B-0829-1332","TransferTypeName":"Unaffiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T14:32:24Z","EstimatedArrivalDateTime":"2026-08-29T17:32:24Z","Transporters":[],"Packages":[]}]}]</t>
         </is>
       </c>
     </row>
@@ -11292,12 +11292,12 @@
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>16006, 16007</t>
+          <t>15910, 15911</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:18+00:00</t>
+          <t>2026-08-29T13:32:25+00:00</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="G13" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/transfers/v2/templates/outgoing?lastModifiedStart=2026-08-26T14%3A02%3A18Z&amp;lastModifiedEnd=2026-08-27T14%3A02%3A18Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/templates/outgoing?lastModifiedStart=2026-08-28T13%3A32%3A25Z&amp;lastModifiedEnd=2026-08-29T13%3A32%3A25Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="H13" s="262" t="inlineStr">
         <is>
-          <t>{"Data":[{"Id":16006,"ManifestNumber":"T-0000016006","InvoiceNumber":"INV-A-0827-1402","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0827-1402","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T14:02:18+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T14:02:18+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":16007,"ManifestNumber":"T-0000016007","InvoiceNumber":"INV-B-0827-1402","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0827-1402","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T14:02:18+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T14:02:18+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15909,"ManifestNumber":"T-0000015909","InvoiceNumber":"INV-A-0827-1400","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0827-1400 (Updated)","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T14:00:28+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T14:00:28+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":16005,"ManifestNumber":"T-0000016005","InvoiceNumber":"INV-B-0827-1400","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0827-1400","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T14:00:28+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T14:00:28+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15907,"ManifestNumber":"T-0000015907","InvoiceNumber":"INV-A-0827-1359","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0827-1359 (Updated)","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:59:46+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:59:46+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15908,"ManifestNumber":"T-0000015908","InvoiceNumber":"INV-B-0827-1359","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0827-1359","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:59:46+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:59:46+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15906,"ManifestNumber":"T-0000015906","InvoiceNumber":"INV-B-0827-1358","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0827-1358","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:59:06+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:59:06+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":16004,"ManifestNumber":"T-0000016004","InvoiceNumber":"INV-A-0827-1358","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0827-1358 (Updated)","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:59:06+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:59:07+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15905,"ManifestNumber":"T-0000015905","InvoiceNumber":"INV-B-0827-1357","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0827-1357","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:57:53+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:57:53+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":16003,"ManifestNumber":"T-0000016003","InvoiceNumber":"INV-A-0827-1357","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0827-1357 (Updated)","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:57:53+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:57:53+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15903,"ManifestNumber":"T-0000015903","InvoiceNumber":"INV-A-0827-1355","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0827-1355 (Updated)","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:56:00+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:56:01+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15904,"ManifestNumber":"T-0000015904","InvoiceNumber":"INV-B-0827-1355","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0827-1355","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:56:00+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:56:00+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15902,"ManifestNumber":"T-0000015902","InvoiceNumber":"INV-A-0827-1353","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0827-1353 (Updated)","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:54:08+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:54:08+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":16002,"ManifestNumber":"T-0000016002","InvoiceNumber":"INV-B-0827-1353","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0827-1353","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-27T13:54:08+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-27T13:54:08+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null}],"Total":14,"TotalRecords":14,"PageSize":14,"RecordsOnPage":14,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
+          <t>{"Data":[{"Id":15910,"ManifestNumber":"T-0000015910","InvoiceNumber":"INV-A-0829-1332","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0829-1332","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-29T13:32:25+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-29T13:32:25+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15911,"ManifestNumber":"T-0000015911","InvoiceNumber":"INV-B-0829-1332","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0829-1332","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-29T13:32:25+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-29T13:32:25+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null}],"Total":2,"TotalRecords":2,"PageSize":2,"RecordsOnPage":2,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
         </is>
       </c>
     </row>
@@ -11372,12 +11372,12 @@
       </c>
       <c r="D17" s="248" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>15910</t>
         </is>
       </c>
       <c r="E17" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:18Z</t>
+          <t>2026-08-29T13:32:25Z</t>
         </is>
       </c>
       <c r="F17" s="247" t="inlineStr">
@@ -11387,12 +11387,12 @@
       </c>
       <c r="G17" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/transfers/v2/templates/outgoing/16006/deliveries</t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/templates/outgoing/15910/deliveries</t>
         </is>
       </c>
       <c r="H17" s="262" t="inlineStr">
         <is>
-          <t>{"Data":[{"Id":16511,"ManifestNumber":null,"DeliveryNumber":0,"RecipientFacilityLicenseNumber":"SF-SBX-NY-5-30301","RecipientFacilityName":"Sandbox AU Dispensary","ShipmentTypeName":"Affiliated Transfer","ShipmentTransactionType":"Standard","InvoiceNumber":"INV-A-0827-1402","PaymentTermDays":null,"PaymentDueDate":null,"EstimatedDepartureDateTime":"2026-08-27T15:02:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"2026-08-27T18:02:00.000","ActualArrivalDateTime":null,"GrossWeight":null,"GrossUnitOfWeightId":null,"GrossUnitOfWeightName":null,"PlannedRoute":"Evaluation route.","DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"RejectedPackagesReturned":false,"PDFDocumentFileSystemId":null}],"Total":1,"TotalRecords":1,"PageSize":1,"RecordsOnPage":1,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
+          <t>{"Data":[{"Id":16412,"ManifestNumber":null,"DeliveryNumber":0,"RecipientFacilityLicenseNumber":"SF-SBX-NY-6-13402","RecipientFacilityName":"Sandbox AU Distributor","ShipmentTypeName":"Unaffiliated Transfer","ShipmentTransactionType":"Wholesale","InvoiceNumber":"INV-A-0829-1332","PaymentTermDays":null,"PaymentDueDate":null,"EstimatedDepartureDateTime":"2026-08-29T14:32:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"2026-08-29T17:32:00.000","ActualArrivalDateTime":null,"GrossWeight":null,"GrossUnitOfWeightId":null,"GrossUnitOfWeightName":null,"PlannedRoute":"Evaluation route.","DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"RejectedPackagesReturned":false,"PDFDocumentFileSystemId":null}],"Total":1,"TotalRecords":1,"PageSize":1,"RecordsOnPage":1,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
         </is>
       </c>
     </row>
@@ -11452,12 +11452,12 @@
       </c>
       <c r="D21" s="248" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>15910</t>
         </is>
       </c>
       <c r="E21" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:18Z</t>
+          <t>2026-08-29T13:32:26Z</t>
         </is>
       </c>
       <c r="F21" s="247" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H21" s="262" t="inlineStr">
         <is>
-          <t>[{"Name":"TP Template A 0827-1402 (Updated)","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-5-30301","InvoiceNumber":"INV-A-0827-1402","TransferTypeName":"Affiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-27T15:02:16Z","EstimatedArrivalDateTime":"2026-08-27T18:02:16Z","Transporters":[],"Packages":[],"TransferDestinationId":0}],"TransferTemplateId":16006}]</t>
+          <t>[{"Name":"TP Template A 0829-1332 (Updated)","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-6-13402","InvoiceNumber":"INV-A-0829-1332","TransferTypeName":"Unaffiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T14:32:24Z","EstimatedArrivalDateTime":"2026-08-29T17:32:24Z","Transporters":[],"Packages":[],"TransferDestinationId":0}],"TransferTemplateId":15910}]</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:18Z</t>
+          <t>2026-08-29T13:32:26Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="H5" s="262" t="inlineStr">
         <is>
-          <t>[{"ShipperLicenseNumber":"SF-SBX-NY-5-30301","ShipperName":"Evaluation Shipper","ShipperMainPhoneNumber":"555-000-0000","ShipperAddress1":"1 Evaluation Way","ShipperAddress2":null,"ShipperAddressCity":"Albany","ShipperAddressState":"NY","ShipperAddressPostalCode":"12207","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-3-30301","InvoiceNumber":"EXT-A-0827-1402","TransferTypeName":"Beginning Inventory","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-27T15:02:18Z","EstimatedArrivalDateTime":"2026-08-27T18:02:18Z","GrossWeight":null,"GrossUnitOfWeightId":null,"Transporters":[],"Packages":[]}]}]</t>
+          <t>[{"ShipperLicenseNumber":"SF-SBX-NY-6-13402","ShipperName":"Evaluation Shipper","ShipperMainPhoneNumber":"555-000-0000","ShipperAddress1":"1 Evaluation Way","ShipperAddress2":null,"ShipperAddressCity":"Albany","ShipperAddressState":"NY","ShipperAddressPostalCode":"12207","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-3-30301","InvoiceNumber":"EXT-A-0829-1332","TransferTypeName":"Beginning Inventory","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T14:32:26Z","EstimatedArrivalDateTime":"2026-08-29T17:32:26Z","GrossWeight":null,"GrossUnitOfWeightId":null,"Transporters":[],"Packages":[]}]}]</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:18Z</t>
+          <t>2026-08-29T13:32:26Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="H9" s="262" t="inlineStr">
         <is>
-          <t>[{"ShipperLicenseNumber":"SF-SBX-NY-5-30301","ShipperName":"Evaluation Shipper","ShipperMainPhoneNumber":"555-000-0000","ShipperAddress1":"1 Evaluation Way","ShipperAddress2":null,"ShipperAddressCity":"Albany","ShipperAddressState":"NY","ShipperAddressPostalCode":"12207","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-3-30301","InvoiceNumber":"EXT-B-0827-1402","TransferTypeName":"Beginning Inventory","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-27T15:02:18Z","EstimatedArrivalDateTime":"2026-08-27T18:02:18Z","GrossWeight":null,"GrossUnitOfWeightId":null,"Transporters":[],"Packages":[]}]}]</t>
+          <t>[{"ShipperLicenseNumber":"SF-SBX-NY-6-13402","ShipperName":"Evaluation Shipper","ShipperMainPhoneNumber":"555-000-0000","ShipperAddress1":"1 Evaluation Way","ShipperAddress2":null,"ShipperAddressCity":"Albany","ShipperAddressState":"NY","ShipperAddressPostalCode":"12207","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-3-30301","InvoiceNumber":"EXT-B-0829-1332","TransferTypeName":"Beginning Inventory","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T14:32:26Z","EstimatedArrivalDateTime":"2026-08-29T17:32:26Z","GrossWeight":null,"GrossUnitOfWeightId":null,"Transporters":[],"Packages":[]}]}]</t>
         </is>
       </c>
     </row>
@@ -12000,7 +12000,7 @@
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:18Z</t>
+          <t>2026-08-29T13:32:26Z</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="G13" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/transfers/v2/incoming?lastModifiedStart=2026-08-26T14%3A02%3A18Z&amp;lastModifiedEnd=2026-08-27T14%3A02%3A18Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/incoming?lastModifiedStart=2026-08-28T13%3A32%3A26Z&amp;lastModifiedEnd=2026-08-29T13%3A32%3A26Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="H13" s="262" t="inlineStr">

--- a/evidence/metrc/Evaluation_NY_completed.xlsx
+++ b/evidence/metrc/Evaluation_NY_completed.xlsx
@@ -2449,12 +2449,12 @@
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>59123</t>
+          <t>59017</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:09Z</t>
+          <t>2026-08-29T14:27:48Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="H5" s="261" t="inlineStr">
         <is>
-          <t>[{"Name":"TP Batch 0827-1402","Type":"Clone","Count":6,"Strain":"Terpenomics Strain 0827-1402","Location":"Terpenomics Loc 0827-1402 (Updated)","Sublocation":null,"PatientLicenseNumber":null,"ActualDate":"2026-08-27","SourcePlantBatches":null}]</t>
+          <t>[{"Name":"TP Batch 0829-1427","Type":"Clone","Count":6,"Strain":"Terpenomics Strain 0829-1427","Location":"Terpenomics Loc 0829-1427 (Updated)","Sublocation":null,"PatientLicenseNumber":null,"ActualDate":"2026-08-29","SourcePlantBatches":null}]</t>
         </is>
       </c>
     </row>
@@ -2529,17 +2529,17 @@
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>217773</t>
+          <t>218945</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:09Z</t>
+          <t>2026-08-29T14:27:48Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004532000001445</t>
+          <t>1A4120300004532000001525</t>
         </is>
       </c>
       <c r="G9" s="104" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="H9" s="261" t="inlineStr">
         <is>
-          <t>[{"Id":null,"PlantBatch":"TP Batch 0827-1402","Count":3,"Location":"Terpenomics Loc 0827-1402 (Updated)","Sublocation":null,"Item":"Terpenomics Clone 0827-1402","Tag":"1A4120300004532000001445","PatientLicenseNumber":null,"Note":"Evaluation step","IsTradeSample":false,"IsDonation":false,"ActualDate":"2026-08-27"}]</t>
+          <t>[{"Id":null,"PlantBatch":"TP Batch 0829-1427","Count":3,"Location":"Terpenomics Loc 0829-1427 (Updated)","Sublocation":null,"Item":"Terpenomics Clone 0829-1427","Tag":"1A4120300004532000001525","PatientLicenseNumber":null,"Note":"Evaluation step","IsTradeSample":false,"IsDonation":false,"ActualDate":"2026-08-29"}]</t>
         </is>
       </c>
     </row>
@@ -2602,17 +2602,17 @@
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>751530, 751531</t>
+          <t>751545, 751546</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:09Z</t>
+          <t>2026-08-29T14:27:49Z</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
         <is>
-          <t>1A4120200004532000001595, 1A4120200004532000001596</t>
+          <t>1A4120200004532000001675, 1A4120200004532000001676</t>
         </is>
       </c>
       <c r="G13" s="104" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="H13" s="261" t="inlineStr">
         <is>
-          <t>[{"Name":"TP Batch 0827-1402","Count":2,"StartingTag":"1A4120200004532000001595","GrowthPhase":"Vegetative","NewLocation":"Terpenomics Loc 0827-1402 (Updated)","NewSublocation":null,"GrowthDate":"2026-08-27","PatientLicenseNumber":null}]</t>
+          <t>[{"Name":"TP Batch 0829-1427","Count":2,"StartingTag":"1A4120200004532000001675","GrowthPhase":"Vegetative","NewLocation":"Terpenomics Loc 0829-1427 (Updated)","NewSublocation":null,"GrowthDate":"2026-08-29","PatientLicenseNumber":null}]</t>
         </is>
       </c>
     </row>
@@ -2682,12 +2682,12 @@
       </c>
       <c r="D17" s="248" t="inlineStr">
         <is>
-          <t>59123</t>
+          <t>59017</t>
         </is>
       </c>
       <c r="E17" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:09Z</t>
+          <t>2026-08-29T14:27:49Z</t>
         </is>
       </c>
       <c r="F17" s="247" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="H17" s="261" t="inlineStr">
         <is>
-          <t>[{"PlantBatch":"TP Batch 0827-1402","Count":1,"WasteMethodName":null,"WasteMaterialMixed":null,"WasteReasonName":"Waste","ReasonNote":"Evaluation step — destroying one immature plant.","WasteWeight":1.0,"WasteUnitOfMeasure":"Grams","ActualDate":"2026-08-27"}]</t>
+          <t>[{"PlantBatch":"TP Batch 0829-1427","Count":1,"WasteMethodName":null,"WasteMaterialMixed":null,"WasteReasonName":"Waste","ReasonNote":"Evaluation step — destroying one immature plant.","WasteWeight":1.0,"WasteUnitOfMeasure":"Grams","ActualDate":"2026-08-29"}]</t>
         </is>
       </c>
     </row>
@@ -3075,12 +3075,12 @@
       </c>
       <c r="E6" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:00:21+00:00</t>
+          <t>2026-08-29T14:27:50+00:00</t>
         </is>
       </c>
       <c r="F6" s="247" t="inlineStr">
         <is>
-          <t>1A4120200004532000001006</t>
+          <t>1A4120200004532000001677</t>
         </is>
       </c>
       <c r="G6" s="104" t="n"/>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="I6" s="262" t="inlineStr">
         <is>
-          <t>[{"Id":null,"Label":"1A4120200004532000001006","Location":"Terpenomics Loc 0827-1402 (Updated)","Sublocation":null,"ActualDate":"2026-08-27"}]</t>
+          <t>[{"Id":null,"Label":"1A4120200004532000001677","Location":"Terpenomics Loc 0829-1427 (Updated)","Sublocation":null,"ActualDate":"2026-08-29"}]</t>
         </is>
       </c>
     </row>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="D10" s="248" t="inlineStr">
         <is>
-          <t>59124</t>
+          <t>59019</t>
         </is>
       </c>
       <c r="E10" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:10Z</t>
+          <t>2026-08-29T14:27:56Z</t>
         </is>
       </c>
       <c r="F10" s="247" t="inlineStr">
         <is>
-          <t>1A4120200004532000001006</t>
+          <t>1A4120200004532000001677</t>
         </is>
       </c>
       <c r="G10" s="104" t="inlineStr">
         <is>
-          <t>TP Immature 0827-1402</t>
+          <t>TP Immature 0829-1427</t>
         </is>
       </c>
       <c r="H10" s="247" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="I10" s="262" t="inlineStr">
         <is>
-          <t>[{"PlantLabel":"1A4120200004532000001006","PlantBatchName":"TP Immature 0827-1402","PlantBatchType":"Clone","PlantCount":3,"LocationName":"Terpenomics Loc 0827-1402 (Updated)","SublocationName":null,"StrainName":"Terpenomics Strain 0827-1402","PatientLicenseNumber":null,"ActualDate":"2026-08-27T14:02:10Z"}]</t>
+          <t>[{"PlantLabel":"1A4120200004532000001677","PlantBatchName":"TP Immature 0829-1427","PlantBatchType":"Clone","PlantCount":3,"LocationName":"Terpenomics Loc 0829-1427 (Updated)","SublocationName":null,"StrainName":"Terpenomics Strain 0829-1427","PatientLicenseNumber":null,"ActualDate":"2026-08-29T14:27:56Z"}]</t>
         </is>
       </c>
     </row>
@@ -3234,17 +3234,17 @@
       </c>
       <c r="D14" s="248" t="inlineStr">
         <is>
-          <t>218906</t>
+          <t>218946</t>
         </is>
       </c>
       <c r="E14" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:10Z</t>
+          <t>2026-08-29T14:27:57Z</t>
         </is>
       </c>
       <c r="F14" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004532000001446</t>
+          <t>1A4120300004532000001526</t>
         </is>
       </c>
       <c r="G14" s="104" t="n"/>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I14" s="262" t="inlineStr">
         <is>
-          <t>[{"PlantLabel":"1A4120200004532000001006","PackageTag":"1A4120300004532000001446","PlantBatchType":"Clone","Item":"Terpenomics Clone 0827-1402","Location":"Terpenomics Loc 0827-1402 (Updated)","Sublocation":null,"Note":null,"IsTradeSample":false,"PatientLicenseNumber":null,"IsDonation":false,"Count":3,"ActualDate":"2026-08-27T14:02:10Z"}]</t>
+          <t>[{"PlantLabel":"1A4120200004532000001677","PackageTag":"1A4120300004532000001526","PlantBatchType":"Clone","Item":"Terpenomics Clone 0829-1427","Location":"Terpenomics Loc 0829-1427 (Updated)","Sublocation":null,"Note":null,"IsTradeSample":false,"PatientLicenseNumber":null,"IsDonation":false,"Count":3,"ActualDate":"2026-08-29T14:27:56Z"}]</t>
         </is>
       </c>
     </row>
@@ -3318,17 +3318,17 @@
       </c>
       <c r="D18" s="248" t="inlineStr">
         <is>
-          <t>752259</t>
+          <t>750774</t>
         </is>
       </c>
       <c r="E18" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:11Z</t>
+          <t>2026-08-29T14:27:57Z</t>
         </is>
       </c>
       <c r="F18" s="247" t="inlineStr">
         <is>
-          <t>1A4120200004532000001085</t>
+          <t>1A4120200004532000001678</t>
         </is>
       </c>
       <c r="G18" s="247" t="n"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="I18" s="262" t="inlineStr">
         <is>
-          <t>[{"Id":null,"Label":"1A4120200004532000001085","WasteMethodName":null,"WasteMaterialMixed":null,"WasteWeight":15.0,"WasteUnitOfMeasureName":"Grams","WasteReasonName":"Waste","Count":0,"ReasonNote":"Evaluation step — plant destruction.","ActualDate":"2026-08-27"}]</t>
+          <t>[{"Id":null,"Label":"1A4120200004532000001678","WasteMethodName":null,"WasteMaterialMixed":null,"WasteWeight":15.0,"WasteUnitOfMeasureName":"Grams","WasteReasonName":"Waste","Count":0,"ReasonNote":"Evaluation step — plant destruction.","ActualDate":"2026-08-29"}]</t>
         </is>
       </c>
     </row>
@@ -3401,17 +3401,17 @@
       </c>
       <c r="D22" s="248" t="inlineStr">
         <is>
-          <t>28811</t>
+          <t>28812</t>
         </is>
       </c>
       <c r="E22" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:11Z</t>
+          <t>2026-08-29T14:27:57Z</t>
         </is>
       </c>
       <c r="F22" s="247" t="inlineStr">
         <is>
-          <t>1A4120200004532000001112</t>
+          <t>1A4120200004532000001679</t>
         </is>
       </c>
       <c r="G22" s="247" t="n"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="I22" s="262" t="inlineStr">
         <is>
-          <t>[{"Plant":"1A4120200004532000001112","Weight":25.0,"UnitOfWeight":"Grams","DryingLocation":"Terpenomics Loc 0827-1402 (Updated)","DryingSublocation":null,"HarvestName":null,"PatientLicenseNumber":null,"ActualDate":"2026-08-27","PlantCount":1}]</t>
+          <t>[{"Plant":"1A4120200004532000001679","Weight":25.0,"UnitOfWeight":"Grams","DryingLocation":"Terpenomics Loc 0829-1427 (Updated)","DryingSublocation":null,"HarvestName":null,"PatientLicenseNumber":null,"ActualDate":"2026-08-29","PlantCount":1}]</t>
         </is>
       </c>
     </row>
@@ -3484,22 +3484,22 @@
       </c>
       <c r="D26" s="248" t="inlineStr">
         <is>
-          <t>28708, 28708</t>
+          <t>28709, 28709</t>
         </is>
       </c>
       <c r="E26" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:11Z</t>
+          <t>2026-08-29T14:27:57Z</t>
         </is>
       </c>
       <c r="F26" s="247" t="inlineStr">
         <is>
-          <t>1A4120200004532000001112, 1A4120200004532000001113</t>
+          <t>1A4120200004532000001679, 1A4120200004532000001680</t>
         </is>
       </c>
       <c r="G26" s="247" t="inlineStr">
         <is>
-          <t>TP Harvest 0827-1402</t>
+          <t>TP Harvest 0829-1427</t>
         </is>
       </c>
       <c r="H26" s="247" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="I26" s="262" t="inlineStr">
         <is>
-          <t>[{"Plant":"1A4120200004532000001112","Weight":100.0,"UnitOfWeight":"Grams","DryingLocation":"Terpenomics Loc 0827-1402 (Updated)","DryingSublocation":null,"HarvestName":"TP Harvest 0827-1402","PatientLicenseNumber":null,"ActualDate":"2026-08-27"},{"Plant":"1A4120200004532000001113","Weight":100.0,"UnitOfWeight":"Grams","DryingLocation":"Terpenomics Loc 0827-1402 (Updated)","DryingSublocation":null,"HarvestName":"TP Harvest 0827-1402","PatientLicenseNumber":null,"ActualDate":"2026-08-27"}]</t>
+          <t>[{"Plant":"1A4120200004532000001679","Weight":100.0,"UnitOfWeight":"Grams","DryingLocation":"Terpenomics Loc 0829-1427 (Updated)","DryingSublocation":null,"HarvestName":"TP Harvest 0829-1427","PatientLicenseNumber":null,"ActualDate":"2026-08-29"},{"Plant":"1A4120200004532000001680","Weight":100.0,"UnitOfWeight":"Grams","DryingLocation":"Terpenomics Loc 0829-1427 (Updated)","DryingSublocation":null,"HarvestName":"TP Harvest 0829-1427","PatientLicenseNumber":null,"ActualDate":"2026-08-29"}]</t>
         </is>
       </c>
     </row>
@@ -3951,22 +3951,22 @@
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>218907</t>
+          <t>218947</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:11Z</t>
+          <t>2026-08-29T14:27:58Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004532000001447</t>
+          <t>1A4120300004532000001527</t>
         </is>
       </c>
       <c r="G5" s="104" t="inlineStr">
         <is>
-          <t>TP Harvest 0827-1402</t>
+          <t>TP Harvest 0829-1427</t>
         </is>
       </c>
       <c r="H5" s="247" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="I5" s="262" t="inlineStr">
         <is>
-          <t>[{"Tag":"1A4120300004532000001447","Location":"Terpenomics Loc 0827-1402 (Updated)","Sublocation":null,"Item":"Terpenomics Item 0827-1402","UnitOfWeight":"Grams","PatientLicenseNumber":null,"Note":"Evaluation step","IsProductionBatch":false,"ProductionBatchNumber":null,"IsTradeSample":false,"IsDonation":false,"ProductRequiresRemediation":false,"RemediateProduct":false,"ActualDate":"2026-08-27","Ingredients":[{"HarvestId":28811,"HarvestName":null,"Weight":50.0,"UnitOfWeight":"Grams"}]}]</t>
+          <t>[{"Tag":"1A4120300004532000001527","Location":"Terpenomics Loc 0829-1427 (Updated)","Sublocation":null,"Item":"Terpenomics Item 0829-1427","UnitOfWeight":"Grams","PatientLicenseNumber":null,"Note":"Evaluation step","IsProductionBatch":false,"ProductionBatchNumber":null,"IsTradeSample":false,"IsDonation":false,"ProductRequiresRemediation":false,"RemediateProduct":false,"ActualDate":"2026-08-29","Ingredients":[{"HarvestId":28709,"HarvestName":null,"Weight":50.0,"UnitOfWeight":"Grams"}]}]</t>
         </is>
       </c>
     </row>
@@ -4039,12 +4039,12 @@
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>28811</t>
+          <t>28709</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:12Z</t>
+          <t>2026-08-29T14:27:58Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="G9" s="104" t="inlineStr">
         <is>
-          <t>TP Harvest 0827-1402</t>
+          <t>TP Harvest 0829-1427</t>
         </is>
       </c>
       <c r="H9" s="247" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="I9" s="262" t="inlineStr">
         <is>
-          <t>[{"Id":28811,"WasteType":"Plant Material","UnitOfWeight":"Grams","WasteWeight":25.0,"ActualDate":"2026-08-27"}]</t>
+          <t>[{"Id":28709,"WasteType":"Plant Material","UnitOfWeight":"Grams","WasteWeight":200.0,"ActualDate":"2026-08-29"}]</t>
         </is>
       </c>
     </row>
@@ -4119,12 +4119,12 @@
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>28811</t>
+          <t>28709</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:12Z</t>
+          <t>2026-08-29T14:27:58Z</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="G13" s="104" t="inlineStr">
         <is>
-          <t>TP Harvest 0827-1402</t>
+          <t>TP Harvest 0829-1427</t>
         </is>
       </c>
       <c r="H13" s="247" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="I13" s="262" t="inlineStr">
         <is>
-          <t>[{"Id":28811,"ActualDate":"2026-08-27"}]</t>
+          <t>[{"Id":28709,"ActualDate":"2026-08-29"}]</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4207,12 @@
       </c>
       <c r="D17" s="248" t="inlineStr">
         <is>
-          <t>28811</t>
+          <t>28709</t>
         </is>
       </c>
       <c r="E17" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:12Z</t>
+          <t>2026-08-29T14:27:58Z</t>
         </is>
       </c>
       <c r="F17" s="247" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="G17" s="104" t="inlineStr">
         <is>
-          <t>TP Harvest 0827-1402</t>
+          <t>TP Harvest 0829-1427</t>
         </is>
       </c>
       <c r="H17" s="247" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="I17" s="262" t="inlineStr">
         <is>
-          <t>[{"Id":28811}]</t>
+          <t>[{"Id":28709}]</t>
         </is>
       </c>
     </row>
@@ -4599,17 +4599,17 @@
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>217774</t>
+          <t>217781</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:12Z</t>
+          <t>2026-08-29T14:27:59Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004532000001448</t>
+          <t>1A4120300004532000001528</t>
         </is>
       </c>
       <c r="G5" s="247" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="H5" s="262" t="inlineStr">
         <is>
-          <t>[{"Tag":"1A4120300004532000001448","Location":"Terpenomics Loc 0827-1402 (Updated)","Sublocation":null,"Item":"Terpenomics Item 0827-1402","Quantity":10.0,"UnitOfMeasure":"Grams","PatientLicenseNumber":null,"Note":"Evaluation step","IsProductionBatch":false,"ProductionBatchNumber":null,"IsDonation":false,"IsTradeSample":false,"ProductRequiresRemediation":false,"UseSameItem":true,"ActualDate":"2026-08-27","Ingredients":[{"Package":"1A4120300004532000001447","Quantity":10.0,"UnitOfMeasure":"Grams"}]}]</t>
+          <t>[{"Tag":"1A4120300004532000001528","Location":"Terpenomics Loc 0829-1427 (Updated)","Sublocation":null,"Item":"Terpenomics Item 0829-1427","Quantity":10.0,"UnitOfMeasure":"Grams","PatientLicenseNumber":null,"Note":"Evaluation step","IsProductionBatch":false,"ProductionBatchNumber":null,"IsDonation":false,"IsTradeSample":false,"ProductRequiresRemediation":false,"UseSameItem":true,"ActualDate":"2026-08-29","Ingredients":[{"Package":"1A4120300004532000001527","Quantity":10.0,"UnitOfMeasure":"Grams"}]}]</t>
         </is>
       </c>
     </row>
@@ -4684,12 +4684,12 @@
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:12Z</t>
+          <t>2026-08-29T14:28:00Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004532000001448</t>
+          <t>1A4120300004532000001528</t>
         </is>
       </c>
       <c r="G9" s="247" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="H9" s="262" t="inlineStr">
         <is>
-          <t>[{"Label":"1A4120300004532000001448","Item":"Terpenomics Alt Item 0827-1402"}]</t>
+          <t>[{"Label":"1A4120300004532000001528","Item":"Terpenomics Alt Item 0829-1427"}]</t>
         </is>
       </c>
     </row>
@@ -4757,12 +4757,12 @@
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:13Z</t>
+          <t>2026-08-29T14:28:01Z</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004532000001448</t>
+          <t>1A4120300004532000001528</t>
         </is>
       </c>
       <c r="G13" s="247" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="H13" s="262" t="inlineStr">
         <is>
-          <t>[{"Label":"1A4120300004532000001448","Quantity":0,"UnitOfMeasure":"Grams","AdjustmentReason":"Drying","AdjustmentDate":"2026-08-27","ReasonNote":"Evaluation step — adjusting to zero."}]</t>
+          <t>[{"Label":"1A4120300004532000001528","Quantity":0,"UnitOfMeasure":"Grams","AdjustmentReason":"Drying","AdjustmentDate":"2026-08-29","ReasonNote":"Evaluation step — adjusting to zero."}]</t>
         </is>
       </c>
     </row>
@@ -4837,12 +4837,12 @@
       </c>
       <c r="E17" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:13Z</t>
+          <t>2026-08-29T14:28:01Z</t>
         </is>
       </c>
       <c r="F17" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004532000001448</t>
+          <t>1A4120300004532000001528</t>
         </is>
       </c>
       <c r="G17" s="247" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="H17" s="262" t="inlineStr">
         <is>
-          <t>[{"Label":"1A4120300004532000001448","ActualDate":"2026-08-27"}]</t>
+          <t>[{"Label":"1A4120300004532000001528","ActualDate":"2026-08-29"}]</t>
         </is>
       </c>
     </row>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E21" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:13Z</t>
+          <t>2026-08-29T14:28:01Z</t>
         </is>
       </c>
       <c r="F21" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004532000001448</t>
+          <t>1A4120300004532000001528</t>
         </is>
       </c>
       <c r="G21" s="247" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="H21" s="262" t="inlineStr">
         <is>
-          <t>[{"Label":"1A4120300004532000001448"}]</t>
+          <t>[{"Label":"1A4120300004532000001528"}]</t>
         </is>
       </c>
     </row>
@@ -7470,27 +7470,27 @@
       </c>
       <c r="C5" s="248" t="inlineStr">
         <is>
-          <t>SF-SBX-NY-17-30301</t>
+          <t>SF-SBX-NY-5-30301</t>
         </is>
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>218855</t>
+          <t>218937</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T13:23:28+00:00</t>
+          <t>2026-08-29T14:28:07+00:00</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004532000001111</t>
+          <t>1A4120300004533000000013</t>
         </is>
       </c>
       <c r="G5" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/labtests/v2/results?packageId=218855&amp;licenseNumber=SF-SBX-NY-17-30301</t>
+          <t>https://sandbox-api-ny.metrc.com/labtests/v2/results?packageId=218937&amp;licenseNumber=SF-SBX-NY-5-30301</t>
         </is>
       </c>
       <c r="H5" s="262" t="inlineStr">
@@ -8196,17 +8196,17 @@
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>683</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:15Z</t>
+          <t>2026-08-29T14:28:03Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004533000000001</t>
+          <t>1A4120300004533000000011</t>
         </is>
       </c>
       <c r="G5" s="248" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="H5" s="262" t="inlineStr">
         <is>
-          <t>[{"SalesDateTime":"2026-08-27T14:02:14Z","ExternalReceiptNumber":"TP-0827-1402","SalesCustomerType":"Consumer","PatientLicenseNumber":null,"CaregiverLicenseNumber":null,"IdentificationMethod":null,"PatientRegistrationLocationId":null,"Transactions":[{"PackageLabel":"1A4120300004533000000001","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":9.99}]}]</t>
+          <t>[{"SalesDateTime":"2026-08-29T14:28:02Z","ExternalReceiptNumber":"TP-0829-1427","SalesCustomerType":"Consumer","PatientLicenseNumber":null,"CaregiverLicenseNumber":null,"IdentificationMethod":null,"PatientRegistrationLocationId":null,"Transactions":[{"PackageLabel":"1A4120300004533000000011","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":9.99}]}]</t>
         </is>
       </c>
     </row>
@@ -8275,17 +8275,17 @@
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>683</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:15Z</t>
+          <t>2026-08-29T14:28:03Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004533000000001</t>
+          <t>1A4120300004533000000011</t>
         </is>
       </c>
       <c r="G9" s="248" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="H9" s="262" t="inlineStr">
         <is>
-          <t>[{"SalesDateTime":"2026-08-27T14:02:15Z","ExternalReceiptNumber":"TP-0827-1402","SalesCustomerType":"Consumer","PatientLicenseNumber":null,"CaregiverLicenseNumber":null,"IdentificationMethod":null,"PatientRegistrationLocationId":null,"Transactions":[{"PackageLabel":"1A4120300004533000000001","Quantity":2.0,"UnitOfMeasure":"Each","TotalAmount":19.98}],"Id":682}]</t>
+          <t>[{"SalesDateTime":"2026-08-29T14:28:03Z","ExternalReceiptNumber":"TP-0829-1427","SalesCustomerType":"Consumer","PatientLicenseNumber":null,"CaregiverLicenseNumber":null,"IdentificationMethod":null,"PatientRegistrationLocationId":null,"Transactions":[{"PackageLabel":"1A4120300004533000000011","Quantity":2.0,"UnitOfMeasure":"Each","TotalAmount":19.98}],"Id":683}]</t>
         </is>
       </c>
     </row>
@@ -8348,22 +8348,22 @@
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>683</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:15Z</t>
+          <t>2026-08-29T14:28:04Z</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004533000000001</t>
+          <t>1A4120300004533000000011</t>
         </is>
       </c>
       <c r="G13" s="248" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/sales/v2/receipts/682?licenseNumber=SF-SBX-NY-5-30301</t>
+          <t>https://sandbox-api-ny.metrc.com/sales/v2/receipts/683?licenseNumber=SF-SBX-NY-5-30301</t>
         </is>
       </c>
       <c r="H13" s="248" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="E17" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:15Z</t>
+          <t>2026-08-29T14:28:04Z</t>
         </is>
       </c>
       <c r="F17" s="247" t="inlineStr">
@@ -8501,17 +8501,17 @@
       </c>
       <c r="D21" s="248" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>684</t>
         </is>
       </c>
       <c r="E21" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:15Z</t>
+          <t>2026-08-29T14:28:04Z</t>
         </is>
       </c>
       <c r="F21" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004533000000001</t>
+          <t>1A4120300004533000000011</t>
         </is>
       </c>
       <c r="G21" s="248" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="H21" s="262" t="inlineStr">
         <is>
-          <t>[{"SalesDateTime":"2026-08-27T14:02:15Z","ExternalReceiptNumber":"TP-0827-1402-EP","SalesCustomerType":"ExternalPatient","PatientLicenseNumber":"PTN-123-456","CaregiverLicenseNumber":null,"IdentificationMethod":null,"PatientRegistrationLocationId":null,"Transactions":[{"PackageLabel":"1A4120300004533000000001","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":9.99}]}]</t>
+          <t>[{"SalesDateTime":"2026-08-29T14:28:04Z","ExternalReceiptNumber":"TP-0829-1427-EP","SalesCustomerType":"ExternalPatient","PatientLicenseNumber":"PTN-123-456","CaregiverLicenseNumber":null,"IdentificationMethod":null,"PatientRegistrationLocationId":null,"Transactions":[{"PackageLabel":"1A4120300004533000000011","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":9.99}]}]</t>
         </is>
       </c>
     </row>
@@ -8857,17 +8857,17 @@
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>411</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:16Z</t>
+          <t>2026-08-29T14:28:05Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004533000000002</t>
+          <t>1A4120300004533000000012</t>
         </is>
       </c>
       <c r="G5" s="247" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H5" s="262" t="inlineStr">
         <is>
-          <t>[{"SalesDateTime":"2026-08-27T14:02:15Z","SalesCustomerType":"Consumer","PatientLicenseNumber":null,"ConsumerId":null,"DriverEmployeeId":"1","DriverName":"Evaluation Driver","DriversLicenseNumber":"D0000001","PhoneNumberForQuestions":"+1-555-000-0000","VehicleMake":"Car","VehicleModel":"Small","VehicleLicensePlateNumber":"TP-0001","RecipientAddressStreet1":"1 Evaluation Way","RecipientAddressCity":"Albany","RecipientAddressState":"NY","RecipientAddressPostalCode":"12207","PlannedRoute":"Drive to destination.","EstimatedDepartureDateTime":"2026-08-27T15:02:15Z","EstimatedArrivalDateTime":"2026-08-27T17:02:15Z","Transactions":[{"PackageLabel":"1A4120300004533000000002","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":9.99},{"PackageLabel":"1A4120300004533000000003","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":19.98},{"PackageLabel":"1A4120300004533000000004","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":29.97}]}]</t>
+          <t>[{"SalesDateTime":"2026-08-29T14:28:04Z","SalesCustomerType":"Consumer","PatientLicenseNumber":null,"ConsumerId":null,"DriverEmployeeId":"1","DriverName":"Evaluation Driver","DriversLicenseNumber":"D0000001","PhoneNumberForQuestions":"+1-555-000-0000","VehicleMake":"Car","VehicleModel":"Small","VehicleLicensePlateNumber":"TP-0001","RecipientAddressStreet1":"1 Evaluation Way","RecipientAddressCity":"Albany","RecipientAddressState":"NY","RecipientAddressPostalCode":"12207","PlannedRoute":"Drive to destination.","EstimatedDepartureDateTime":"2026-08-29T15:28:04Z","EstimatedArrivalDateTime":"2026-08-29T17:28:04Z","Transactions":[{"PackageLabel":"1A4120300004533000000012","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":9.99},{"PackageLabel":"1A4120300004533000000013","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":19.98},{"PackageLabel":"1A4120300004533000000014","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":29.97}]}]</t>
         </is>
       </c>
     </row>
@@ -8937,17 +8937,17 @@
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>411</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:16Z</t>
+          <t>2026-08-29T14:28:05Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004533000000002</t>
+          <t>1A4120300004533000000012</t>
         </is>
       </c>
       <c r="G9" s="247" t="inlineStr">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="H9" s="262" t="inlineStr">
         <is>
-          <t>[{"SalesDateTime":"2026-08-27T14:02:15Z","SalesCustomerType":"Consumer","PatientLicenseNumber":null,"ConsumerId":null,"DriverEmployeeId":"1","DriverName":"Evaluation Driver","DriversLicenseNumber":"D0000001","PhoneNumberForQuestions":"+1-555-000-0000","VehicleMake":"Car","VehicleModel":"Small","VehicleLicensePlateNumber":"TP-0001","RecipientAddressStreet1":"1 Evaluation Way","RecipientAddressCity":"Albany","RecipientAddressState":"NY","RecipientAddressPostalCode":"12207","PlannedRoute":"Drive to destination.","EstimatedDepartureDateTime":"2026-08-27T15:02:15Z","EstimatedArrivalDateTime":"2026-08-27T17:02:15Z","Transactions":[{"PackageLabel":"1A4120300004533000000002","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":9.99},{"PackageLabel":"1A4120300004533000000003","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":19.98}],"Id":405}]</t>
+          <t>[{"SalesDateTime":"2026-08-29T14:28:04Z","SalesCustomerType":"Consumer","PatientLicenseNumber":null,"ConsumerId":null,"DriverEmployeeId":"1","DriverName":"Evaluation Driver","DriversLicenseNumber":"D0000001","PhoneNumberForQuestions":"+1-555-000-0000","VehicleMake":"Car","VehicleModel":"Small","VehicleLicensePlateNumber":"TP-0001","RecipientAddressStreet1":"1 Evaluation Way","RecipientAddressCity":"Albany","RecipientAddressState":"NY","RecipientAddressPostalCode":"12207","PlannedRoute":"Drive to destination.","EstimatedDepartureDateTime":"2026-08-29T15:28:04Z","EstimatedArrivalDateTime":"2026-08-29T17:28:04Z","Transactions":[{"PackageLabel":"1A4120300004533000000012","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":9.99},{"PackageLabel":"1A4120300004533000000013","Quantity":1.0,"UnitOfMeasure":"Each","TotalAmount":19.98}],"Id":411}]</t>
         </is>
       </c>
     </row>
@@ -9010,17 +9010,17 @@
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>411</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:16Z</t>
+          <t>2026-08-29T14:28:06Z</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
         <is>
-          <t>1A4120300004533000000002</t>
+          <t>1A4120300004533000000012</t>
         </is>
       </c>
       <c r="G13" s="247" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="H13" s="262" t="inlineStr">
         <is>
-          <t>[{"Id":405,"ActualArrivalDateTime":"2026-08-27T14:02:16Z","PaymentType":null,"AcceptedPackages":["1A4120300004533000000002"],"ReturnedPackages":[{"Label":"1A4120300004533000000003","ReturnQuantityVerified":1.0,"ReturnUnitOfMeasure":"Each","ReturnReason":"Unable to Deliver","ReturnReasonNote":"Evaluation step"}]}]</t>
+          <t>[{"Id":411,"ActualArrivalDateTime":"2026-08-29T14:28:05Z","PaymentType":null,"AcceptedPackages":["1A4120300004533000000012"],"ReturnedPackages":[{"Label":"1A4120300004533000000013","ReturnQuantityVerified":1.0,"ReturnUnitOfMeasure":"Each","ReturnReason":"Unable to Deliver","ReturnReasonNote":"Evaluation step"}]}]</t>
         </is>
       </c>
     </row>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="G5" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/transfers/v2/incoming?lastModifiedStart=2026-08-26T14%3A02%3A32Z&amp;lastModifiedEnd=2026-08-27T14%3A02%3A32Z&amp;licenseNumber=SF-SBX-NY-14-30301</t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/incoming?lastModifiedStart=2026-08-26T14%3A28%3A26Z&amp;lastModifiedEnd=2026-08-27T14%3A28%3A26Z&amp;licenseNumber=SF-SBX-NY-14-30301</t>
         </is>
       </c>
       <c r="H5" s="262" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="G9" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/transfers/v2/outgoing?lastModifiedStart=2026-08-26T14%3A02%3A32Z&amp;lastModifiedEnd=2026-08-27T14%3A02%3A32Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/outgoing?lastModifiedStart=2026-08-26T14%3A28%3A28Z&amp;lastModifiedEnd=2026-08-27T14%3A28%3A28Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="H9" s="262" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="G13" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/transfers/v2/rejected?lastModifiedStart=2026-08-25T14%3A02%3A33Z&amp;lastModifiedEnd=2026-08-26T14%3A02%3A33Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/rejected?lastModifiedStart=2026-08-27T14%3A28%3A29Z&amp;lastModifiedEnd=2026-08-28T14%3A28%3A29Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="H13" s="262" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="E21" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:33Z</t>
+          <t>2026-08-29T14:28:29Z</t>
         </is>
       </c>
       <c r="F21" s="247" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="E25" s="250" t="inlineStr">
         <is>
-          <t>2026-08-27T14:02:33Z</t>
+          <t>2026-08-29T14:28:29Z</t>
         </is>
       </c>
       <c r="F25" s="247" t="inlineStr">
@@ -11145,12 +11145,12 @@
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t>2026-08-29T13:32:25Z</t>
+          <t>2026-08-29T14:28:06Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="H5" s="262" t="inlineStr">
         <is>
-          <t>[{"Name":"TP Template A 0829-1332","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-6-13402","InvoiceNumber":"INV-A-0829-1332","TransferTypeName":"Unaffiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T14:32:24Z","EstimatedArrivalDateTime":"2026-08-29T17:32:24Z","Transporters":[],"Packages":[]}]}]</t>
+          <t>[{"Name":"TP Template A 0829-1427","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-6-13402","InvoiceNumber":"INV-A-0829-1427","TransferTypeName":"Unaffiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T15:28:06Z","EstimatedArrivalDateTime":"2026-08-29T18:28:06Z","Transporters":[],"Packages":[]}]}]</t>
         </is>
       </c>
     </row>
@@ -11219,12 +11219,12 @@
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>15911</t>
+          <t>16010</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t>2026-08-29T13:32:25Z</t>
+          <t>2026-08-29T14:28:07Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="H9" s="262" t="inlineStr">
         <is>
-          <t>[{"Name":"TP Template B 0829-1332","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-6-13402","InvoiceNumber":"INV-B-0829-1332","TransferTypeName":"Unaffiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T14:32:24Z","EstimatedArrivalDateTime":"2026-08-29T17:32:24Z","Transporters":[],"Packages":[]}]}]</t>
+          <t>[{"Name":"TP Template B 0829-1427","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-6-13402","InvoiceNumber":"INV-B-0829-1427","TransferTypeName":"Unaffiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T15:28:06Z","EstimatedArrivalDateTime":"2026-08-29T18:28:06Z","Transporters":[],"Packages":[]}]}]</t>
         </is>
       </c>
     </row>
@@ -11292,12 +11292,12 @@
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>15910, 15911</t>
+          <t>16009, 16010</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t>2026-08-29T13:32:25+00:00</t>
+          <t>2026-08-29T14:28:07+00:00</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="G13" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/transfers/v2/templates/outgoing?lastModifiedStart=2026-08-28T13%3A32%3A25Z&amp;lastModifiedEnd=2026-08-29T13%3A32%3A25Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/templates/outgoing?lastModifiedStart=2026-08-28T14%3A28%3A07Z&amp;lastModifiedEnd=2026-08-29T14%3A28%3A07Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="H13" s="262" t="inlineStr">
         <is>
-          <t>{"Data":[{"Id":15910,"ManifestNumber":"T-0000015910","InvoiceNumber":"INV-A-0829-1332","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0829-1332","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-29T13:32:25+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-29T13:32:25+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15911,"ManifestNumber":"T-0000015911","InvoiceNumber":"INV-B-0829-1332","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0829-1332","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-29T13:32:25+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-29T13:32:25+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null}],"Total":2,"TotalRecords":2,"PageSize":2,"RecordsOnPage":2,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
+          <t>{"Data":[{"Id":16009,"ManifestNumber":"T-0000016009","InvoiceNumber":"INV-A-0829-1427","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0829-1427","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-29T14:28:07+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-29T14:28:07+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":16010,"ManifestNumber":"T-0000016010","InvoiceNumber":"INV-B-0829-1427","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0829-1427","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-29T14:28:07+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-29T14:28:07+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15912,"ManifestNumber":"T-0000015912","InvoiceNumber":"INV-B-0829-1426","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0829-1426","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-29T14:26:36+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-29T14:26:36+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":16008,"ManifestNumber":"T-0000016008","InvoiceNumber":"INV-A-0829-1426","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0829-1426 (Updated)","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-29T14:26:36+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-29T14:26:36+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15910,"ManifestNumber":"T-0000015910","InvoiceNumber":"INV-A-0829-1332","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template A 0829-1332 (Updated)","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-29T13:32:25+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-29T13:32:26+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null},{"Id":15911,"ManifestNumber":"T-0000015911","InvoiceNumber":"INV-B-0829-1332","ShipmentLicenseType":"Licensed","ShipperFacilityLicenseNumber":"SF-SBX-NY-3-30301","ShipperFacilityName":"Sandbox AU Cultivator","Name":"TP Template B 0829-1332","TransporterFacilityLicenseNumber":null,"TransporterFacilityName":null,"DriverName":null,"DriverOccupationalLicenseNumber":null,"DriverVehicleLicenseNumber":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"DeliveryCount":1,"ReceivedDeliveryCount":0,"PackageCount":0,"ReceivedPackageCount":0,"ContainsPlantPackage":false,"ContainsProductPackage":false,"ContainsTradeSample":false,"ContainsDonation":false,"ContainsTestingSample":false,"ContainsProductRequiresRemediation":false,"ContainsRemediatedProductPackage":false,"ContainsPreTreatedProductPackage":false,"IsVoided":false,"CreatedDateTime":"2026-08-29T13:32:25+00:00","CreatedByUserName":"Pablo Dayton","LastModified":"2026-08-29T13:32:25+00:00","DeliveryId":0,"RecipientFacilityLicenseNumber":null,"RecipientFacilityName":null,"ShipmentTypeName":null,"ShipmentTransactionType":null,"EstimatedDepartureDateTime":"0001-01-01T00:00:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"0001-01-01T00:00:00.000","ActualArrivalDateTime":null,"DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"OriginatingTemplateId":null}],"Total":6,"TotalRecords":6,"PageSize":6,"RecordsOnPage":6,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
         </is>
       </c>
     </row>
@@ -11372,12 +11372,12 @@
       </c>
       <c r="D17" s="248" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="E17" s="250" t="inlineStr">
         <is>
-          <t>2026-08-29T13:32:25Z</t>
+          <t>2026-08-29T14:28:07Z</t>
         </is>
       </c>
       <c r="F17" s="247" t="inlineStr">
@@ -11387,12 +11387,12 @@
       </c>
       <c r="G17" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/transfers/v2/templates/outgoing/15910/deliveries</t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/templates/outgoing/16009/deliveries</t>
         </is>
       </c>
       <c r="H17" s="262" t="inlineStr">
         <is>
-          <t>{"Data":[{"Id":16412,"ManifestNumber":null,"DeliveryNumber":0,"RecipientFacilityLicenseNumber":"SF-SBX-NY-6-13402","RecipientFacilityName":"Sandbox AU Distributor","ShipmentTypeName":"Unaffiliated Transfer","ShipmentTransactionType":"Wholesale","InvoiceNumber":"INV-A-0829-1332","PaymentTermDays":null,"PaymentDueDate":null,"EstimatedDepartureDateTime":"2026-08-29T14:32:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"2026-08-29T17:32:00.000","ActualArrivalDateTime":null,"GrossWeight":null,"GrossUnitOfWeightId":null,"GrossUnitOfWeightName":null,"PlannedRoute":"Evaluation route.","DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"RejectedPackagesReturned":false,"PDFDocumentFileSystemId":null}],"Total":1,"TotalRecords":1,"PageSize":1,"RecordsOnPage":1,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
+          <t>{"Data":[{"Id":16515,"ManifestNumber":null,"DeliveryNumber":0,"RecipientFacilityLicenseNumber":"SF-SBX-NY-6-13402","RecipientFacilityName":"Sandbox AU Distributor","ShipmentTypeName":"Unaffiliated Transfer","ShipmentTransactionType":"Wholesale","InvoiceNumber":"INV-A-0829-1427","PaymentTermDays":null,"PaymentDueDate":null,"EstimatedDepartureDateTime":"2026-08-29T15:28:00.000","ActualDepartureDateTime":null,"EstimatedArrivalDateTime":"2026-08-29T18:28:00.000","ActualArrivalDateTime":null,"GrossWeight":null,"GrossUnitOfWeightId":null,"GrossUnitOfWeightName":null,"PlannedRoute":"Evaluation route.","DeliveryPackageCount":0,"DeliveryReceivedPackageCount":0,"ReceivedDateTime":null,"EstimatedReturnDepartureDateTime":null,"ActualReturnDepartureDateTime":null,"EstimatedReturnArrivalDateTime":null,"ActualReturnArrivalDateTime":null,"RejectedPackagesReturned":false,"PDFDocumentFileSystemId":null}],"Total":1,"TotalRecords":1,"PageSize":1,"RecordsOnPage":1,"Page":1,"CurrentPage":1,"TotalPages":1}</t>
         </is>
       </c>
     </row>
@@ -11452,12 +11452,12 @@
       </c>
       <c r="D21" s="248" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="E21" s="250" t="inlineStr">
         <is>
-          <t>2026-08-29T13:32:26Z</t>
+          <t>2026-08-29T14:28:07Z</t>
         </is>
       </c>
       <c r="F21" s="247" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H21" s="262" t="inlineStr">
         <is>
-          <t>[{"Name":"TP Template A 0829-1332 (Updated)","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-6-13402","InvoiceNumber":"INV-A-0829-1332","TransferTypeName":"Unaffiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T14:32:24Z","EstimatedArrivalDateTime":"2026-08-29T17:32:24Z","Transporters":[],"Packages":[],"TransferDestinationId":0}],"TransferTemplateId":15910}]</t>
+          <t>[{"Name":"TP Template A 0829-1427 (Updated)","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-6-13402","InvoiceNumber":"INV-A-0829-1427","TransferTypeName":"Unaffiliated Transfer","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T15:28:06Z","EstimatedArrivalDateTime":"2026-08-29T18:28:06Z","Transporters":[],"Packages":[],"TransferDestinationId":0}],"TransferTemplateId":16009}]</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t>2026-08-29T13:32:26Z</t>
+          <t>2026-08-29T14:28:07Z</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="H5" s="262" t="inlineStr">
         <is>
-          <t>[{"ShipperLicenseNumber":"SF-SBX-NY-6-13402","ShipperName":"Evaluation Shipper","ShipperMainPhoneNumber":"555-000-0000","ShipperAddress1":"1 Evaluation Way","ShipperAddress2":null,"ShipperAddressCity":"Albany","ShipperAddressState":"NY","ShipperAddressPostalCode":"12207","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-3-30301","InvoiceNumber":"EXT-A-0829-1332","TransferTypeName":"Beginning Inventory","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T14:32:26Z","EstimatedArrivalDateTime":"2026-08-29T17:32:26Z","GrossWeight":null,"GrossUnitOfWeightId":null,"Transporters":[],"Packages":[]}]}]</t>
+          <t>[{"ShipperLicenseNumber":"SF-SBX-NY-6-13402","ShipperName":"Evaluation Shipper","ShipperMainPhoneNumber":"555-000-0000","ShipperAddress1":"1 Evaluation Way","ShipperAddress2":null,"ShipperAddressCity":"Albany","ShipperAddressState":"NY","ShipperAddressPostalCode":"12207","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-3-30301","InvoiceNumber":"EXT-A-0829-1427","TransferTypeName":"Beginning Inventory","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T15:28:07Z","EstimatedArrivalDateTime":"2026-08-29T18:28:07Z","GrossWeight":null,"GrossUnitOfWeightId":null,"Transporters":[],"Packages":[]}]}]</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t>2026-08-29T13:32:26Z</t>
+          <t>2026-08-29T14:28:07Z</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="H9" s="262" t="inlineStr">
         <is>
-          <t>[{"ShipperLicenseNumber":"SF-SBX-NY-6-13402","ShipperName":"Evaluation Shipper","ShipperMainPhoneNumber":"555-000-0000","ShipperAddress1":"1 Evaluation Way","ShipperAddress2":null,"ShipperAddressCity":"Albany","ShipperAddressState":"NY","ShipperAddressPostalCode":"12207","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-3-30301","InvoiceNumber":"EXT-B-0829-1332","TransferTypeName":"Beginning Inventory","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T14:32:26Z","EstimatedArrivalDateTime":"2026-08-29T17:32:26Z","GrossWeight":null,"GrossUnitOfWeightId":null,"Transporters":[],"Packages":[]}]}]</t>
+          <t>[{"ShipperLicenseNumber":"SF-SBX-NY-6-13402","ShipperName":"Evaluation Shipper","ShipperMainPhoneNumber":"555-000-0000","ShipperAddress1":"1 Evaluation Way","ShipperAddress2":null,"ShipperAddressCity":"Albany","ShipperAddressState":"NY","ShipperAddressPostalCode":"12207","TransporterFacilityLicenseNumber":null,"DriverOccupationalLicenseNumber":null,"DriverName":null,"DriverLicenseNumber":null,"PhoneNumberForQuestions":null,"VehicleMake":null,"VehicleModel":null,"VehicleLicensePlateNumber":null,"VehicleRegistrationNumber":null,"Destinations":[{"RecipientLicenseNumber":"SF-SBX-NY-3-30301","InvoiceNumber":"EXT-B-0829-1427","TransferTypeName":"Beginning Inventory","PlannedRoute":"Evaluation route.","EstimatedDepartureDateTime":"2026-08-29T15:28:07Z","EstimatedArrivalDateTime":"2026-08-29T18:28:07Z","GrossWeight":null,"GrossUnitOfWeightId":null,"Transporters":[],"Packages":[]}]}]</t>
         </is>
       </c>
     </row>
@@ -12000,7 +12000,7 @@
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t>2026-08-29T13:32:26Z</t>
+          <t>2026-08-29T14:28:07Z</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="G13" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/transfers/v2/incoming?lastModifiedStart=2026-08-28T13%3A32%3A26Z&amp;lastModifiedEnd=2026-08-29T13%3A32%3A26Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
+          <t>https://sandbox-api-ny.metrc.com/transfers/v2/incoming?lastModifiedStart=2026-08-28T14%3A28%3A07Z&amp;lastModifiedEnd=2026-08-29T14%3A28%3A07Z&amp;licenseNumber=SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="H13" s="262" t="inlineStr">
@@ -15810,12 +15810,12 @@
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>39528</t>
+          <t>39532</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t>Terpenomics Loc 0827-1402</t>
+          <t>Terpenomics Loc 0829-1427</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="G5" s="255" t="inlineStr">
         <is>
-          <t>[{"Name":"Terpenomics Loc 0827-1402","LocationTypeName":"Default Location Type"}]</t>
+          <t>[{"Name":"Terpenomics Loc 0829-1427","LocationTypeName":"Default Location Type"}]</t>
         </is>
       </c>
       <c r="H5" s="247" t="inlineStr">
@@ -15898,12 +15898,12 @@
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>39528</t>
+          <t>39532</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t>Terpenomics Loc 0827-1402 (Updated)</t>
+          <t>Terpenomics Loc 0829-1427 (Updated)</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
@@ -15913,7 +15913,7 @@
       </c>
       <c r="G9" s="255" t="inlineStr">
         <is>
-          <t>[{"Id":39528,"Name":"Terpenomics Loc 0827-1402 (Updated)","LocationTypeName":"Default Location Type"}]</t>
+          <t>[{"Id":39532,"Name":"Terpenomics Loc 0829-1427 (Updated)","LocationTypeName":"Default Location Type"}]</t>
         </is>
       </c>
       <c r="H9" s="247" t="inlineStr">
@@ -15978,22 +15978,22 @@
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>39528</t>
+          <t>39532</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t>Terpenomics Loc 0827-1402 (Updated)</t>
+          <t>Terpenomics Loc 0829-1427 (Updated)</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/locations/v2/39528?licenseNumber=SF-SBX-NY-3-30301</t>
+          <t>https://sandbox-api-ny.metrc.com/locations/v2/39532?licenseNumber=SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="G13" s="255" t="inlineStr">
         <is>
-          <t>{"Id":39528,"Name":"Terpenomics Loc 0827-1402 (Updated)","LocationTypeId":1,"LocationTypeName":"Default Location Type","ForPlantBatches":true,"ForPlants":true,"ForHarvests":true,"ForPackages":true}</t>
+          <t>{"Id":39532,"Name":"Terpenomics Loc 0829-1427 (Updated)","LocationTypeId":1,"LocationTypeName":"Default Location Type","ForPlantBatches":true,"ForPlants":true,"ForHarvests":true,"ForPackages":true}</t>
         </is>
       </c>
       <c r="H13" s="247" t="inlineStr">
@@ -16286,12 +16286,12 @@
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>62112</t>
+          <t>62119</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t>Terpenomics Strain 0827-1402</t>
+          <t>Terpenomics Strain 0829-1427</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
@@ -16301,7 +16301,7 @@
       </c>
       <c r="G5" s="255" t="inlineStr">
         <is>
-          <t>[{"Name":"Terpenomics Strain 0827-1402","TestingStatus":"None","ThcLevel":0.1865,"CbdLevel":0.1075,"IndicaPercentage":25.0,"SativaPercentage":75.0}]</t>
+          <t>[{"Name":"Terpenomics Strain 0829-1427","TestingStatus":"None","ThcLevel":0.1865,"CbdLevel":0.1075,"IndicaPercentage":25.0,"SativaPercentage":75.0}]</t>
         </is>
       </c>
       <c r="H5" s="247" t="inlineStr">
@@ -16374,12 +16374,12 @@
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>62112</t>
+          <t>62119</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t>Terpenomics Strain 0827-1402</t>
+          <t>Terpenomics Strain 0829-1427</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
@@ -16389,7 +16389,7 @@
       </c>
       <c r="G9" s="255" t="inlineStr">
         <is>
-          <t>[{"Id":62112,"Name":"Terpenomics Strain 0827-1402","TestingStatus":"None","ThcLevel":0.1865,"CbdLevel":0.1075,"IndicaPercentage":60.0,"SativaPercentage":40.0}]</t>
+          <t>[{"Id":62119,"Name":"Terpenomics Strain 0829-1427","TestingStatus":"None","ThcLevel":0.1865,"CbdLevel":0.1075,"IndicaPercentage":60.0,"SativaPercentage":40.0}]</t>
         </is>
       </c>
       <c r="H9" s="247" t="inlineStr">
@@ -16454,22 +16454,22 @@
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>62112</t>
+          <t>62119</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t>Terpenomics Strain 0827-1402</t>
+          <t>Terpenomics Strain 0829-1427</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/strains/v2/62112?licenseNumber=SF-SBX-NY-3-30301</t>
+          <t>https://sandbox-api-ny.metrc.com/strains/v2/62119?licenseNumber=SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="G13" s="255" t="inlineStr">
         <is>
-          <t>{"Id":62112,"Name":"Terpenomics Strain 0827-1402","TestingStatus":"None","ThcLevel":0.1865,"CbdLevel":0.1075,"IndicaPercentage":60.0,"SativaPercentage":40.0,"IsUsed":false,"Genetics":"60% Indica / 40% Sativa"}</t>
+          <t>{"Id":62119,"Name":"Terpenomics Strain 0829-1427","TestingStatus":"None","ThcLevel":0.1865,"CbdLevel":0.1075,"IndicaPercentage":60.0,"SativaPercentage":40.0,"IsUsed":false,"Genetics":"60% Indica / 40% Sativa"}</t>
         </is>
       </c>
       <c r="H13" s="247" t="inlineStr">
@@ -16762,12 +16762,12 @@
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>293817</t>
+          <t>294234</t>
         </is>
       </c>
       <c r="E5" s="250" t="inlineStr">
         <is>
-          <t>Terpenomics Item 0827-1402</t>
+          <t>Terpenomics Item 0829-1427</t>
         </is>
       </c>
       <c r="F5" s="247" t="inlineStr">
@@ -16777,7 +16777,7 @@
       </c>
       <c r="G5" s="255" t="inlineStr">
         <is>
-          <t>[{"ItemCategory":"Bud/Flower - Bulk","Name":"Terpenomics Item 0827-1402","UnitOfMeasure":"Grams","Strain":"Terpenomics Strain 0827-1402"}]</t>
+          <t>[{"ItemCategory":"Bud/Flower - Bulk","Name":"Terpenomics Item 0829-1427","UnitOfMeasure":"Grams","Strain":"Terpenomics Strain 0829-1427"}]</t>
         </is>
       </c>
       <c r="H5" s="247" t="inlineStr">
@@ -16850,12 +16850,12 @@
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>293817</t>
+          <t>294234</t>
         </is>
       </c>
       <c r="E9" s="250" t="inlineStr">
         <is>
-          <t>Terpenomics Item 0827-1402</t>
+          <t>Terpenomics Item 0829-1427</t>
         </is>
       </c>
       <c r="F9" s="247" t="inlineStr">
@@ -16865,7 +16865,7 @@
       </c>
       <c r="G9" s="255" t="inlineStr">
         <is>
-          <t>[{"ItemCategory":"Bud/Flower - Bulk","Name":"Terpenomics Item 0827-1402","UnitOfMeasure":"Kilograms","Strain":"Terpenomics Strain 0827-1402","Id":293817}]</t>
+          <t>[{"ItemCategory":"Bud/Flower - Bulk","Name":"Terpenomics Item 0829-1427","UnitOfMeasure":"Kilograms","Strain":"Terpenomics Strain 0829-1427","Id":294234}]</t>
         </is>
       </c>
       <c r="H9" s="247" t="inlineStr">
@@ -16930,22 +16930,22 @@
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>293817</t>
+          <t>294234</t>
         </is>
       </c>
       <c r="E13" s="250" t="inlineStr">
         <is>
-          <t>Terpenomics Item 0827-1402</t>
+          <t>Terpenomics Item 0829-1427</t>
         </is>
       </c>
       <c r="F13" s="247" t="inlineStr">
         <is>
-          <t>https://sandbox-api-ny.metrc.com/items/v2/293817?licenseNumber=SF-SBX-NY-3-30301</t>
+          <t>https://sandbox-api-ny.metrc.com/items/v2/294234?licenseNumber=SF-SBX-NY-3-30301</t>
         </is>
       </c>
       <c r="G13" s="255" t="inlineStr">
         <is>
-          <t>{"Id":293817,"Name":"Terpenomics Item 0827-1402","GlobalProductName":null,"GlobalProductNumber":null,"ProductCategoryName":"Bud/Flower - Bulk","ProductCategoryType":"Buds","IsExpirationDateRequired":false,"HasExpirationDate":false,"IsSellByDateRequired":false,"HasSellByDate":false,"IsUseByDateRequired":false,"HasUseByDate":false,"QuantityType":"WeightBased","DefaultLabTestingState":"NotSubmitted","UnitOfMeasureName":"Kilograms","ApprovalStatus":"Approved","ApprovalStatusDateTime":"2026-08-27T14:02:08+00:00","StrainId":62112,"StrainName":"Terpenomics Strain 0827-1402","ItemBrandId":0,"ItemBrandName":null,"AdministrationMethod":"","UnitCbdPercent":null,"UnitCbdContent":null,"UnitCbdContentUnitOfMeasureName":null,"UnitCbdContentDose":null,"UnitCbdContentDoseUnitOfMeasureName":null,"UnitCbdAPercent":null,"UnitCbdAContent":null,"UnitCbdAContentUnitOfMeasureName":null,"UnitCbdAContentDose":null,"UnitCbdAContentDoseUnitOfMeasureName":null,"UnitThcAPercent":null,"UnitThcAContent":null,"UnitThcAContentUnitOfMeasureName":null,"UnitThcAContentDose":null,"UnitThcAContentDoseUnitOfMeasureId":null,"UnitThcAContentDoseUnitOfMeasureName":null,"UnitThcPercent":null,"UnitThcContent":null,"UnitThcContentUnitOfMeasureName":null,"UnitThcContentDose":null,"UnitThcContentDoseUnitOfMeasureId":null,"UnitThcContentDoseUnitOfMeasureName":null,"UnitVolume":null,"UnitVolumeUnitOfMeasureName":null,"UnitWeight":null,"UnitWeightUnitOfMeasureName":null,"ServingSize":"","NumberOfDoses":null,"UnitQuantity":null,"UnitQuantityUnitOfMeasureName":null,"PublicIngredients":"","Description":"","Allergens":"","ProductImages":[],"ProductPhotoDescription":"","LabelImages":[],"LabelPhotoDescription":"","PackagingImages":[],"PackagingPhotoDescription":"","ProductPDFDocuments":[],"IsUsed":false,"CreatedDateTime":"2026-08-27T14:02:07.54+00:00","LabTestBatchNames":[],"ProcessingJobCategoryName":null,"ProcessingJobTypeName":null,"ProductBrandName":null}</t>
+          <t>{"Id":294234,"Name":"Terpenomics Item 0829-1427","GlobalProductName":null,"GlobalProductNumber":null,"ProductCategoryName":"Bud/Flower - Bulk","ProductCategoryType":"Buds","IsExpirationDateRequired":false,"HasExpirationDate":false,"IsSellByDateRequired":false,"HasSellByDate":false,"IsUseByDateRequired":false,"HasUseByDate":false,"QuantityType":"WeightBased","DefaultLabTestingState":"NotSubmitted","UnitOfMeasureName":"Kilograms","ApprovalStatus":"Approved","ApprovalStatusDateTime":"2026-08-29T14:27:48+00:00","StrainId":62119,"StrainName":"Terpenomics Strain 0829-1427","ItemBrandId":0,"ItemBrandName":null,"AdministrationMethod":"","UnitCbdPercent":null,"UnitCbdContent":null,"UnitCbdContentUnitOfMeasureName":null,"UnitCbdContentDose":null,"UnitCbdContentDoseUnitOfMeasureName":null,"UnitCbdAPercent":null,"UnitCbdAContent":null,"UnitCbdAContentUnitOfMeasureName":null,"UnitCbdAContentDose":null,"UnitCbdAContentDoseUnitOfMeasureName":null,"UnitThcAPercent":null,"UnitThcAContent":null,"UnitThcAContentUnitOfMeasureName":null,"UnitThcAContentDose":null,"UnitThcAContentDoseUnitOfMeasureId":null,"UnitThcAContentDoseUnitOfMeasureName":null,"UnitThcPercent":null,"UnitThcContent":null,"UnitThcContentUnitOfMeasureName":null,"UnitThcContentDose":null,"UnitThcContentDoseUnitOfMeasureId":null,"UnitThcContentDoseUnitOfMeasureName":null,"UnitVolume":null,"UnitVolumeUnitOfMeasureName":null,"UnitWeight":null,"UnitWeightUnitOfMeasureName":null,"ServingSize":"","NumberOfDoses":null,"UnitQuantity":null,"UnitQuantityUnitOfMeasureName":null,"PublicIngredients":"","Description":"","Allergens":"","ProductImages":[],"ProductPhotoDescription":"","LabelImages":[],"LabelPhotoDescription":"","PackagingImages":[],"PackagingPhotoDescription":"","ProductPDFDocuments":[],"IsUsed":false,"CreatedDateTime":"2026-08-29T14:27:47.9+00:00","LabTestBatchNames":[],"ProcessingJobCategoryName":null,"ProcessingJobTypeName":null,"ProductBrandName":null}</t>
         </is>
       </c>
       <c r="H13" s="247" t="inlineStr">
